--- a/japan_studies_problem_list.xlsx
+++ b/japan_studies_problem_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shuum\Desktop\JC復習用アプリ\JC_reviewapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04935298-ACA5-41DB-B229-0AFA1D39E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BFAD88-2017-44ED-84E6-46FED092970B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,12 +21,25 @@
     <sheet name="画像準備リスト" sheetId="6" r:id="rId6"/>
     <sheet name="ランダム出題メモ" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3984" uniqueCount="1190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4790" uniqueCount="1879">
   <si>
     <t>日本事情オンライン復習　問題入力テンプレート</t>
   </si>
@@ -4220,6 +4233,5689 @@
   <si>
     <t>カブト虫</t>
     <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>やけど</t>
+  </si>
+  <si>
+    <t>ねんざ</t>
+  </si>
+  <si>
+    <t>めまい</t>
+  </si>
+  <si>
+    <t>くしゃみ</t>
+  </si>
+  <si>
+    <t>うがい</t>
+  </si>
+  <si>
+    <t>つがい</t>
+  </si>
+  <si>
+    <t>むがい</t>
+  </si>
+  <si>
+    <t>ふがい</t>
+  </si>
+  <si>
+    <t>小児科</t>
+  </si>
+  <si>
+    <t>こじか</t>
+  </si>
+  <si>
+    <t>しょうじか</t>
+  </si>
+  <si>
+    <t>しょうにか</t>
+  </si>
+  <si>
+    <t>しょうごか</t>
+  </si>
+  <si>
+    <t>なだれ</t>
+  </si>
+  <si>
+    <t>つらら</t>
+  </si>
+  <si>
+    <t>つなみ</t>
+  </si>
+  <si>
+    <t>ひょう</t>
+  </si>
+  <si>
+    <t>吹雪</t>
+  </si>
+  <si>
+    <t>ふゆき</t>
+  </si>
+  <si>
+    <t>ふむき</t>
+  </si>
+  <si>
+    <t>ふうき</t>
+  </si>
+  <si>
+    <t>ふぶき</t>
+  </si>
+  <si>
+    <t>車椅子</t>
+  </si>
+  <si>
+    <t>地震、雷、火事、親父</t>
+  </si>
+  <si>
+    <t>松葉杖</t>
+  </si>
+  <si>
+    <t>もんぺ</t>
+  </si>
+  <si>
+    <t>たすき</t>
+  </si>
+  <si>
+    <t>振り袖</t>
+  </si>
+  <si>
+    <t>足袋</t>
+  </si>
+  <si>
+    <t>げた</t>
+  </si>
+  <si>
+    <t>わらじ</t>
+  </si>
+  <si>
+    <t>ぞうり</t>
+  </si>
+  <si>
+    <t>たび</t>
+  </si>
+  <si>
+    <t>兜・鎧</t>
+  </si>
+  <si>
+    <t>ふんどし</t>
+  </si>
+  <si>
+    <t>セーラー服</t>
+  </si>
+  <si>
+    <t>喪服</t>
+  </si>
+  <si>
+    <t>十二単</t>
+  </si>
+  <si>
+    <t>じゅうにたん</t>
+  </si>
+  <si>
+    <t>はにたん</t>
+  </si>
+  <si>
+    <t>じゅうにひとえ</t>
+  </si>
+  <si>
+    <t>かみひとえ</t>
+  </si>
+  <si>
+    <t>ちょんまげ</t>
+  </si>
+  <si>
+    <t>「ちょんまげ」をしているのは、だれですか。</t>
+  </si>
+  <si>
+    <t>ランドセル</t>
+  </si>
+  <si>
+    <t>厳島神社</t>
+  </si>
+  <si>
+    <t>いくつしま</t>
+  </si>
+  <si>
+    <t>いつくしま</t>
+  </si>
+  <si>
+    <t>つくいしま</t>
+  </si>
+  <si>
+    <t>ついくしま</t>
+  </si>
+  <si>
+    <t>浅草寺</t>
+  </si>
+  <si>
+    <t>通天閣</t>
+  </si>
+  <si>
+    <t>大正時代</t>
+  </si>
+  <si>
+    <t>だいせい</t>
+  </si>
+  <si>
+    <t>たいせい</t>
+  </si>
+  <si>
+    <t>たいしょう</t>
+  </si>
+  <si>
+    <t>おおしょう</t>
+  </si>
+  <si>
+    <t>明治時代</t>
+  </si>
+  <si>
+    <t>聖徳太子</t>
+  </si>
+  <si>
+    <t>せいとくたこ</t>
+  </si>
+  <si>
+    <t>しょうとくたこ</t>
+  </si>
+  <si>
+    <t>しょうとくたじ</t>
+  </si>
+  <si>
+    <t>しょうとくたいし</t>
+  </si>
+  <si>
+    <t>鳥居</t>
+  </si>
+  <si>
+    <t>江戸</t>
+  </si>
+  <si>
+    <t>豊臣秀吉</t>
+  </si>
+  <si>
+    <t>カエル</t>
+  </si>
+  <si>
+    <t>ヘビ</t>
+  </si>
+  <si>
+    <t>トカゲ</t>
+  </si>
+  <si>
+    <t>ワニ</t>
+  </si>
+  <si>
+    <t>カニ</t>
+  </si>
+  <si>
+    <t>エビ</t>
+  </si>
+  <si>
+    <t>カメ</t>
+  </si>
+  <si>
+    <t>クモ</t>
+  </si>
+  <si>
+    <t>アリ</t>
+  </si>
+  <si>
+    <t>バッタ</t>
+  </si>
+  <si>
+    <t>ホタル</t>
+  </si>
+  <si>
+    <t>ハエ</t>
+  </si>
+  <si>
+    <t>ミミズ</t>
+  </si>
+  <si>
+    <t>ペンギン</t>
+  </si>
+  <si>
+    <t>フクロウ</t>
+  </si>
+  <si>
+    <t>カモ</t>
+  </si>
+  <si>
+    <t>オウム</t>
+  </si>
+  <si>
+    <t>オタマジャクシ</t>
+  </si>
+  <si>
+    <t>猫の手も借りたい</t>
+  </si>
+  <si>
+    <t>ウグイス</t>
+  </si>
+  <si>
+    <t>タカ</t>
+  </si>
+  <si>
+    <t>トキ</t>
+  </si>
+  <si>
+    <t>コウノトリ</t>
+  </si>
+  <si>
+    <t>スズメの涙</t>
+  </si>
+  <si>
+    <t>三味線</t>
+  </si>
+  <si>
+    <t>みみせん</t>
+  </si>
+  <si>
+    <t>さんみせん</t>
+  </si>
+  <si>
+    <t>ざんまいせん</t>
+  </si>
+  <si>
+    <t>しゃみせん</t>
+  </si>
+  <si>
+    <t>鼓</t>
+  </si>
+  <si>
+    <t>剣道</t>
+  </si>
+  <si>
+    <t>節分</t>
+  </si>
+  <si>
+    <t>トマト</t>
+  </si>
+  <si>
+    <t>こいのぼり</t>
+  </si>
+  <si>
+    <t>サンマ</t>
+  </si>
+  <si>
+    <t>イワシ</t>
+  </si>
+  <si>
+    <t>タイ</t>
+  </si>
+  <si>
+    <t>コイ</t>
+  </si>
+  <si>
+    <t>河童</t>
+  </si>
+  <si>
+    <t>キュウリ</t>
+  </si>
+  <si>
+    <t>キャベツ</t>
+  </si>
+  <si>
+    <t>レタス</t>
+  </si>
+  <si>
+    <t>七夕</t>
+  </si>
+  <si>
+    <t>NHK</t>
+  </si>
+  <si>
+    <t>終戦記念日</t>
+  </si>
+  <si>
+    <t>カラオケ</t>
+  </si>
+  <si>
+    <t>プリンター</t>
+  </si>
+  <si>
+    <t>レコード</t>
+  </si>
+  <si>
+    <t>自動車会社</t>
+  </si>
+  <si>
+    <t>ビール</t>
+  </si>
+  <si>
+    <t>製菓会社</t>
+  </si>
+  <si>
+    <t>ガソリン</t>
+  </si>
+  <si>
+    <t>家電メーカー</t>
+  </si>
+  <si>
+    <t>サントリー</t>
+  </si>
+  <si>
+    <t>シャープ</t>
+  </si>
+  <si>
+    <t>パナソニック</t>
+  </si>
+  <si>
+    <t>夏目漱石</t>
+  </si>
+  <si>
+    <t>横綱</t>
+  </si>
+  <si>
+    <t>師走</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;熱&lt;rt&gt;あつ&lt;/rt&gt;&lt;/ruby&gt;いお&lt;ruby&gt;湯&lt;rt&gt;ゆ&lt;/rt&gt;&lt;/ruby&gt;に&lt;ruby&gt;手&lt;rt&gt;て&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;入&lt;rt&gt;い&lt;/rt&gt;&lt;/ruby&gt;れてしまいました。&lt;ruby&gt;手&lt;rt&gt;て&lt;/rt&gt;&lt;/ruby&gt;はどうなりましたか。</t>
+  </si>
+  <si>
+    <t>You put your hand in hot water. What happened to your hand?</t>
+  </si>
+  <si>
+    <t>sprain</t>
+  </si>
+  <si>
+    <t>dizziness</t>
+  </si>
+  <si>
+    <t>burn</t>
+  </si>
+  <si>
+    <t>sneeze</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;熱&lt;rt&gt;あつ&lt;/rt&gt;&lt;/ruby&gt;いお&lt;ruby&gt;湯&lt;rt&gt;ゆ&lt;/rt&gt;&lt;/ruby&gt;などに&lt;ruby&gt;触&lt;rt&gt;ふ&lt;/rt&gt;&lt;/ruby&gt;れて、&lt;ruby&gt;皮膚&lt;rt&gt;ひふ&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;傷&lt;rt&gt;いた&lt;/rt&gt;&lt;/ruby&gt;めることを「やけど」と&lt;ruby&gt;言&lt;rt&gt;い&lt;/rt&gt;&lt;/ruby&gt;います。</t>
+  </si>
+  <si>
+    <t>A burn is an injury to the skin caused by touching something hot, such as hot water.</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;手&lt;rt&gt;て&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;洗&lt;rt&gt;あら&lt;/rt&gt;&lt;/ruby&gt;って、&lt;ruby&gt;何&lt;rt&gt;なに&lt;/rt&gt;&lt;/ruby&gt;をしていますか。</t>
+  </si>
+  <si>
+    <t>After washing your hands, what are you doing?</t>
+  </si>
+  <si>
+    <t>lesson07_gargling.jpg</t>
+  </si>
+  <si>
+    <t>gargling</t>
+  </si>
+  <si>
+    <t>pair; couple</t>
+  </si>
+  <si>
+    <t>harmless</t>
+  </si>
+  <si>
+    <t>incompetence</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;口&lt;rt&gt;くち&lt;/rt&gt;&lt;/ruby&gt;に&lt;ruby&gt;水&lt;rt&gt;みず&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;含&lt;rt&gt;ふく&lt;/rt&gt;&lt;/ruby&gt;んで、のどや&lt;ruby&gt;口&lt;rt&gt;くち&lt;/rt&gt;&lt;/ruby&gt;をすすぐことを「うがい」と&lt;ruby&gt;言&lt;rt&gt;い&lt;/rt&gt;&lt;/ruby&gt;います。</t>
+  </si>
+  <si>
+    <t>Gargling means rinsing your throat or mouth with water held in your mouth.</t>
+  </si>
+  <si>
+    <t>How do you read 小児科, a department in a hospital?</t>
+  </si>
+  <si>
+    <t>しょうにか|ショウニカ</t>
+  </si>
+  <si>
+    <t>kojika</t>
+  </si>
+  <si>
+    <t>shōjika</t>
+  </si>
+  <si>
+    <t>shōnika; pediatrics</t>
+  </si>
+  <si>
+    <t>shōgoka</t>
+  </si>
+  <si>
+    <t>「&lt;ruby&gt;小児科&lt;rt&gt;しょうにか&lt;/rt&gt;&lt;/ruby&gt;」は「しょうにか」と&lt;ruby&gt;読&lt;rt&gt;よ&lt;/rt&gt;&lt;/ruby&gt;みます。&lt;ruby&gt;子&lt;rt&gt;こ&lt;/rt&gt;&lt;/ruby&gt;どもの&lt;ruby&gt;病気&lt;rt&gt;びょうき&lt;/rt&gt;&lt;/ruby&gt;やけがを&lt;ruby&gt;診&lt;rt&gt;み&lt;/rt&gt;&lt;/ruby&gt;る&lt;ruby&gt;診療科&lt;rt&gt;しんりょうか&lt;/rt&gt;&lt;/ruby&gt;です。</t>
+  </si>
+  <si>
+    <t>小児科 is read as shōnika. It is the hospital department that treats illnesses and injuries in children.</t>
+  </si>
+  <si>
+    <t>How do you read 雪崩?</t>
+  </si>
+  <si>
+    <t>なだれ|ナダレ</t>
+  </si>
+  <si>
+    <t>icicle</t>
+  </si>
+  <si>
+    <t>tsunami</t>
+  </si>
+  <si>
+    <t>avalanche</t>
+  </si>
+  <si>
+    <t>hail; graupel</t>
+  </si>
+  <si>
+    <t>「&lt;ruby&gt;雪崩&lt;rt&gt;なだれ&lt;/rt&gt;&lt;/ruby&gt;」は「なだれ」と&lt;ruby&gt;読&lt;rt&gt;よ&lt;/rt&gt;&lt;/ruby&gt;みます。&lt;ruby&gt;山&lt;rt&gt;やま&lt;/rt&gt;&lt;/ruby&gt;に&lt;ruby&gt;積&lt;rt&gt;つ&lt;/rt&gt;&lt;/ruby&gt;もった&lt;ruby&gt;雪&lt;rt&gt;ゆき&lt;/rt&gt;&lt;/ruby&gt;が、&lt;ruby&gt;急&lt;rt&gt;きゅう&lt;/rt&gt;&lt;/ruby&gt;に&lt;ruby&gt;大量&lt;rt&gt;たいりょう&lt;/rt&gt;&lt;/ruby&gt;に&lt;ruby&gt;崩&lt;rt&gt;くず&lt;/rt&gt;&lt;/ruby&gt;れ&lt;ruby&gt;落&lt;rt&gt;お&lt;/rt&gt;&lt;/ruby&gt;ちることです。</t>
+  </si>
+  <si>
+    <t>雪崩 is read as nadare. It is an avalanche, when a large mass of snow suddenly slides down a mountain.</t>
+  </si>
+  <si>
+    <t>What is hyō (hail)?</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;砂&lt;rt&gt;すな&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;粒&lt;rt&gt;つぶ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>grains of sand</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;水&lt;rt&gt;みず&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;粒&lt;rt&gt;つぶ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>drops of water</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;氷&lt;rt&gt;こおり&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;粒&lt;rt&gt;つぶ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>pieces of ice</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;石&lt;rt&gt;いし&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;粒&lt;rt&gt;つぶ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>small stones</t>
+  </si>
+  <si>
+    <t>Hail consists of pieces of ice that fall from the sky.</t>
+  </si>
+  <si>
+    <t>How do you read 吹雪?</t>
+  </si>
+  <si>
+    <t>ふぶき|フブキ</t>
+  </si>
+  <si>
+    <t>fuyuki</t>
+  </si>
+  <si>
+    <t>fumuki</t>
+  </si>
+  <si>
+    <t>fūki</t>
+  </si>
+  <si>
+    <t>fubuki; snowstorm</t>
+  </si>
+  <si>
+    <t>「&lt;ruby&gt;吹雪&lt;rt&gt;ふぶき&lt;/rt&gt;&lt;/ruby&gt;」は「ふぶき」と&lt;ruby&gt;読&lt;rt&gt;よ&lt;/rt&gt;&lt;/ruby&gt;みます。&lt;ruby&gt;強&lt;rt&gt;つよ&lt;/rt&gt;&lt;/ruby&gt;い&lt;ruby&gt;風&lt;rt&gt;かぜ&lt;/rt&gt;&lt;/ruby&gt;とともに&lt;ruby&gt;雪&lt;rt&gt;ゆき&lt;/rt&gt;&lt;/ruby&gt;が&lt;ruby&gt;激&lt;rt&gt;はげ&lt;/rt&gt;&lt;/ruby&gt;しく&lt;ruby&gt;降&lt;rt&gt;ふ&lt;/rt&gt;&lt;/ruby&gt;ることです。</t>
+  </si>
+  <si>
+    <t>吹雪 is read as fubuki. It is a snowstorm in which snow falls heavily with strong winds.</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;足&lt;rt&gt;あし&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;骨折&lt;rt&gt;こっせつ&lt;/rt&gt;&lt;/ruby&gt;しました。&lt;ruby&gt;何&lt;rt&gt;なに&lt;/rt&gt;&lt;/ruby&gt;に&lt;ruby&gt;乗&lt;rt&gt;の&lt;/rt&gt;&lt;/ruby&gt;って&lt;ruby&gt;生活&lt;rt&gt;せいかつ&lt;/rt&gt;&lt;/ruby&gt;しますか。</t>
+  </si>
+  <si>
+    <t>You broke your leg. What do you use to get around?</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;肩車&lt;rt&gt;かたぐるま&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>shoulder ride</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;乳母車&lt;rt&gt;うばぐるま&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>baby carriage</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;車椅子&lt;rt&gt;くるまいす&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>wheelchair</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;座椅子&lt;rt&gt;ざいす&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>legless floor chair</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;足&lt;rt&gt;あし&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;骨折&lt;rt&gt;こっせつ&lt;/rt&gt;&lt;/ruby&gt;して&lt;ruby&gt;歩&lt;rt&gt;ある&lt;/rt&gt;&lt;/ruby&gt;くことが&lt;ruby&gt;難&lt;rt&gt;むずか&lt;/rt&gt;&lt;/ruby&gt;しいときは、&lt;ruby&gt;車椅子&lt;rt&gt;くるまいす&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;使&lt;rt&gt;つか&lt;/rt&gt;&lt;/ruby&gt;うことがあります。</t>
+  </si>
+  <si>
+    <t>When it is difficult to walk because of a broken leg, a wheelchair may be used.</t>
+  </si>
+  <si>
+    <t>「&lt;ruby&gt;怖&lt;rt&gt;こわ&lt;/rt&gt;&lt;/ruby&gt;い（&lt;ruby&gt;恐&lt;rt&gt;おそ&lt;/rt&gt;&lt;/ruby&gt;ろしい）もの」を&lt;ruby&gt;代表&lt;rt&gt;だいひょう&lt;/rt&gt;&lt;/ruby&gt;するものとして、「&lt;ruby&gt;地震&lt;rt&gt;じしん&lt;/rt&gt;&lt;/ruby&gt;、&lt;ruby&gt;雷&lt;rt&gt;かみなり&lt;/rt&gt;&lt;/ruby&gt;、&lt;ruby&gt;火事&lt;rt&gt;かじ&lt;/rt&gt;&lt;/ruby&gt;、○○」という&lt;ruby&gt;言葉&lt;rt&gt;ことば&lt;/rt&gt;&lt;/ruby&gt;（&lt;ruby&gt;慣用句&lt;rt&gt;かんようく&lt;/rt&gt;&lt;/ruby&gt;）があります。○○には、&lt;ruby&gt;何&lt;rt&gt;なに&lt;/rt&gt;&lt;/ruby&gt;が&lt;ruby&gt;入&lt;rt&gt;はい&lt;/rt&gt;&lt;/ruby&gt;りますか。</t>
+  </si>
+  <si>
+    <t>There is a traditional saying listing frightening things: “earthquakes, thunder, fires, and ___.” What goes in the blank?</t>
+  </si>
+  <si>
+    <t>親父|おやじ|オヤジ</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;親父&lt;rt&gt;おやじ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>father; old man</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;母親&lt;rt&gt;ははおや&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>mother</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;洪水&lt;rt&gt;こうずい&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>flood</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;台風&lt;rt&gt;たいふう&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>typhoon</t>
+  </si>
+  <si>
+    <t>「&lt;ruby&gt;地震&lt;rt&gt;じしん&lt;/rt&gt;&lt;/ruby&gt;、&lt;ruby&gt;雷&lt;rt&gt;かみなり&lt;/rt&gt;&lt;/ruby&gt;、&lt;ruby&gt;火事&lt;rt&gt;かじ&lt;/rt&gt;&lt;/ruby&gt;、&lt;ruby&gt;親父&lt;rt&gt;おやじ&lt;/rt&gt;&lt;/ruby&gt;」という&lt;ruby&gt;言&lt;rt&gt;い&lt;/rt&gt;&lt;/ruby&gt;い&lt;ruby&gt;方&lt;rt&gt;かた&lt;/rt&gt;&lt;/ruby&gt;があります。&lt;ruby&gt;昔&lt;rt&gt;むかし&lt;/rt&gt;&lt;/ruby&gt;から、&lt;ruby&gt;怖&lt;rt&gt;こわ&lt;/rt&gt;&lt;/ruby&gt;いものを&lt;ruby&gt;並&lt;rt&gt;なら&lt;/rt&gt;&lt;/ruby&gt;べた&lt;ruby&gt;言葉&lt;rt&gt;ことば&lt;/rt&gt;&lt;/ruby&gt;として&lt;ruby&gt;知&lt;rt&gt;し&lt;/rt&gt;&lt;/ruby&gt;られています。</t>
+  </si>
+  <si>
+    <t>There is a traditional expression, “earthquakes, thunder, fires, and fathers.” It is known as a list of things traditionally considered frightening.</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;転&lt;rt&gt;ころ&lt;/rt&gt;&lt;/ruby&gt;んで&lt;ruby&gt;足首&lt;rt&gt;あしくび&lt;/rt&gt;&lt;/ruby&gt;をねんざしました。&lt;ruby&gt;何&lt;rt&gt;なに&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;使&lt;rt&gt;つか&lt;/rt&gt;&lt;/ruby&gt;って&lt;ruby&gt;生活&lt;rt&gt;せいかつ&lt;/rt&gt;&lt;/ruby&gt;しますか。</t>
+  </si>
+  <si>
+    <t>You fell and sprained your ankle. What do you use to help you get around?</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;鉢巻&lt;rt&gt;はちまき&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>headband</t>
+  </si>
+  <si>
+    <t>monpe work pants</t>
+  </si>
+  <si>
+    <t>tasuki sash</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;松葉杖&lt;rt&gt;まつばづえ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>crutches</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;足&lt;rt&gt;あし&lt;/rt&gt;&lt;/ruby&gt;をけがして&lt;ruby&gt;歩&lt;rt&gt;ある&lt;/rt&gt;&lt;/ruby&gt;きにくいときは、&lt;ruby&gt;松葉杖&lt;rt&gt;まつばづえ&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;使&lt;rt&gt;つか&lt;/rt&gt;&lt;/ruby&gt;うことがあります。</t>
+  </si>
+  <si>
+    <t>When a leg or ankle injury makes walking difficult, crutches may be used.</t>
+  </si>
+  <si>
+    <t>「&lt;ruby&gt;振&lt;rt&gt;ふ&lt;/rt&gt;&lt;/ruby&gt;り&lt;ruby&gt;袖&lt;rt&gt;そで&lt;/rt&gt;&lt;/ruby&gt;」は、どれですか。</t>
+  </si>
+  <si>
+    <t>Which one is a furisode?</t>
+  </si>
+  <si>
+    <t>lesson08_furisode.jpg</t>
+  </si>
+  <si>
+    <t>furisode</t>
+  </si>
+  <si>
+    <t>lesson08_yukata.jpg</t>
+  </si>
+  <si>
+    <t>yukata</t>
+  </si>
+  <si>
+    <t>lesson08_kimono-style-uniform.jpg</t>
+  </si>
+  <si>
+    <t>kimono-style uniform</t>
+  </si>
+  <si>
+    <t>lesson08_tomesode.jpg</t>
+  </si>
+  <si>
+    <t>tomesode</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;振&lt;rt&gt;ふ&lt;/rt&gt;&lt;/ruby&gt;り&lt;ruby&gt;袖&lt;rt&gt;そで&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;浴衣&lt;rt&gt;ゆかた&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;着物風&lt;rt&gt;きものふう&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;制服&lt;rt&gt;せいふく&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;留袖&lt;rt&gt;とめそで&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;振&lt;rt&gt;ふ&lt;/rt&gt;&lt;/ruby&gt;り&lt;ruby&gt;袖&lt;rt&gt;そで&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;袖&lt;rt&gt;そで&lt;/rt&gt;&lt;/ruby&gt;が&lt;ruby&gt;長&lt;rt&gt;なが&lt;/rt&gt;&lt;/ruby&gt;い&lt;ruby&gt;着物&lt;rt&gt;きもの&lt;/rt&gt;&lt;/ruby&gt;です。&lt;ruby&gt;成人式&lt;rt&gt;せいじんしき&lt;/rt&gt;&lt;/ruby&gt;などで&lt;ruby&gt;着&lt;rt&gt;き&lt;/rt&gt;&lt;/ruby&gt;ることがあります。</t>
+  </si>
+  <si>
+    <t>A furisode is a kimono with long sleeves. It is often worn for occasions such as Coming-of-Age ceremonies.</t>
+  </si>
+  <si>
+    <t>How do you read 足袋?</t>
+  </si>
+  <si>
+    <t>たび|タビ</t>
+  </si>
+  <si>
+    <t>geta sandals</t>
+  </si>
+  <si>
+    <t>straw sandals</t>
+  </si>
+  <si>
+    <t>zori sandals</t>
+  </si>
+  <si>
+    <t>tabi socks</t>
+  </si>
+  <si>
+    <t>「&lt;ruby&gt;足袋&lt;rt&gt;たび&lt;/rt&gt;&lt;/ruby&gt;」は「たび」と&lt;ruby&gt;読&lt;rt&gt;よ&lt;/rt&gt;&lt;/ruby&gt;みます。&lt;ruby&gt;着物&lt;rt&gt;きもの&lt;/rt&gt;&lt;/ruby&gt;などを&lt;ruby&gt;着&lt;rt&gt;き&lt;/rt&gt;&lt;/ruby&gt;るときに&lt;ruby&gt;履&lt;rt&gt;は&lt;/rt&gt;&lt;/ruby&gt;く、&lt;ruby&gt;親指&lt;rt&gt;おやゆび&lt;/rt&gt;&lt;/ruby&gt;とほかの&lt;ruby&gt;指&lt;rt&gt;ゆび&lt;/rt&gt;&lt;/ruby&gt;が&lt;ruby&gt;分&lt;rt&gt;わ&lt;/rt&gt;&lt;/ruby&gt;かれた&lt;ruby&gt;履物&lt;rt&gt;はきもの&lt;/rt&gt;&lt;/ruby&gt;です。</t>
+  </si>
+  <si>
+    <t>足袋 is read as tabi. Tabi are split-toe socks worn with kimono and other traditional clothing.</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;昔&lt;rt&gt;むかし&lt;/rt&gt;&lt;/ruby&gt;、「&lt;ruby&gt;兜&lt;rt&gt;かぶと&lt;/rt&gt;&lt;/ruby&gt;」と「&lt;ruby&gt;鎧&lt;rt&gt;よろい&lt;/rt&gt;&lt;/ruby&gt;」は、&lt;ruby&gt;何&lt;rt&gt;なに&lt;/rt&gt;&lt;/ruby&gt;をするときに&lt;ruby&gt;身&lt;rt&gt;み&lt;/rt&gt;&lt;/ruby&gt;につけていましたか。</t>
+  </si>
+  <si>
+    <t>In the past, when were helmets and armor worn?</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;戦&lt;rt&gt;たたか&lt;/rt&gt;&lt;/ruby&gt;い（&lt;ruby&gt;戦争&lt;rt&gt;せんそう&lt;/rt&gt;&lt;/ruby&gt;）</t>
+  </si>
+  <si>
+    <t>battle; war</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;掃除&lt;rt&gt;そうじ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>cleaning</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;運動&lt;rt&gt;うんどう&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>exercise</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;登山&lt;rt&gt;とざん&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>mountain climbing</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;兜&lt;rt&gt;かぶと&lt;/rt&gt;&lt;/ruby&gt;と&lt;ruby&gt;鎧&lt;rt&gt;よろい&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;昔&lt;rt&gt;むかし&lt;/rt&gt;&lt;/ruby&gt;、&lt;ruby&gt;武士&lt;rt&gt;ぶし&lt;/rt&gt;&lt;/ruby&gt;などが&lt;ruby&gt;戦&lt;rt&gt;たたか&lt;/rt&gt;&lt;/ruby&gt;いのときに&lt;ruby&gt;身&lt;rt&gt;み&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;守&lt;rt&gt;まも&lt;/rt&gt;&lt;/ruby&gt;るために&lt;ruby&gt;身&lt;rt&gt;み&lt;/rt&gt;&lt;/ruby&gt;につけました。</t>
+  </si>
+  <si>
+    <t>In the past, warriors such as samurai wore helmets and armor to protect themselves in battle.</t>
+  </si>
+  <si>
+    <t>「PTA」と&lt;ruby&gt;書&lt;rt&gt;か&lt;/rt&gt;&lt;/ruby&gt;かれたものを&lt;ruby&gt;身&lt;rt&gt;み&lt;/rt&gt;&lt;/ruby&gt;につけています。これは、&lt;ruby&gt;何&lt;rt&gt;なん&lt;/rt&gt;&lt;/ruby&gt;ですか。</t>
+  </si>
+  <si>
+    <t>This person is wearing something marked “PTA.” What is it?</t>
+  </si>
+  <si>
+    <t>lesson08_tasuki.jpg</t>
+  </si>
+  <si>
+    <t>たすき|タスキ</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;帯&lt;rt&gt;おび&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>obi belt</t>
+  </si>
+  <si>
+    <t>fundoshi loincloth</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;袈裟&lt;rt&gt;けさ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Buddhist priest’s robe</t>
+  </si>
+  <si>
+    <t>これは「たすき」です。&lt;ruby&gt;肩&lt;rt&gt;かた&lt;/rt&gt;&lt;/ruby&gt;から&lt;ruby&gt;斜&lt;rt&gt;なな&lt;/rt&gt;&lt;/ruby&gt;めにかける&lt;ruby&gt;細長&lt;rt&gt;ほそなが&lt;/rt&gt;&lt;/ruby&gt;い&lt;ruby&gt;布&lt;rt&gt;ぬの&lt;/rt&gt;&lt;/ruby&gt;で、&lt;ruby&gt;学校&lt;rt&gt;がっこう&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;活動&lt;rt&gt;かつどう&lt;/rt&gt;&lt;/ruby&gt;などでも&lt;ruby&gt;使&lt;rt&gt;つか&lt;/rt&gt;&lt;/ruby&gt;われます。</t>
+  </si>
+  <si>
+    <t>This is a tasuki, a long narrow sash worn diagonally over the shoulder. It is also used in activities such as school or PTA events.</t>
+  </si>
+  <si>
+    <t>lesson08_sailor-uniform.jpg</t>
+  </si>
+  <si>
+    <t>sailor-style school uniform</t>
+  </si>
+  <si>
+    <t>セーラー服|セーラーふく</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;詰&lt;rt&gt;つ&lt;/rt&gt;&lt;/ruby&gt;め&lt;ruby&gt;襟&lt;rt&gt;えり&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>stand-collar school uniform</t>
+  </si>
+  <si>
+    <t>セーラー&lt;ruby&gt;服&lt;rt&gt;ふく&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;喪服&lt;rt&gt;もふく&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>mourning clothes</t>
+  </si>
+  <si>
+    <t>これは、セーラー&lt;ruby&gt;服&lt;rt&gt;ふく&lt;/rt&gt;&lt;/ruby&gt;です。セーラー&lt;ruby&gt;服&lt;rt&gt;ふく&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;日本&lt;rt&gt;にほん&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;学校&lt;rt&gt;がっこう&lt;/rt&gt;&lt;/ruby&gt;で&lt;ruby&gt;制服&lt;rt&gt;せいふく&lt;/rt&gt;&lt;/ruby&gt;として&lt;ruby&gt;使&lt;rt&gt;つか&lt;/rt&gt;&lt;/ruby&gt;われてきた&lt;ruby&gt;服&lt;rt&gt;ふく&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;一&lt;rt&gt;ひと&lt;/rt&gt;&lt;/ruby&gt;つです。</t>
+  </si>
+  <si>
+    <t>This is a sailor-style school uniform, one type of uniform traditionally used in Japanese schools.</t>
+  </si>
+  <si>
+    <t>How do you read 十二単?</t>
+  </si>
+  <si>
+    <t>じゅうにひとえ|ジュウニヒトエ</t>
+  </si>
+  <si>
+    <t>jūnitan</t>
+  </si>
+  <si>
+    <t>hanitan</t>
+  </si>
+  <si>
+    <t>jūnihitoe</t>
+  </si>
+  <si>
+    <t>kamihitoe</t>
+  </si>
+  <si>
+    <t>十二単 is read as jūnihitoe. It is known as a layered court costume worn by women in the Heian period.</t>
+  </si>
+  <si>
+    <t>Who is shown wearing a chonmage hairstyle?</t>
+  </si>
+  <si>
+    <t>お&lt;ruby&gt;坊&lt;rt&gt;ぼう&lt;/rt&gt;&lt;/ruby&gt;さん</t>
+  </si>
+  <si>
+    <t>Buddhist priest</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;武士&lt;rt&gt;ぶし&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>samurai; warrior</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;花婿&lt;rt&gt;はなむこ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>groom</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;花嫁&lt;rt&gt;はなよめ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>bride</t>
+  </si>
+  <si>
+    <t>ちょんまげは、&lt;ruby&gt;江戸時代&lt;rt&gt;えどじだい&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;武士&lt;rt&gt;ぶし&lt;/rt&gt;&lt;/ruby&gt;などに&lt;ruby&gt;見&lt;rt&gt;み&lt;/rt&gt;&lt;/ruby&gt;られた&lt;ruby&gt;髪型&lt;rt&gt;かみがた&lt;/rt&gt;&lt;/ruby&gt;です。</t>
+  </si>
+  <si>
+    <t>The chonmage is a hairstyle associated with samurai and others in the Edo period.</t>
+  </si>
+  <si>
+    <t>ふつう「ランドセル」を&lt;ruby&gt;背負&lt;rt&gt;せお&lt;/rt&gt;&lt;/ruby&gt;うのは、だれですか。</t>
+  </si>
+  <si>
+    <t>Who usually carries a randoseru school backpack?</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;幼稚園児&lt;rt&gt;ようちえんじ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>kindergarten child</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;小学生&lt;rt&gt;しょうがくせい&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>elementary school student</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;中学生&lt;rt&gt;ちゅうがくせい&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>junior high school student</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;高校生&lt;rt&gt;こうこうせい&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>high school student</t>
+  </si>
+  <si>
+    <t>ランドセルは、ふつう&lt;ruby&gt;小学生&lt;rt&gt;しょうがくせい&lt;/rt&gt;&lt;/ruby&gt;が&lt;ruby&gt;教科書&lt;rt&gt;きょうかしょ&lt;/rt&gt;&lt;/ruby&gt;などを&lt;ruby&gt;入&lt;rt&gt;い&lt;/rt&gt;&lt;/ruby&gt;れて&lt;ruby&gt;背負&lt;rt&gt;せお&lt;/rt&gt;&lt;/ruby&gt;うかばんです。</t>
+  </si>
+  <si>
+    <t>A randoseru is a school backpack usually carried by elementary school students for books and other school items.</t>
+  </si>
+  <si>
+    <t>「&lt;ruby&gt;喪服&lt;rt&gt;もふく&lt;/rt&gt;&lt;/ruby&gt;」は、どんなときに&lt;ruby&gt;着&lt;rt&gt;き&lt;/rt&gt;&lt;/ruby&gt;ますか。</t>
+  </si>
+  <si>
+    <t>When do people wear mofuku (mourning clothes)?</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;七五三&lt;rt&gt;しちごさん&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Shichi-Go-San festival</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;成人式&lt;rt&gt;せいじんしき&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Coming-of-Age ceremony</t>
+  </si>
+  <si>
+    <t>お&lt;ruby&gt;葬式&lt;rt&gt;そうしき&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>funeral</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;喪服&lt;rt&gt;もふく&lt;/rt&gt;&lt;/ruby&gt;は、お&lt;ruby&gt;葬式&lt;rt&gt;そうしき&lt;/rt&gt;&lt;/ruby&gt;など、&lt;ruby&gt;亡&lt;rt&gt;な&lt;/rt&gt;&lt;/ruby&gt;くなった&lt;ruby&gt;人&lt;rt&gt;ひと&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;悼&lt;rt&gt;いた&lt;/rt&gt;&lt;/ruby&gt;むときに&lt;ruby&gt;着&lt;rt&gt;き&lt;/rt&gt;&lt;/ruby&gt;る&lt;ruby&gt;服&lt;rt&gt;ふく&lt;/rt&gt;&lt;/ruby&gt;です。</t>
+  </si>
+  <si>
+    <t>Mofuku are mourning clothes worn at funerals and other occasions to mourn someone who has died.</t>
+  </si>
+  <si>
+    <t>How do you read 厳島 in 厳島神社?</t>
+  </si>
+  <si>
+    <t>いつくしま|イツクシマ</t>
+  </si>
+  <si>
+    <t>ikutsushima</t>
+  </si>
+  <si>
+    <t>Itsukushima</t>
+  </si>
+  <si>
+    <t>tsukuishima</t>
+  </si>
+  <si>
+    <t>tsuikushima</t>
+  </si>
+  <si>
+    <t>厳島 is read as Itsukushima. Itsukushima Shrine is located on Miyajima in Hiroshima Prefecture.</t>
+  </si>
+  <si>
+    <t>このお&lt;ruby&gt;寺&lt;rt&gt;てら&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;名前&lt;rt&gt;なまえ&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;何&lt;rt&gt;なん&lt;/rt&gt;&lt;/ruby&gt;ですか。</t>
+  </si>
+  <si>
+    <t>What is the name of this temple?</t>
+  </si>
+  <si>
+    <t>lesson09_sensoji.jpg</t>
+  </si>
+  <si>
+    <t>Sensoji Temple</t>
+  </si>
+  <si>
+    <t>浅草寺|せんそうじ|センソウジ</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;清水寺&lt;rt&gt;きよみずでら&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Kiyomizu-dera Temple</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;東大寺&lt;rt&gt;とうだいじ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Todai-ji Temple</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;浅草寺&lt;rt&gt;せんそうじ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;鹿苑寺&lt;rt&gt;ろくおんじ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Rokuon-ji Temple</t>
+  </si>
+  <si>
+    <t>This is Sensoji Temple in Asakusa, Tokyo. 浅草寺 is read as Sensōji.</t>
+  </si>
+  <si>
+    <t>「&lt;ruby&gt;通天閣&lt;rt&gt;つうてんかく&lt;/rt&gt;&lt;/ruby&gt;」は、どれですか。</t>
+  </si>
+  <si>
+    <t>Which one is Tsutenkaku?</t>
+  </si>
+  <si>
+    <t>lesson09_tokyo-tower.jpg</t>
+  </si>
+  <si>
+    <t>Tokyo Tower</t>
+  </si>
+  <si>
+    <t>lesson09_eiffel-tower.jpg</t>
+  </si>
+  <si>
+    <t>Eiffel Tower</t>
+  </si>
+  <si>
+    <t>lesson09_tsutenkaku.jpg</t>
+  </si>
+  <si>
+    <t>Tsutenkaku</t>
+  </si>
+  <si>
+    <t>lesson09_kyoto-tower.jpg</t>
+  </si>
+  <si>
+    <t>Kyoto Tower</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;東京&lt;rt&gt;とうきょう&lt;/rt&gt;&lt;/ruby&gt;タワー</t>
+  </si>
+  <si>
+    <t>エッフェル&lt;ruby&gt;塔&lt;rt&gt;とう&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;通天閣&lt;rt&gt;つうてんかく&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;京都&lt;rt&gt;きょうと&lt;/rt&gt;&lt;/ruby&gt;タワー</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;通天閣&lt;rt&gt;つうてんかく&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;大阪&lt;rt&gt;おおさか&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;新世界&lt;rt&gt;しんせかい&lt;/rt&gt;&lt;/ruby&gt;にある&lt;ruby&gt;展望塔&lt;rt&gt;てんぼうとう&lt;/rt&gt;&lt;/ruby&gt;です。</t>
+  </si>
+  <si>
+    <t>Tsutenkaku is an observation tower in the Shinsekai area of Osaka.</t>
+  </si>
+  <si>
+    <t>How do you read 大正 in 大正時代?</t>
+  </si>
+  <si>
+    <t>たいしょう|タイショウ</t>
+  </si>
+  <si>
+    <t>daisei</t>
+  </si>
+  <si>
+    <t>taisei</t>
+  </si>
+  <si>
+    <t>Taishō</t>
+  </si>
+  <si>
+    <t>ōshō</t>
+  </si>
+  <si>
+    <t>大正 is read as Taishō. The Taishō period lasted from 1912 to 1926.</t>
+  </si>
+  <si>
+    <t>「&lt;ruby&gt;明治時代&lt;rt&gt;めいじじだい&lt;/rt&gt;&lt;/ruby&gt;」は、いつ&lt;ruby&gt;頃&lt;rt&gt;ごろ&lt;/rt&gt;&lt;/ruby&gt;ですか。</t>
+  </si>
+  <si>
+    <t>Around when was the Meiji period?</t>
+  </si>
+  <si>
+    <t>12&lt;ruby&gt;世紀&lt;rt&gt;せいき&lt;/rt&gt;&lt;/ruby&gt;&lt;ruby&gt;前半&lt;rt&gt;ぜんはん&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>first half of the 12th century</t>
+  </si>
+  <si>
+    <t>15&lt;ruby&gt;世紀&lt;rt&gt;せいき&lt;/rt&gt;&lt;/ruby&gt;&lt;ruby&gt;後半&lt;rt&gt;こうはん&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>second half of the 15th century</t>
+  </si>
+  <si>
+    <t>17&lt;ruby&gt;世紀&lt;rt&gt;せいき&lt;/rt&gt;&lt;/ruby&gt;&lt;ruby&gt;前半&lt;rt&gt;ぜんはん&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>first half of the 17th century</t>
+  </si>
+  <si>
+    <t>19&lt;ruby&gt;世紀&lt;rt&gt;せいき&lt;/rt&gt;&lt;/ruby&gt;&lt;ruby&gt;後半&lt;rt&gt;こうはん&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>second half of the 19th century</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;明治時代&lt;rt&gt;めいじじだい&lt;/rt&gt;&lt;/ruby&gt;は1868&lt;ruby&gt;年&lt;rt&gt;ねん&lt;/rt&gt;&lt;/ruby&gt;から1912&lt;ruby&gt;年&lt;rt&gt;ねん&lt;/rt&gt;&lt;/ruby&gt;までです。19&lt;ruby&gt;世紀&lt;rt&gt;せいき&lt;/rt&gt;&lt;/ruby&gt;&lt;ruby&gt;後半&lt;rt&gt;こうはん&lt;/rt&gt;&lt;/ruby&gt;から20&lt;ruby&gt;世紀&lt;rt&gt;せいき&lt;/rt&gt;&lt;/ruby&gt;&lt;ruby&gt;初&lt;rt&gt;はじ&lt;/rt&gt;&lt;/ruby&gt;めにあたります。</t>
+  </si>
+  <si>
+    <t>The Meiji period lasted from 1868 to 1912, from the latter half of the 19th century into the early 20th century.</t>
+  </si>
+  <si>
+    <t>How do you read 聖徳太子?</t>
+  </si>
+  <si>
+    <t>しょうとくたいし|ショウトクタイシ</t>
+  </si>
+  <si>
+    <t>seitokutako</t>
+  </si>
+  <si>
+    <t>shōtokutako</t>
+  </si>
+  <si>
+    <t>shōtokutaji</t>
+  </si>
+  <si>
+    <t>Shōtoku Taishi</t>
+  </si>
+  <si>
+    <t>聖徳太子 is read as Shōtoku Taishi. He is known as a historical figure from the Asuka period.</t>
+  </si>
+  <si>
+    <t>lesson09_torii.jpg</t>
+  </si>
+  <si>
+    <t>torii gate</t>
+  </si>
+  <si>
+    <t>鳥居|とりい|トリイ</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;仏壇&lt;rt&gt;ぶつだん&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Buddhist altar</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;神棚&lt;rt&gt;かみだな&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>household Shinto altar</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;門松&lt;rt&gt;かどまつ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>kadomatsu</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;鳥居&lt;rt&gt;とりい&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>これは、&lt;ruby&gt;鳥居&lt;rt&gt;とりい&lt;/rt&gt;&lt;/ruby&gt;です。&lt;ruby&gt;鳥居&lt;rt&gt;とりい&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;神社&lt;rt&gt;じんじゃ&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;入口&lt;rt&gt;いりぐち&lt;/rt&gt;&lt;/ruby&gt;などにある&lt;ruby&gt;門&lt;rt&gt;もん&lt;/rt&gt;&lt;/ruby&gt;です。</t>
+  </si>
+  <si>
+    <t>This is a torii gate. Torii gates are found at the entrances to Shinto shrines and other sacred areas.</t>
+  </si>
+  <si>
+    <t>「&lt;ruby&gt;江戸&lt;rt&gt;えど&lt;/rt&gt;&lt;/ruby&gt;」は、&lt;ruby&gt;今&lt;rt&gt;いま&lt;/rt&gt;&lt;/ruby&gt;のどのあたりですか。</t>
+  </si>
+  <si>
+    <t>What present-day area was Edo?</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;横浜&lt;rt&gt;よこはま&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Yokohama</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;長崎&lt;rt&gt;ながさき&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Nagasaki</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;東京&lt;rt&gt;とうきょう&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Tokyo</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;江戸&lt;rt&gt;えど&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;今&lt;rt&gt;いま&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;東京&lt;rt&gt;とうきょう&lt;/rt&gt;&lt;/ruby&gt;にあたります。1868&lt;ruby&gt;年&lt;rt&gt;ねん&lt;/rt&gt;&lt;/ruby&gt;に「&lt;ruby&gt;東京&lt;rt&gt;とうきょう&lt;/rt&gt;&lt;/ruby&gt;」という&lt;ruby&gt;名前&lt;rt&gt;なまえ&lt;/rt&gt;&lt;/ruby&gt;になりました。</t>
+  </si>
+  <si>
+    <t>Edo corresponds to present-day Tokyo. It was renamed Tokyo in 1868.</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;大阪城&lt;rt&gt;おおさかじょう&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;建&lt;rt&gt;た&lt;/rt&gt;&lt;/ruby&gt;てた&lt;ruby&gt;人&lt;rt&gt;ひと&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;名前&lt;rt&gt;なまえ&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;何&lt;rt&gt;なん&lt;/rt&gt;&lt;/ruby&gt;ですか。</t>
+  </si>
+  <si>
+    <t>Who built Osaka Castle?</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;豊田秀吉&lt;rt&gt;とよだひでよし&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Toyoda Hideyoshi</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;豊川秀吉&lt;rt&gt;とよかわひでよし&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Toyokawa Hideyoshi</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;豊臣秀吉&lt;rt&gt;とよとみひでよし&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Toyotomi Hideyoshi</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;豊村秀吉&lt;rt&gt;とよむらひでよし&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Toyomura Hideyoshi</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;大阪城&lt;rt&gt;おおさかじょう&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;豊臣秀吉&lt;rt&gt;とよとみひでよし&lt;/rt&gt;&lt;/ruby&gt;によって&lt;ruby&gt;築&lt;rt&gt;きず&lt;/rt&gt;&lt;/ruby&gt;かれました。</t>
+  </si>
+  <si>
+    <t>Osaka Castle was built by Toyotomi Hideyoshi.</t>
+  </si>
+  <si>
+    <t>lesson10_frog.jpg</t>
+  </si>
+  <si>
+    <t>frog</t>
+  </si>
+  <si>
+    <t>カエル|蛙|かえる</t>
+  </si>
+  <si>
+    <t>snake</t>
+  </si>
+  <si>
+    <t>lizard</t>
+  </si>
+  <si>
+    <t>crocodile; alligator</t>
+  </si>
+  <si>
+    <t>これは、カエルです。カエルは、&lt;ruby&gt;水辺&lt;rt&gt;みずべ&lt;/rt&gt;&lt;/ruby&gt;などでよく&lt;ruby&gt;見&lt;rt&gt;み&lt;/rt&gt;&lt;/ruby&gt;られる&lt;ruby&gt;生&lt;rt&gt;い&lt;/rt&gt;&lt;/ruby&gt;き&lt;ruby&gt;物&lt;rt&gt;もの&lt;/rt&gt;&lt;/ruby&gt;です。</t>
+  </si>
+  <si>
+    <t>This is a frog. Frogs are animals commonly found around water.</t>
+  </si>
+  <si>
+    <t>lesson10_crab.jpg</t>
+  </si>
+  <si>
+    <t>crab</t>
+  </si>
+  <si>
+    <t>カニ|蟹|かに</t>
+  </si>
+  <si>
+    <t>turtle</t>
+  </si>
+  <si>
+    <t>これは、カニです。カニは、&lt;ruby&gt;海&lt;rt&gt;うみ&lt;/rt&gt;&lt;/ruby&gt;や&lt;ruby&gt;川&lt;rt&gt;かわ&lt;/rt&gt;&lt;/ruby&gt;などにすむ&lt;ruby&gt;生&lt;rt&gt;い&lt;/rt&gt;&lt;/ruby&gt;き&lt;ruby&gt;物&lt;rt&gt;もの&lt;/rt&gt;&lt;/ruby&gt;です。</t>
+  </si>
+  <si>
+    <t>This is a crab. Crabs are animals that live in places such as the sea and rivers.</t>
+  </si>
+  <si>
+    <t>これは、&lt;ruby&gt;何&lt;rt&gt;なん&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;巣&lt;rt&gt;す&lt;/rt&gt;&lt;/ruby&gt;ですか。</t>
+  </si>
+  <si>
+    <t>What kind of web is this?</t>
+  </si>
+  <si>
+    <t>lesson10_spider-web.jpg</t>
+  </si>
+  <si>
+    <t>spider web</t>
+  </si>
+  <si>
+    <t>クモ|蜘蛛|くも|クモの巣|くもの巣|蜘蛛の巣</t>
+  </si>
+  <si>
+    <t>spider</t>
+  </si>
+  <si>
+    <t>ant</t>
+  </si>
+  <si>
+    <t>grasshopper</t>
+  </si>
+  <si>
+    <t>これは、クモの&lt;ruby&gt;巣&lt;rt&gt;す&lt;/rt&gt;&lt;/ruby&gt;です。クモは、&lt;ruby&gt;糸&lt;rt&gt;いと&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;出&lt;rt&gt;だ&lt;/rt&gt;&lt;/ruby&gt;して&lt;ruby&gt;巣&lt;rt&gt;す&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;作&lt;rt&gt;つく&lt;/rt&gt;&lt;/ruby&gt;ります。</t>
+  </si>
+  <si>
+    <t>This is a spider web. Spiders produce silk and use it to make webs.</t>
+  </si>
+  <si>
+    <t>おしりが&lt;ruby&gt;光&lt;rt&gt;ひか&lt;/rt&gt;&lt;/ruby&gt;る&lt;ruby&gt;虫&lt;rt&gt;むし&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;何&lt;rt&gt;なん&lt;/rt&gt;&lt;/ruby&gt;ですか。</t>
+  </si>
+  <si>
+    <t>What insect has a glowing abdomen?</t>
+  </si>
+  <si>
+    <t>ホタル|蛍|ほたる</t>
+  </si>
+  <si>
+    <t>firefly</t>
+  </si>
+  <si>
+    <t>fly</t>
+  </si>
+  <si>
+    <t>earthworm</t>
+  </si>
+  <si>
+    <t>ホタルは、おしりの&lt;ruby&gt;部分&lt;rt&gt;ぶぶん&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;光&lt;rt&gt;ひか&lt;/rt&gt;&lt;/ruby&gt;らせる&lt;ruby&gt;虫&lt;rt&gt;むし&lt;/rt&gt;&lt;/ruby&gt;です。&lt;ruby&gt;初夏&lt;rt&gt;しょか&lt;/rt&gt;&lt;/ruby&gt;ごろに&lt;ruby&gt;見&lt;rt&gt;み&lt;/rt&gt;&lt;/ruby&gt;られます。</t>
+  </si>
+  <si>
+    <t>Fireflies are insects that produce light from their abdomens. They can often be seen in early summer.</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;空&lt;rt&gt;そら&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;飛&lt;rt&gt;と&lt;/rt&gt;&lt;/ruby&gt;べない&lt;ruby&gt;鳥&lt;rt&gt;とり&lt;/rt&gt;&lt;/ruby&gt;は、どれですか。</t>
+  </si>
+  <si>
+    <t>Which bird cannot fly?</t>
+  </si>
+  <si>
+    <t>owl</t>
+  </si>
+  <si>
+    <t>duck</t>
+  </si>
+  <si>
+    <t>parrot</t>
+  </si>
+  <si>
+    <t>penguin</t>
+  </si>
+  <si>
+    <t>ペンギンは&lt;ruby&gt;鳥&lt;rt&gt;とり&lt;/rt&gt;&lt;/ruby&gt;ですが、&lt;ruby&gt;空&lt;rt&gt;そら&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;飛&lt;rt&gt;と&lt;/rt&gt;&lt;/ruby&gt;ぶことはできません。&lt;ruby&gt;翼&lt;rt&gt;つばさ&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;使&lt;rt&gt;つか&lt;/rt&gt;&lt;/ruby&gt;って&lt;ruby&gt;水&lt;rt&gt;みず&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;中&lt;rt&gt;なか&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;泳&lt;rt&gt;およ&lt;/rt&gt;&lt;/ruby&gt;ぎます。</t>
+  </si>
+  <si>
+    <t>Penguins are birds, but they cannot fly. They use their wings to swim through the water.</t>
+  </si>
+  <si>
+    <t>「オタマジャクシ」は、&lt;ruby&gt;何&lt;rt&gt;なん&lt;/rt&gt;&lt;/ruby&gt;ですか。</t>
+  </si>
+  <si>
+    <t>What is a tadpole?</t>
+  </si>
+  <si>
+    <t>スズメの&lt;ruby&gt;子&lt;rt&gt;こ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>a baby sparrow</t>
+  </si>
+  <si>
+    <t>ツバメの&lt;ruby&gt;子&lt;rt&gt;こ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>a baby swallow</t>
+  </si>
+  <si>
+    <t>カエルの&lt;ruby&gt;子&lt;rt&gt;こ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>a young frog; tadpole</t>
+  </si>
+  <si>
+    <t>ハチの&lt;ruby&gt;子&lt;rt&gt;こ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>bee larva</t>
+  </si>
+  <si>
+    <t>オタマジャクシは、カエルの&lt;ruby&gt;子&lt;rt&gt;こ&lt;/rt&gt;&lt;/ruby&gt;どもです。&lt;ruby&gt;水&lt;rt&gt;みず&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;中&lt;rt&gt;なか&lt;/rt&gt;&lt;/ruby&gt;で&lt;ruby&gt;育&lt;rt&gt;そだ&lt;/rt&gt;&lt;/ruby&gt;ち、やがて&lt;ruby&gt;足&lt;rt&gt;あし&lt;/rt&gt;&lt;/ruby&gt;が&lt;ruby&gt;生&lt;rt&gt;は&lt;/rt&gt;&lt;/ruby&gt;えてカエルになります。</t>
+  </si>
+  <si>
+    <t>A tadpole is a young frog. It grows in water, develops legs, and eventually becomes a frog.</t>
+  </si>
+  <si>
+    <t>「&lt;ruby&gt;猫&lt;rt&gt;ねこ&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;手&lt;rt&gt;て&lt;/rt&gt;&lt;/ruby&gt;も&lt;ruby&gt;借&lt;rt&gt;か&lt;/rt&gt;&lt;/ruby&gt;りたい」のは、どんなときですか。</t>
+  </si>
+  <si>
+    <t>When would you say “I would even borrow a cat’s paw”?</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;暇&lt;rt&gt;ひま&lt;/rt&gt;&lt;/ruby&gt;なとき</t>
+  </si>
+  <si>
+    <t>when you have free time</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;楽&lt;rt&gt;たの&lt;/rt&gt;&lt;/ruby&gt;しいとき</t>
+  </si>
+  <si>
+    <t>when you are having fun</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;忙&lt;rt&gt;いそが&lt;/rt&gt;&lt;/ruby&gt;しいとき</t>
+  </si>
+  <si>
+    <t>when you are very busy</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;甘&lt;rt&gt;あま&lt;/rt&gt;&lt;/ruby&gt;えたいとき</t>
+  </si>
+  <si>
+    <t>when you want attention or affection</t>
+  </si>
+  <si>
+    <t>「&lt;ruby&gt;猫&lt;rt&gt;ねこ&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;手&lt;rt&gt;て&lt;/rt&gt;&lt;/ruby&gt;も&lt;ruby&gt;借&lt;rt&gt;か&lt;/rt&gt;&lt;/ruby&gt;りたい」は、とても&lt;ruby&gt;忙&lt;rt&gt;いそが&lt;/rt&gt;&lt;/ruby&gt;しくて、だれでもいいから&lt;ruby&gt;手伝&lt;rt&gt;てつだ&lt;/rt&gt;&lt;/ruby&gt;ってほしいという&lt;ruby&gt;意味&lt;rt&gt;いみ&lt;/rt&gt;&lt;/ruby&gt;です。</t>
+  </si>
+  <si>
+    <t>“I would even borrow a cat’s paw” means being so busy that you would accept help from anyone.</t>
+  </si>
+  <si>
+    <t>「ホーホケキョ」と&lt;ruby&gt;鳴&lt;rt&gt;な&lt;/rt&gt;&lt;/ruby&gt;く&lt;ruby&gt;鳥&lt;rt&gt;とり&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;何&lt;rt&gt;なん&lt;/rt&gt;&lt;/ruby&gt;ですか。</t>
+  </si>
+  <si>
+    <t>Which bird sings “hō-hokekyo”?</t>
+  </si>
+  <si>
+    <t>ウグイス|鶯|うぐいす</t>
+  </si>
+  <si>
+    <t>hawk</t>
+  </si>
+  <si>
+    <t>crested ibis</t>
+  </si>
+  <si>
+    <t>stork</t>
+  </si>
+  <si>
+    <t>Japanese bush warbler</t>
+  </si>
+  <si>
+    <t>「ホーホケキョ」という&lt;ruby&gt;鳴&lt;rt&gt;な&lt;/rt&gt;&lt;/ruby&gt;き&lt;ruby&gt;声&lt;rt&gt;ごえ&lt;/rt&gt;&lt;/ruby&gt;で&lt;ruby&gt;知&lt;rt&gt;し&lt;/rt&gt;&lt;/ruby&gt;られている&lt;ruby&gt;鳥&lt;rt&gt;とり&lt;/rt&gt;&lt;/ruby&gt;は、ウグイスです。&lt;ruby&gt;春&lt;rt&gt;はる&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;感&lt;rt&gt;かん&lt;/rt&gt;&lt;/ruby&gt;じさせる&lt;ruby&gt;鳥&lt;rt&gt;とり&lt;/rt&gt;&lt;/ruby&gt;としても&lt;ruby&gt;知&lt;rt&gt;し&lt;/rt&gt;&lt;/ruby&gt;られています。</t>
+  </si>
+  <si>
+    <t>The Japanese bush warbler, or uguisu, is known for its “hō-hokekyo” song and is associated with spring in Japan.</t>
+  </si>
+  <si>
+    <t>「とても&lt;ruby&gt;少&lt;rt&gt;すく&lt;/rt&gt;&lt;/ruby&gt;ないこと」を&lt;ruby&gt;何&lt;rt&gt;なん&lt;/rt&gt;&lt;/ruby&gt;と&lt;ruby&gt;言&lt;rt&gt;い&lt;/rt&gt;&lt;/ruby&gt;いますか。</t>
+  </si>
+  <si>
+    <t>Which expression means “a very small amount”?</t>
+  </si>
+  <si>
+    <t>アリの&lt;ruby&gt;涙&lt;rt&gt;なみだ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>ant’s tears</t>
+  </si>
+  <si>
+    <t>ヒヨコの&lt;ruby&gt;涙&lt;rt&gt;なみだ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>chick’s tears</t>
+  </si>
+  <si>
+    <t>スズメの&lt;ruby&gt;涙&lt;rt&gt;なみだ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>sparrow’s tears; a very small amount</t>
+  </si>
+  <si>
+    <t>ヘビの&lt;ruby&gt;涙&lt;rt&gt;なみだ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>snake’s tears</t>
+  </si>
+  <si>
+    <t>「スズメの&lt;ruby&gt;涙&lt;rt&gt;なみだ&lt;/rt&gt;&lt;/ruby&gt;」は、「とても&lt;ruby&gt;少&lt;rt&gt;すく&lt;/rt&gt;&lt;/ruby&gt;ない&lt;ruby&gt;量&lt;rt&gt;りょう&lt;/rt&gt;&lt;/ruby&gt;」という&lt;ruby&gt;意味&lt;rt&gt;いみ&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;表現&lt;rt&gt;ひょうげん&lt;/rt&gt;&lt;/ruby&gt;です。</t>
+  </si>
+  <si>
+    <t>“A sparrow’s tears” is an expression meaning a very small amount.</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;楽器&lt;rt&gt;がっき&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;名前&lt;rt&gt;なまえ&lt;/rt&gt;&lt;/ruby&gt;「&lt;ruby&gt;三味線&lt;rt&gt;しゃみせん&lt;/rt&gt;&lt;/ruby&gt;」の&lt;ruby&gt;読&lt;rt&gt;よ&lt;/rt&gt;&lt;/ruby&gt;み&lt;ruby&gt;方&lt;rt&gt;かた&lt;/rt&gt;&lt;/ruby&gt;は、どれですか。</t>
+  </si>
+  <si>
+    <t>How do you read the name of the instrument 三味線?</t>
+  </si>
+  <si>
+    <t>しゃみせん|シャミセン</t>
+  </si>
+  <si>
+    <t>mimisen</t>
+  </si>
+  <si>
+    <t>sanmisen</t>
+  </si>
+  <si>
+    <t>zanmaisen</t>
+  </si>
+  <si>
+    <t>shamisen</t>
+  </si>
+  <si>
+    <t>三味線 is read as shamisen. It is a traditional Japanese musical instrument with three strings.</t>
+  </si>
+  <si>
+    <t>「&lt;ruby&gt;鼓&lt;rt&gt;つづみ&lt;/rt&gt;&lt;/ruby&gt;」は、どれですか。</t>
+  </si>
+  <si>
+    <t>Which one is a tsuzumi hand drum?</t>
+  </si>
+  <si>
+    <t>lesson11_tsuzumi.jpg</t>
+  </si>
+  <si>
+    <t>tsuzumi hand drum</t>
+  </si>
+  <si>
+    <t>lesson11_sensu.jpg</t>
+  </si>
+  <si>
+    <t>folding fan</t>
+  </si>
+  <si>
+    <t>lesson11_shamisen.jpg</t>
+  </si>
+  <si>
+    <t>lesson11_shakuhachi.jpg</t>
+  </si>
+  <si>
+    <t>shakuhachi</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;鼓&lt;rt&gt;つづみ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;扇子&lt;rt&gt;せんす&lt;/rt&gt;&lt;/ruby&gt;・&lt;ruby&gt;扇&lt;rt&gt;おうぎ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;三味線&lt;rt&gt;しゃみせん&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;尺八&lt;rt&gt;しゃくはち&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>shakuhachi bamboo flute</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;鼓&lt;rt&gt;つづみ&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;手&lt;rt&gt;て&lt;/rt&gt;&lt;/ruby&gt;で&lt;ruby&gt;打&lt;rt&gt;う&lt;/rt&gt;&lt;/ruby&gt;って&lt;ruby&gt;音&lt;rt&gt;おと&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;出&lt;rt&gt;だ&lt;/rt&gt;&lt;/ruby&gt;す&lt;ruby&gt;日本&lt;rt&gt;にほん&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;伝統的&lt;rt&gt;でんとうてき&lt;/rt&gt;&lt;/ruby&gt;な&lt;ruby&gt;楽器&lt;rt&gt;がっき&lt;/rt&gt;&lt;/ruby&gt;です。</t>
+  </si>
+  <si>
+    <t>A tsuzumi is a traditional Japanese hand drum played by striking it with the hands.</t>
+  </si>
+  <si>
+    <t>「&lt;ruby&gt;剣道&lt;rt&gt;けんどう&lt;/rt&gt;&lt;/ruby&gt;」は、どれですか。</t>
+  </si>
+  <si>
+    <t>Which one is kendo?</t>
+  </si>
+  <si>
+    <t>lesson11_manzai.jpg</t>
+  </si>
+  <si>
+    <t>manzai comedy</t>
+  </si>
+  <si>
+    <t>lesson11_judo.jpg</t>
+  </si>
+  <si>
+    <t>judo</t>
+  </si>
+  <si>
+    <t>lesson11_sumo.jpg</t>
+  </si>
+  <si>
+    <t>sumo</t>
+  </si>
+  <si>
+    <t>lesson11_kendo.jpg</t>
+  </si>
+  <si>
+    <t>kendo</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;漫才&lt;rt&gt;まんざい&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;柔道&lt;rt&gt;じゅうどう&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;相撲&lt;rt&gt;すもう&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;剣道&lt;rt&gt;けんどう&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;剣道&lt;rt&gt;けんどう&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;竹刀&lt;rt&gt;しない&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;使&lt;rt&gt;つか&lt;/rt&gt;&lt;/ruby&gt;って&lt;ruby&gt;行&lt;rt&gt;おこな&lt;/rt&gt;&lt;/ruby&gt;う&lt;ruby&gt;日本&lt;rt&gt;にほん&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;武道&lt;rt&gt;ぶどう&lt;/rt&gt;&lt;/ruby&gt;です。</t>
+  </si>
+  <si>
+    <t>Kendo is a Japanese martial art practiced using bamboo swords called shinai.</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;節分&lt;rt&gt;せつぶん&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;日&lt;rt&gt;ひ&lt;/rt&gt;&lt;/ruby&gt;に「&lt;ruby&gt;鬼&lt;rt&gt;おに&lt;/rt&gt;&lt;/ruby&gt;は&lt;ruby&gt;外&lt;rt&gt;そと&lt;/rt&gt;&lt;/ruby&gt;、&lt;ruby&gt;福&lt;rt&gt;ふく&lt;/rt&gt;&lt;/ruby&gt;は&lt;ruby&gt;内&lt;rt&gt;うち&lt;/rt&gt;&lt;/ruby&gt;」と&lt;ruby&gt;言&lt;rt&gt;い&lt;/rt&gt;&lt;/ruby&gt;って、&lt;ruby&gt;何&lt;rt&gt;なに&lt;/rt&gt;&lt;/ruby&gt;をまきますか。</t>
+  </si>
+  <si>
+    <t>On Setsubun, what do people throw while saying “Oni wa soto, fuku wa uchi”?</t>
+  </si>
+  <si>
+    <t>豆|まめ|マメ</t>
+  </si>
+  <si>
+    <t>eggs</t>
+  </si>
+  <si>
+    <t>tomatoes</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;豆&lt;rt&gt;まめ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>beans</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;種&lt;rt&gt;たね&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>seeds</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;節分&lt;rt&gt;せつぶん&lt;/rt&gt;&lt;/ruby&gt;には、「&lt;ruby&gt;鬼&lt;rt&gt;おに&lt;/rt&gt;&lt;/ruby&gt;は&lt;ruby&gt;外&lt;rt&gt;そと&lt;/rt&gt;&lt;/ruby&gt;、&lt;ruby&gt;福&lt;rt&gt;ふく&lt;/rt&gt;&lt;/ruby&gt;は&lt;ruby&gt;内&lt;rt&gt;うち&lt;/rt&gt;&lt;/ruby&gt;」と&lt;ruby&gt;言&lt;rt&gt;い&lt;/rt&gt;&lt;/ruby&gt;いながら&lt;ruby&gt;豆&lt;rt&gt;まめ&lt;/rt&gt;&lt;/ruby&gt;をまく「&lt;ruby&gt;豆&lt;rt&gt;まめ&lt;/rt&gt;&lt;/ruby&gt;まき」をします。</t>
+  </si>
+  <si>
+    <t>On Setsubun, people scatter beans in a custom called mamemaki while saying “Demons out, good fortune in.”</t>
+  </si>
+  <si>
+    <t>こどもの&lt;ruby&gt;日&lt;rt&gt;ひ&lt;/rt&gt;&lt;/ruby&gt;によく&lt;ruby&gt;見&lt;rt&gt;み&lt;/rt&gt;&lt;/ruby&gt;られるものです。この&lt;ruby&gt;魚&lt;rt&gt;さかな&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;何&lt;rt&gt;なん&lt;/rt&gt;&lt;/ruby&gt;ですか。</t>
+  </si>
+  <si>
+    <t>This is commonly seen on Children’s Day. What fish does it represent?</t>
+  </si>
+  <si>
+    <t>lesson11_koinobori.jpg</t>
+  </si>
+  <si>
+    <t>carp streamer</t>
+  </si>
+  <si>
+    <t>コイ|鯉|こい</t>
+  </si>
+  <si>
+    <t>Pacific saury</t>
+  </si>
+  <si>
+    <t>sardine</t>
+  </si>
+  <si>
+    <t>sea bream</t>
+  </si>
+  <si>
+    <t>carp</t>
+  </si>
+  <si>
+    <t>こいのぼりは、&lt;ruby&gt;鯉&lt;rt&gt;こい&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;形&lt;rt&gt;かたち&lt;/rt&gt;&lt;/ruby&gt;をした&lt;ruby&gt;飾&lt;rt&gt;かざ&lt;/rt&gt;&lt;/ruby&gt;りです。こどもの&lt;ruby&gt;日&lt;rt&gt;ひ&lt;/rt&gt;&lt;/ruby&gt;に、&lt;ruby&gt;子&lt;rt&gt;こ&lt;/rt&gt;&lt;/ruby&gt;どもの&lt;ruby&gt;成長&lt;rt&gt;せいちょう&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;願&lt;rt&gt;ねが&lt;/rt&gt;&lt;/ruby&gt;って&lt;ruby&gt;飾&lt;rt&gt;かざ&lt;/rt&gt;&lt;/ruby&gt;ります。</t>
+  </si>
+  <si>
+    <t>Koinobori are carp-shaped streamers displayed on Children’s Day to wish for children’s healthy growth.</t>
+  </si>
+  <si>
+    <t>かっぱ（&lt;ruby&gt;河童&lt;rt&gt;かっぱ&lt;/rt&gt;&lt;/ruby&gt;）の&lt;ruby&gt;好&lt;rt&gt;す&lt;/rt&gt;&lt;/ruby&gt;きな&lt;ruby&gt;食&lt;rt&gt;た&lt;/rt&gt;&lt;/ruby&gt;べ&lt;ruby&gt;物&lt;rt&gt;もの&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;何&lt;rt&gt;なん&lt;/rt&gt;&lt;/ruby&gt;ですか。</t>
+  </si>
+  <si>
+    <t>What food is the kappa said to like?</t>
+  </si>
+  <si>
+    <t>キュウリ|きゅうり|胡瓜</t>
+  </si>
+  <si>
+    <t>cucumber</t>
+  </si>
+  <si>
+    <t>cabbage</t>
+  </si>
+  <si>
+    <t>lettuce</t>
+  </si>
+  <si>
+    <t>かっぱ（&lt;ruby&gt;河童&lt;rt&gt;かっぱ&lt;/rt&gt;&lt;/ruby&gt;）は、&lt;ruby&gt;日本&lt;rt&gt;にほん&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;伝承&lt;rt&gt;でんしょう&lt;/rt&gt;&lt;/ruby&gt;に&lt;ruby&gt;登場&lt;rt&gt;とうじょう&lt;/rt&gt;&lt;/ruby&gt;する&lt;ruby&gt;生&lt;rt&gt;い&lt;/rt&gt;&lt;/ruby&gt;き&lt;ruby&gt;物&lt;rt&gt;もの&lt;/rt&gt;&lt;/ruby&gt;で、キュウリが&lt;ruby&gt;好&lt;rt&gt;す&lt;/rt&gt;&lt;/ruby&gt;きだと&lt;ruby&gt;言&lt;rt&gt;い&lt;/rt&gt;&lt;/ruby&gt;われています。</t>
+  </si>
+  <si>
+    <t>The kappa is a creature from Japanese folklore and is traditionally said to like cucumbers.</t>
+  </si>
+  <si>
+    <r>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>病院</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>びょういん</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>にある「小児科」の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>読</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>よ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>み</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>かた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>は、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>何</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>なん</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ですか。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「雪崩」の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>読</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>よ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>み</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>かた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>は、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>何</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>なん</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ですか。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「ひょう（雹）」とは、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>何</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>なん</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ですか。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「吹雪」の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>読</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>よ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>み</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>かた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>は、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>何</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>なん</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ですか。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「足袋」の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>読</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>よ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>み</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>かた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>は、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>何</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>なん</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ですか。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「十二単」の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>読</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>よ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>み</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>かた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>は、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>何</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>なん</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ですか。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「厳島&lt;ruby&gt;神社</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>じんじゃ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>」の「厳島」の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>読</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>よ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>み</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>かた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>は、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>何</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>なん</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ですか。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「大正&lt;ruby&gt;時代</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>じだい</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>」の「大正」の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>読</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>よ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>み</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>かた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>は、どれですか。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「聖徳太子」の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>読</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>よ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>み</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>かた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>は、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>何</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>なん</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ですか。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>戦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>戦争</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>たたかい</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>せんそう|いくさ</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;織&lt;rt&gt;お&lt;/rt&gt;&lt;/ruby&gt;り&lt;ruby&gt;姫&lt;rt&gt;ひめ&lt;/rt&gt;&lt;/ruby&gt;と&lt;ruby&gt;彦星&lt;rt&gt;ひこぼし&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;一年&lt;rt&gt;いちねん&lt;/rt&gt;&lt;/ruby&gt;に&lt;ruby&gt;一回&lt;rt&gt;いっかい&lt;/rt&gt;&lt;/ruby&gt;しか&lt;ruby&gt;会&lt;rt&gt;あ&lt;/rt&gt;&lt;/ruby&gt;えません。いつ&lt;ruby&gt;会&lt;rt&gt;あ&lt;/rt&gt;&lt;/ruby&gt;えますか。</t>
+  </si>
+  <si>
+    <t>Orihime and Hikoboshi can meet only once a year. When can they meet?</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;七夕&lt;rt&gt;たなばた&lt;/rt&gt;&lt;/ruby&gt;は7&lt;ruby&gt;月&lt;rt&gt;がつ&lt;/rt&gt;&lt;/ruby&gt;7&lt;ruby&gt;日&lt;rt&gt;なのか&lt;/rt&gt;&lt;/ruby&gt;です。&lt;ruby&gt;織&lt;rt&gt;お&lt;/rt&gt;&lt;/ruby&gt;り&lt;ruby&gt;姫&lt;rt&gt;ひめ&lt;/rt&gt;&lt;/ruby&gt;と&lt;ruby&gt;彦星&lt;rt&gt;ひこぼし&lt;/rt&gt;&lt;/ruby&gt;が&lt;ruby&gt;一年&lt;rt&gt;いちねん&lt;/rt&gt;&lt;/ruby&gt;に&lt;ruby&gt;一度&lt;rt&gt;いちど&lt;/rt&gt;&lt;/ruby&gt;&lt;ruby&gt;会&lt;rt&gt;あ&lt;/rt&gt;&lt;/ruby&gt;うという&lt;ruby&gt;伝説&lt;rt&gt;でんせつ&lt;/rt&gt;&lt;/ruby&gt;があります。</t>
+  </si>
+  <si>
+    <t>Tanabata is celebrated on July 7. According to legend, Orihime and Hikoboshi meet once a year on this day.</t>
+  </si>
+  <si>
+    <t>「NHK」とは、&lt;ruby&gt;何&lt;rt&gt;なん&lt;/rt&gt;&lt;/ruby&gt;ですか。</t>
+  </si>
+  <si>
+    <t>What is NHK?</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;日本放送協会&lt;rt&gt;にっぽんほうそうきょうかい&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Japan Broadcasting Corporation</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;日本発明協会&lt;rt&gt;にほんはつめいきょうかい&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Japan Invention Association</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;日本平和協会&lt;rt&gt;にほんへいわきょうかい&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Japan Peace Association</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;日本法律協会&lt;rt&gt;にほんほうりつきょうかい&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Japan Legal Association</t>
+  </si>
+  <si>
+    <t>NHKは「&lt;ruby&gt;日本放送協会&lt;rt&gt;にっぽんほうそうきょうかい&lt;/rt&gt;&lt;/ruby&gt;」のことです。&lt;ruby&gt;日本&lt;rt&gt;にほん&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;公共放送&lt;rt&gt;こうきょうほうそう&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;行&lt;rt&gt;おこな&lt;/rt&gt;&lt;/ruby&gt;っています。</t>
+  </si>
+  <si>
+    <t>NHK stands for the Japan Broadcasting Corporation, Japan's public broadcaster.</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;日本&lt;rt&gt;にほん&lt;/rt&gt;&lt;/ruby&gt;での&lt;ruby&gt;終戦記念日&lt;rt&gt;しゅうせんきねんび&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;何月何日&lt;rt&gt;なんがつなんにち&lt;/rt&gt;&lt;/ruby&gt;ですか。</t>
+  </si>
+  <si>
+    <t>What date is observed in Japan as the anniversary of the end of World War II?</t>
+  </si>
+  <si>
+    <t>8月15日|8/15|８月１５日|八月十五日</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;日本&lt;rt&gt;にほん&lt;/rt&gt;&lt;/ruby&gt;では、8&lt;ruby&gt;月&lt;rt&gt;がつ&lt;/rt&gt;&lt;/ruby&gt;15&lt;ruby&gt;日&lt;rt&gt;にち&lt;/rt&gt;&lt;/ruby&gt;が&lt;ruby&gt;終戦&lt;rt&gt;しゅうせん&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;日&lt;rt&gt;ひ&lt;/rt&gt;&lt;/ruby&gt;として&lt;ruby&gt;広&lt;rt&gt;ひろ&lt;/rt&gt;&lt;/ruby&gt;く&lt;ruby&gt;認識&lt;rt&gt;にんしき&lt;/rt&gt;&lt;/ruby&gt;されています。</t>
+  </si>
+  <si>
+    <t>In Japan, August 15 is widely recognized as the day marking the end of World War II.</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;日本&lt;rt&gt;にほん&lt;/rt&gt;&lt;/ruby&gt;で&lt;ruby&gt;発明&lt;rt&gt;はつめい&lt;/rt&gt;&lt;/ruby&gt;されたものは、どれですか。</t>
+  </si>
+  <si>
+    <t>Which of the following was invented in Japan?</t>
+  </si>
+  <si>
+    <t>karaoke</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;電話&lt;rt&gt;でんわ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>telephone</t>
+  </si>
+  <si>
+    <t>printer</t>
+  </si>
+  <si>
+    <t>record</t>
+  </si>
+  <si>
+    <t>カラオケは、&lt;ruby&gt;日本&lt;rt&gt;にほん&lt;/rt&gt;&lt;/ruby&gt;で&lt;ruby&gt;生&lt;rt&gt;う&lt;/rt&gt;&lt;/ruby&gt;まれた&lt;ruby&gt;娯楽&lt;rt&gt;ごらく&lt;/rt&gt;&lt;/ruby&gt;です。&lt;ruby&gt;音楽&lt;rt&gt;おんがく&lt;/rt&gt;&lt;/ruby&gt;に&lt;ruby&gt;合&lt;rt&gt;あ&lt;/rt&gt;&lt;/ruby&gt;わせて&lt;ruby&gt;歌&lt;rt&gt;うた&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;歌&lt;rt&gt;うた&lt;/rt&gt;&lt;/ruby&gt;います。</t>
+  </si>
+  <si>
+    <t>Karaoke originated in Japan. People sing along to recorded instrumental music.</t>
+  </si>
+  <si>
+    <t>「トヨタ、&lt;ruby&gt;日産&lt;rt&gt;にっさん&lt;/rt&gt;&lt;/ruby&gt;、マツダ」と&lt;ruby&gt;言&lt;rt&gt;い&lt;/rt&gt;&lt;/ruby&gt;えば、&lt;ruby&gt;何&lt;rt&gt;なん&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;会社&lt;rt&gt;かいしゃ&lt;/rt&gt;&lt;/ruby&gt;ですか。</t>
+  </si>
+  <si>
+    <t>What kind of companies are Toyota, Nissan, and Mazda?</t>
+  </si>
+  <si>
+    <t>自動車|自動車会社|車|車の会社|じどうしゃ</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;化粧品&lt;rt&gt;けしょうひん&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>cosmetics</t>
+  </si>
+  <si>
+    <t>beer</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;自動車&lt;rt&gt;じどうしゃ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>automobiles</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;家電&lt;rt&gt;かでん&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>home appliances</t>
+  </si>
+  <si>
+    <t>トヨタ、&lt;ruby&gt;日産&lt;rt&gt;にっさん&lt;/rt&gt;&lt;/ruby&gt;、マツダは、いずれも&lt;ruby&gt;自動車&lt;rt&gt;じどうしゃ&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;作&lt;rt&gt;つく&lt;/rt&gt;&lt;/ruby&gt;る&lt;ruby&gt;会社&lt;rt&gt;かいしゃ&lt;/rt&gt;&lt;/ruby&gt;です。</t>
+  </si>
+  <si>
+    <t>Toyota, Nissan, and Mazda are all automobile manufacturers.</t>
+  </si>
+  <si>
+    <t>「グリコ、&lt;ruby&gt;明治&lt;rt&gt;めいじ&lt;/rt&gt;&lt;/ruby&gt;、&lt;ruby&gt;森永&lt;rt&gt;もりなが&lt;/rt&gt;&lt;/ruby&gt;」と&lt;ruby&gt;言&lt;rt&gt;い&lt;/rt&gt;&lt;/ruby&gt;えば、&lt;ruby&gt;何&lt;rt&gt;なん&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;会社&lt;rt&gt;かいしゃ&lt;/rt&gt;&lt;/ruby&gt;ですか。</t>
+  </si>
+  <si>
+    <t>What kind of companies are Glico, Meiji, and Morinaga?</t>
+  </si>
+  <si>
+    <t>お菓子|菓子|製菓|おかし|お菓子の会社|製菓会社</t>
+  </si>
+  <si>
+    <t>airplanes</t>
+  </si>
+  <si>
+    <t>gasoline</t>
+  </si>
+  <si>
+    <t>sweets; confectionery</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;都市銀行&lt;rt&gt;としぎんこう&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>city banks</t>
+  </si>
+  <si>
+    <t>グリコ、&lt;ruby&gt;明治&lt;rt&gt;めいじ&lt;/rt&gt;&lt;/ruby&gt;、&lt;ruby&gt;森永&lt;rt&gt;もりなが&lt;/rt&gt;&lt;/ruby&gt;は、いずれもお&lt;ruby&gt;菓子&lt;rt&gt;かし&lt;/rt&gt;&lt;/ruby&gt;などの&lt;ruby&gt;食品&lt;rt&gt;しょくひん&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby&gt;作&lt;rt&gt;つく&lt;/rt&gt;&lt;/ruby&gt;る&lt;ruby&gt;会社&lt;rt&gt;かいしゃ&lt;/rt&gt;&lt;/ruby&gt;です。</t>
+  </si>
+  <si>
+    <t>Glico, Meiji, and Morinaga are companies that make sweets and other food products.</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;家電&lt;rt&gt;かでん&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;会社&lt;rt&gt;かいしゃ&lt;/rt&gt;&lt;/ruby&gt;ではないのは、どれですか。</t>
+  </si>
+  <si>
+    <t>Which of these is not a home electronics company?</t>
+  </si>
+  <si>
+    <t>Suntory</t>
+  </si>
+  <si>
+    <t>Sharp</t>
+  </si>
+  <si>
+    <t>Panasonic</t>
+  </si>
+  <si>
+    <t>ソニー、シャープ、パナソニックは&lt;ruby&gt;家電製品&lt;rt&gt;かでんせいひん&lt;/rt&gt;&lt;/ruby&gt;などを&lt;ruby&gt;作&lt;rt&gt;つく&lt;/rt&gt;&lt;/ruby&gt;る&lt;ruby&gt;会社&lt;rt&gt;かいしゃ&lt;/rt&gt;&lt;/ruby&gt;です。サントリーは、&lt;ruby&gt;飲料&lt;rt&gt;いんりょう&lt;/rt&gt;&lt;/ruby&gt;などを&lt;ruby&gt;扱&lt;rt&gt;あつか&lt;/rt&gt;&lt;/ruby&gt;う&lt;ruby&gt;会社&lt;rt&gt;かいしゃ&lt;/rt&gt;&lt;/ruby&gt;です。</t>
+  </si>
+  <si>
+    <t>Sony, Sharp, and Panasonic make home electronics and related products. Suntory is a beverage company.</t>
+  </si>
+  <si>
+    <t>「&lt;ruby&gt;夏目漱石&lt;rt&gt;なつめそうせき&lt;/rt&gt;&lt;/ruby&gt;」は、どんな&lt;ruby&gt;人&lt;rt&gt;ひと&lt;/rt&gt;&lt;/ruby&gt;ですか。</t>
+  </si>
+  <si>
+    <t>What kind of person was Natsume Soseki?</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;総理大臣&lt;rt&gt;そうりだいじん&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>prime minister</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;野球選手&lt;rt&gt;やきゅうせんしゅ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>baseball player</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;小説家&lt;rt&gt;しょうせつか&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>novelist</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;戦国武将&lt;rt&gt;せんごくぶしょう&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>warlord of the Sengoku period</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;夏目漱石&lt;rt&gt;なつめそうせき&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;明治時代&lt;rt&gt;めいじじだい&lt;/rt&gt;&lt;/ruby&gt;から&lt;ruby&gt;大正時代&lt;rt&gt;たいしょうじだい&lt;/rt&gt;&lt;/ruby&gt;にかけて&lt;ruby&gt;活躍&lt;rt&gt;かつやく&lt;/rt&gt;&lt;/ruby&gt;した&lt;ruby&gt;小説家&lt;rt&gt;しょうせつか&lt;/rt&gt;&lt;/ruby&gt;です。</t>
+  </si>
+  <si>
+    <t>Natsume Soseki was a novelist active from the Meiji period into the Taisho period.</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;相撲&lt;rt&gt;すもう&lt;/rt&gt;&lt;/ruby&gt;で&lt;ruby&gt;一番&lt;rt&gt;いちばん&lt;/rt&gt;&lt;/ruby&gt;&lt;ruby&gt;強&lt;rt&gt;つよ&lt;/rt&gt;&lt;/ruby&gt;い&lt;ruby&gt;人&lt;rt&gt;ひと&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;何&lt;rt&gt;なん&lt;/rt&gt;&lt;/ruby&gt;と&lt;ruby&gt;言&lt;rt&gt;い&lt;/rt&gt;&lt;/ruby&gt;いますか。</t>
+  </si>
+  <si>
+    <t>What is the highest rank in sumo called?</t>
+  </si>
+  <si>
+    <t>横綱|よこづな|ヨコヅナ</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;十両&lt;rt&gt;じゅうりょう&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>juryo</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;大関&lt;rt&gt;おおぜき&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>ozeki</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;横綱&lt;rt&gt;よこづな&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>yokozuna</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;関脇&lt;rt&gt;せきわけ&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>sekiwake</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;横綱&lt;rt&gt;よこづな&lt;/rt&gt;&lt;/ruby&gt;は、&lt;ruby&gt;相撲&lt;rt&gt;すもう&lt;/rt&gt;&lt;/ruby&gt;で&lt;ruby&gt;最&lt;rt&gt;もっと&lt;/rt&gt;&lt;/ruby&gt;も&lt;ruby&gt;高&lt;rt&gt;たか&lt;/rt&gt;&lt;/ruby&gt;い&lt;ruby&gt;位&lt;rt&gt;くらい&lt;/rt&gt;&lt;/ruby&gt;です。</t>
+  </si>
+  <si>
+    <t>Yokozuna is the highest rank in sumo.</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;和風月名&lt;rt&gt;わふうげつめい&lt;/rt&gt;&lt;/ruby&gt;で「12&lt;ruby&gt;月&lt;rt&gt;がつ&lt;/rt&gt;&lt;/ruby&gt;」は、&lt;ruby&gt;何&lt;rt&gt;なん&lt;/rt&gt;&lt;/ruby&gt;と&lt;ruby&gt;言&lt;rt&gt;い&lt;/rt&gt;&lt;/ruby&gt;いますか。</t>
+  </si>
+  <si>
+    <t>What is the traditional Japanese name for the twelfth month?</t>
+  </si>
+  <si>
+    <t>師走|しわす|シワス</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;弥生&lt;rt&gt;やよい&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Yayoi</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;神無月&lt;rt&gt;かんなづき&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Kannazuki</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;水無月&lt;rt&gt;みなづき&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Minazuki</t>
+  </si>
+  <si>
+    <t>&lt;ruby&gt;師走&lt;rt&gt;しわす&lt;/rt&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>Shiwasu</t>
+  </si>
+  <si>
+    <t>12&lt;ruby&gt;月&lt;rt&gt;がつ&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;和風月名&lt;rt&gt;わふうげつめい&lt;/rt&gt;&lt;/ruby&gt;は「&lt;ruby&gt;師走&lt;rt&gt;しわす&lt;/rt&gt;&lt;/ruby&gt;」です。</t>
+  </si>
+  <si>
+    <t>The traditional Japanese name for December is Shiwasu.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ひょう（雹）は、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>空</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>そら</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>から</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>降</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ふ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ってくる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>氷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>こおり</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>粒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>つぶ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「十二単」は「じゅうにひとえ」と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>読</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>よ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>みます。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>平安時代</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>へいあんじだい</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>宮中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>きゅうちゅう</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>女性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>じょせい</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>着</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>き</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>た</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>衣装</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>いしょう</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>として</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>知</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>し</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>られています。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「厳島」は「いつくしま」と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>読</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>よ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>みます。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>厳島神社</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>いつくしまじんじゃ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>は、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>広島県</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ひろしまけん</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>宮島</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>みやじま</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>にあります。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>これは、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>東京</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>とうきょう</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>浅草</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>あさくさ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>にある</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>浅草寺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>せんそうじ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>です。「浅草寺」は「せんそうじ」と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>読</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>よ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>みます。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「大正」は「たいしょう」と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>読</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>よ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>みます。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>大正時代</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>たいしょうじだい</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1912&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ねん</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>から</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1926&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ねん</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>までです。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「聖徳太子」は「しょうとくたいし」と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>読</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>よ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>みます。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>飛鳥時代</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>あすかじだい</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>人物</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>じんぶつ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>として</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>知</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>し</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>られています。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「三味線」は「しゃみせん」と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>読</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>よ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>みます。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>三本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>さんぼん</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>弦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>げん</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>がある</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>日本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>にほん</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>伝統的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>でんとうてき</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>な</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>楽器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>がっき</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <t>&lt;ruby&gt;4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>しがつようか</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>8-Apr</t>
+  </si>
+  <si>
+    <r>
+      <t>&lt;ruby&gt;7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>しちがつなのか</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>7-Jul</t>
+  </si>
+  <si>
+    <r>
+      <t>&lt;ruby&gt;11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>じゅういちがつじゅういちにち</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>11-Nov</t>
+  </si>
+  <si>
+    <r>
+      <t>&lt;ruby&gt;12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>じゅうにがつにじゅうよっか</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>24-Dec</t>
+  </si>
+  <si>
+    <r>
+      <t>&lt;ruby&gt;8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>はちがつむいか</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>6-Aug</t>
+  </si>
+  <si>
+    <r>
+      <t>&lt;ruby&gt;8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>はちがつここのか</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>9-Aug</t>
+  </si>
+  <si>
+    <r>
+      <t>&lt;ruby&gt;8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>はちがつじゅうごにち</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>15-Aug</t>
+  </si>
+  <si>
+    <r>
+      <t>&lt;ruby&gt;12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>じゅうにがつようか</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>8-Dec</t>
   </si>
 </sst>
 </file>
@@ -4590,7 +10286,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
@@ -4762,11 +10458,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -4877,7 +10576,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuestionsTable" displayName="QuestionsTable" ref="A1:AA48" headerRowDxfId="29" dataDxfId="28" totalsRowDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuestionsTable" displayName="QuestionsTable" ref="A1:AA100" headerRowDxfId="29" dataDxfId="28" totalsRowDxfId="27">
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="課番号" dataDxfId="26"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="問題番号" dataDxfId="25"/>
@@ -5068,14 +10767,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -7332,7 +13031,7 @@
       <c r="X31" s="46">
         <v>4</v>
       </c>
-      <c r="Y31" s="73" t="s">
+      <c r="Y31" s="71" t="s">
         <v>1171</v>
       </c>
       <c r="Z31" t="s">
@@ -8282,322 +13981,3494 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="49" spans="1:24">
-      <c r="A49" s="16"/>
-      <c r="B49" s="16"/>
-      <c r="X49" s="16"/>
-    </row>
-    <row r="50" spans="1:24">
-      <c r="A50" s="16"/>
-      <c r="B50" s="16"/>
-      <c r="X50" s="16"/>
-    </row>
-    <row r="51" spans="1:24">
-      <c r="A51" s="16"/>
-      <c r="B51" s="16"/>
-      <c r="X51" s="16"/>
-    </row>
-    <row r="52" spans="1:24">
-      <c r="A52" s="16"/>
-      <c r="B52" s="16"/>
-      <c r="X52" s="16"/>
-    </row>
-    <row r="53" spans="1:24">
-      <c r="A53" s="16"/>
-      <c r="B53" s="16"/>
-      <c r="X53" s="16"/>
-    </row>
-    <row r="54" spans="1:24">
-      <c r="A54" s="16"/>
-      <c r="B54" s="16"/>
-      <c r="X54" s="16"/>
-    </row>
-    <row r="55" spans="1:24">
-      <c r="A55" s="16"/>
-      <c r="B55" s="16"/>
-      <c r="X55" s="16"/>
-    </row>
-    <row r="56" spans="1:24">
-      <c r="A56" s="16"/>
-      <c r="B56" s="16"/>
-      <c r="X56" s="16"/>
-    </row>
-    <row r="57" spans="1:24">
-      <c r="A57" s="16"/>
-      <c r="B57" s="16"/>
-      <c r="X57" s="16"/>
-    </row>
-    <row r="58" spans="1:24">
-      <c r="A58" s="16"/>
-      <c r="B58" s="16"/>
-      <c r="X58" s="16"/>
-    </row>
-    <row r="59" spans="1:24">
-      <c r="A59" s="16"/>
-      <c r="B59" s="16"/>
-      <c r="X59" s="16"/>
-    </row>
-    <row r="60" spans="1:24">
-      <c r="A60" s="16"/>
-      <c r="B60" s="16"/>
-      <c r="X60" s="16"/>
-    </row>
-    <row r="61" spans="1:24">
-      <c r="A61" s="16"/>
-      <c r="B61" s="16"/>
-      <c r="X61" s="16"/>
-    </row>
-    <row r="62" spans="1:24">
-      <c r="A62" s="16"/>
-      <c r="B62" s="16"/>
-      <c r="X62" s="16"/>
-    </row>
-    <row r="63" spans="1:24">
-      <c r="A63" s="16"/>
-      <c r="B63" s="16"/>
-      <c r="X63" s="16"/>
-    </row>
-    <row r="64" spans="1:24">
-      <c r="A64" s="16"/>
-      <c r="B64" s="16"/>
-      <c r="X64" s="16"/>
-    </row>
-    <row r="65" spans="1:24">
-      <c r="A65" s="16"/>
-      <c r="B65" s="16"/>
-      <c r="X65" s="16"/>
-    </row>
-    <row r="66" spans="1:24">
-      <c r="A66" s="16"/>
-      <c r="B66" s="16"/>
-      <c r="X66" s="16"/>
-    </row>
-    <row r="67" spans="1:24">
-      <c r="A67" s="16"/>
-      <c r="B67" s="16"/>
-      <c r="X67" s="16"/>
-    </row>
-    <row r="68" spans="1:24">
-      <c r="A68" s="16"/>
-      <c r="B68" s="16"/>
-      <c r="X68" s="16"/>
-    </row>
-    <row r="69" spans="1:24">
-      <c r="A69" s="16"/>
-      <c r="B69" s="16"/>
-      <c r="X69" s="16"/>
-    </row>
-    <row r="70" spans="1:24">
-      <c r="A70" s="16"/>
-      <c r="B70" s="16"/>
-      <c r="X70" s="16"/>
-    </row>
-    <row r="71" spans="1:24">
-      <c r="A71" s="16"/>
-      <c r="B71" s="16"/>
-      <c r="X71" s="16"/>
-    </row>
-    <row r="72" spans="1:24">
-      <c r="A72" s="16"/>
-      <c r="B72" s="16"/>
-      <c r="X72" s="16"/>
-    </row>
-    <row r="73" spans="1:24">
-      <c r="A73" s="16"/>
-      <c r="B73" s="16"/>
-      <c r="X73" s="16"/>
-    </row>
-    <row r="74" spans="1:24">
-      <c r="A74" s="16"/>
-      <c r="B74" s="16"/>
-      <c r="X74" s="16"/>
-    </row>
-    <row r="75" spans="1:24">
-      <c r="A75" s="16"/>
-      <c r="B75" s="16"/>
-      <c r="X75" s="16"/>
-    </row>
-    <row r="76" spans="1:24">
-      <c r="A76" s="16"/>
-      <c r="B76" s="16"/>
-      <c r="X76" s="16"/>
-    </row>
-    <row r="77" spans="1:24">
-      <c r="A77" s="16"/>
-      <c r="B77" s="16"/>
-      <c r="X77" s="16"/>
-    </row>
-    <row r="78" spans="1:24">
-      <c r="A78" s="16"/>
-      <c r="B78" s="16"/>
-      <c r="X78" s="16"/>
-    </row>
-    <row r="79" spans="1:24">
-      <c r="A79" s="16"/>
-      <c r="B79" s="16"/>
-      <c r="X79" s="16"/>
-    </row>
-    <row r="80" spans="1:24">
-      <c r="A80" s="16"/>
-      <c r="B80" s="16"/>
-      <c r="X80" s="16"/>
-    </row>
-    <row r="81" spans="1:24">
-      <c r="A81" s="16"/>
-      <c r="B81" s="16"/>
-      <c r="X81" s="16"/>
-    </row>
-    <row r="82" spans="1:24">
-      <c r="A82" s="16"/>
-      <c r="B82" s="16"/>
-      <c r="X82" s="16"/>
-    </row>
-    <row r="83" spans="1:24">
-      <c r="A83" s="16"/>
-      <c r="B83" s="16"/>
-      <c r="X83" s="16"/>
-    </row>
-    <row r="84" spans="1:24">
-      <c r="A84" s="16"/>
-      <c r="B84" s="16"/>
-      <c r="X84" s="16"/>
-    </row>
-    <row r="85" spans="1:24">
-      <c r="A85" s="16"/>
-      <c r="B85" s="16"/>
-      <c r="X85" s="16"/>
-    </row>
-    <row r="86" spans="1:24">
-      <c r="A86" s="16"/>
-      <c r="B86" s="16"/>
-      <c r="X86" s="16"/>
-    </row>
-    <row r="87" spans="1:24">
-      <c r="A87" s="16"/>
-      <c r="B87" s="16"/>
-      <c r="X87" s="16"/>
-    </row>
-    <row r="88" spans="1:24">
-      <c r="A88" s="16"/>
-      <c r="B88" s="16"/>
-      <c r="X88" s="16"/>
-    </row>
-    <row r="89" spans="1:24">
-      <c r="A89" s="16"/>
-      <c r="B89" s="16"/>
-      <c r="X89" s="16"/>
-    </row>
-    <row r="90" spans="1:24">
-      <c r="A90" s="16"/>
-      <c r="B90" s="16"/>
-      <c r="X90" s="16"/>
-    </row>
-    <row r="91" spans="1:24">
-      <c r="A91" s="16"/>
-      <c r="B91" s="16"/>
-      <c r="X91" s="16"/>
-    </row>
-    <row r="92" spans="1:24">
-      <c r="A92" s="16"/>
-      <c r="B92" s="16"/>
-      <c r="X92" s="16"/>
-    </row>
-    <row r="93" spans="1:24">
-      <c r="A93" s="16"/>
-      <c r="B93" s="16"/>
-      <c r="X93" s="16"/>
-    </row>
-    <row r="94" spans="1:24">
-      <c r="A94" s="16"/>
-      <c r="B94" s="16"/>
-      <c r="X94" s="16"/>
-    </row>
-    <row r="95" spans="1:24">
-      <c r="A95" s="16"/>
-      <c r="B95" s="16"/>
-      <c r="X95" s="16"/>
-    </row>
-    <row r="96" spans="1:24">
-      <c r="A96" s="16"/>
-      <c r="B96" s="16"/>
-      <c r="X96" s="16"/>
-    </row>
-    <row r="97" spans="1:24">
-      <c r="A97" s="16"/>
-      <c r="B97" s="16"/>
-      <c r="X97" s="16"/>
-    </row>
-    <row r="98" spans="1:24">
-      <c r="A98" s="16"/>
-      <c r="B98" s="16"/>
-      <c r="X98" s="16"/>
-    </row>
-    <row r="99" spans="1:24">
-      <c r="A99" s="16"/>
-      <c r="B99" s="16"/>
-      <c r="X99" s="16"/>
-    </row>
-    <row r="100" spans="1:24">
-      <c r="A100" s="16"/>
-      <c r="B100" s="16"/>
-      <c r="X100" s="16"/>
-    </row>
-    <row r="101" spans="1:24">
+    <row r="49" spans="1:27">
+      <c r="A49" s="16">
+        <v>7</v>
+      </c>
+      <c r="B49" s="16">
+        <v>48</v>
+      </c>
+      <c r="C49" s="74" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D49" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" s="74" t="s">
+        <v>1315</v>
+      </c>
+      <c r="F49" s="74" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G49" s="74"/>
+      <c r="H49" s="74"/>
+      <c r="I49" s="74"/>
+      <c r="J49" s="74"/>
+      <c r="K49" s="74"/>
+      <c r="L49" s="74"/>
+      <c r="M49" s="74"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="74"/>
+      <c r="P49" s="74" t="s">
+        <v>1191</v>
+      </c>
+      <c r="Q49" s="74" t="s">
+        <v>1317</v>
+      </c>
+      <c r="R49" s="74" t="s">
+        <v>1192</v>
+      </c>
+      <c r="S49" s="74" t="s">
+        <v>1318</v>
+      </c>
+      <c r="T49" s="74" t="s">
+        <v>1190</v>
+      </c>
+      <c r="U49" s="74" t="s">
+        <v>1319</v>
+      </c>
+      <c r="V49" s="74" t="s">
+        <v>1193</v>
+      </c>
+      <c r="W49" s="74" t="s">
+        <v>1320</v>
+      </c>
+      <c r="X49" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y49" s="74" t="s">
+        <v>1321</v>
+      </c>
+      <c r="Z49" s="74" t="s">
+        <v>1322</v>
+      </c>
+      <c r="AA49" s="74"/>
+    </row>
+    <row r="50" spans="1:27">
+      <c r="A50" s="16">
+        <v>7</v>
+      </c>
+      <c r="B50" s="16">
+        <v>49</v>
+      </c>
+      <c r="C50" s="74" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D50" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E50" s="74" t="s">
+        <v>1323</v>
+      </c>
+      <c r="F50" s="74" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G50" s="74" t="s">
+        <v>1325</v>
+      </c>
+      <c r="H50" s="74" t="s">
+        <v>1326</v>
+      </c>
+      <c r="I50" s="74"/>
+      <c r="J50" s="74"/>
+      <c r="K50" s="74"/>
+      <c r="L50" s="74"/>
+      <c r="M50" s="74"/>
+      <c r="N50" s="74"/>
+      <c r="O50" s="74"/>
+      <c r="P50" s="74" t="s">
+        <v>1195</v>
+      </c>
+      <c r="Q50" s="74" t="s">
+        <v>1327</v>
+      </c>
+      <c r="R50" s="74" t="s">
+        <v>1194</v>
+      </c>
+      <c r="S50" s="74" t="s">
+        <v>1326</v>
+      </c>
+      <c r="T50" s="74" t="s">
+        <v>1196</v>
+      </c>
+      <c r="U50" s="74" t="s">
+        <v>1328</v>
+      </c>
+      <c r="V50" s="74" t="s">
+        <v>1197</v>
+      </c>
+      <c r="W50" s="74" t="s">
+        <v>1329</v>
+      </c>
+      <c r="X50" s="16">
+        <v>2</v>
+      </c>
+      <c r="Y50" s="74" t="s">
+        <v>1330</v>
+      </c>
+      <c r="Z50" s="74" t="s">
+        <v>1331</v>
+      </c>
+      <c r="AA50" s="74"/>
+    </row>
+    <row r="51" spans="1:27">
+      <c r="A51" s="16">
+        <v>7</v>
+      </c>
+      <c r="B51" s="16">
+        <v>50</v>
+      </c>
+      <c r="C51" s="74" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D51" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" s="74" t="s">
+        <v>1749</v>
+      </c>
+      <c r="F51" s="74" t="s">
+        <v>1332</v>
+      </c>
+      <c r="G51" s="74"/>
+      <c r="H51" s="74"/>
+      <c r="I51" s="74"/>
+      <c r="J51" s="74"/>
+      <c r="K51" s="74"/>
+      <c r="L51" s="74"/>
+      <c r="M51" s="74"/>
+      <c r="N51" s="74"/>
+      <c r="O51" s="74" t="s">
+        <v>1333</v>
+      </c>
+      <c r="P51" s="74" t="s">
+        <v>1199</v>
+      </c>
+      <c r="Q51" s="74" t="s">
+        <v>1334</v>
+      </c>
+      <c r="R51" s="74" t="s">
+        <v>1200</v>
+      </c>
+      <c r="S51" s="74" t="s">
+        <v>1335</v>
+      </c>
+      <c r="T51" s="74" t="s">
+        <v>1201</v>
+      </c>
+      <c r="U51" s="74" t="s">
+        <v>1336</v>
+      </c>
+      <c r="V51" s="74" t="s">
+        <v>1202</v>
+      </c>
+      <c r="W51" s="74" t="s">
+        <v>1337</v>
+      </c>
+      <c r="X51" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y51" s="74" t="s">
+        <v>1338</v>
+      </c>
+      <c r="Z51" s="74" t="s">
+        <v>1339</v>
+      </c>
+      <c r="AA51" s="74"/>
+    </row>
+    <row r="52" spans="1:27">
+      <c r="A52" s="16">
+        <v>7</v>
+      </c>
+      <c r="B52" s="16">
+        <v>51</v>
+      </c>
+      <c r="C52" s="74" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D52" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" s="75" t="s">
+        <v>1750</v>
+      </c>
+      <c r="F52" s="74" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G52" s="74"/>
+      <c r="H52" s="74"/>
+      <c r="I52" s="74"/>
+      <c r="J52" s="74"/>
+      <c r="K52" s="74"/>
+      <c r="L52" s="74"/>
+      <c r="M52" s="74"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="74" t="s">
+        <v>1341</v>
+      </c>
+      <c r="P52" s="74" t="s">
+        <v>1204</v>
+      </c>
+      <c r="Q52" s="74" t="s">
+        <v>1342</v>
+      </c>
+      <c r="R52" s="74" t="s">
+        <v>1205</v>
+      </c>
+      <c r="S52" s="74" t="s">
+        <v>1343</v>
+      </c>
+      <c r="T52" s="74" t="s">
+        <v>1203</v>
+      </c>
+      <c r="U52" s="74" t="s">
+        <v>1344</v>
+      </c>
+      <c r="V52" s="74" t="s">
+        <v>286</v>
+      </c>
+      <c r="W52" s="74" t="s">
+        <v>1345</v>
+      </c>
+      <c r="X52" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y52" s="74" t="s">
+        <v>1346</v>
+      </c>
+      <c r="Z52" s="74" t="s">
+        <v>1347</v>
+      </c>
+      <c r="AA52" s="74"/>
+    </row>
+    <row r="53" spans="1:27">
+      <c r="A53" s="16">
+        <v>7</v>
+      </c>
+      <c r="B53" s="16">
+        <v>52</v>
+      </c>
+      <c r="C53" s="74" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D53" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" s="75" t="s">
+        <v>1751</v>
+      </c>
+      <c r="F53" s="74" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G53" s="74"/>
+      <c r="H53" s="74"/>
+      <c r="I53" s="74"/>
+      <c r="J53" s="74"/>
+      <c r="K53" s="74"/>
+      <c r="L53" s="74"/>
+      <c r="M53" s="74"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="74"/>
+      <c r="P53" s="74" t="s">
+        <v>1349</v>
+      </c>
+      <c r="Q53" s="74" t="s">
+        <v>1350</v>
+      </c>
+      <c r="R53" s="74" t="s">
+        <v>1351</v>
+      </c>
+      <c r="S53" s="74" t="s">
+        <v>1352</v>
+      </c>
+      <c r="T53" s="74" t="s">
+        <v>1353</v>
+      </c>
+      <c r="U53" s="74" t="s">
+        <v>1354</v>
+      </c>
+      <c r="V53" s="74" t="s">
+        <v>1355</v>
+      </c>
+      <c r="W53" s="74" t="s">
+        <v>1356</v>
+      </c>
+      <c r="X53" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y53" s="75" t="s">
+        <v>1856</v>
+      </c>
+      <c r="Z53" s="74" t="s">
+        <v>1357</v>
+      </c>
+      <c r="AA53" s="74"/>
+    </row>
+    <row r="54" spans="1:27">
+      <c r="A54" s="16">
+        <v>7</v>
+      </c>
+      <c r="B54" s="16">
+        <v>53</v>
+      </c>
+      <c r="C54" s="74" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D54" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" s="75" t="s">
+        <v>1752</v>
+      </c>
+      <c r="F54" s="74" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G54" s="74"/>
+      <c r="H54" s="74"/>
+      <c r="I54" s="74"/>
+      <c r="J54" s="74"/>
+      <c r="K54" s="74"/>
+      <c r="L54" s="74"/>
+      <c r="M54" s="74"/>
+      <c r="N54" s="74"/>
+      <c r="O54" s="74" t="s">
+        <v>1359</v>
+      </c>
+      <c r="P54" s="74" t="s">
+        <v>1208</v>
+      </c>
+      <c r="Q54" s="74" t="s">
+        <v>1360</v>
+      </c>
+      <c r="R54" s="74" t="s">
+        <v>1209</v>
+      </c>
+      <c r="S54" s="74" t="s">
+        <v>1361</v>
+      </c>
+      <c r="T54" s="74" t="s">
+        <v>1210</v>
+      </c>
+      <c r="U54" s="74" t="s">
+        <v>1362</v>
+      </c>
+      <c r="V54" s="74" t="s">
+        <v>1211</v>
+      </c>
+      <c r="W54" s="74" t="s">
+        <v>1363</v>
+      </c>
+      <c r="X54" s="16">
+        <v>4</v>
+      </c>
+      <c r="Y54" s="74" t="s">
+        <v>1364</v>
+      </c>
+      <c r="Z54" s="74" t="s">
+        <v>1365</v>
+      </c>
+      <c r="AA54" s="74"/>
+    </row>
+    <row r="55" spans="1:27">
+      <c r="A55" s="16">
+        <v>7</v>
+      </c>
+      <c r="B55" s="16">
+        <v>54</v>
+      </c>
+      <c r="C55" s="74" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D55" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E55" s="74" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F55" s="74" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G55" s="74"/>
+      <c r="H55" s="74"/>
+      <c r="I55" s="74"/>
+      <c r="J55" s="74"/>
+      <c r="K55" s="74"/>
+      <c r="L55" s="74"/>
+      <c r="M55" s="74"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="74"/>
+      <c r="P55" s="74" t="s">
+        <v>1368</v>
+      </c>
+      <c r="Q55" s="74" t="s">
+        <v>1369</v>
+      </c>
+      <c r="R55" s="74" t="s">
+        <v>1370</v>
+      </c>
+      <c r="S55" s="74" t="s">
+        <v>1371</v>
+      </c>
+      <c r="T55" s="74" t="s">
+        <v>1372</v>
+      </c>
+      <c r="U55" s="74" t="s">
+        <v>1373</v>
+      </c>
+      <c r="V55" s="74" t="s">
+        <v>1374</v>
+      </c>
+      <c r="W55" s="74" t="s">
+        <v>1375</v>
+      </c>
+      <c r="X55" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y55" s="74" t="s">
+        <v>1376</v>
+      </c>
+      <c r="Z55" s="74" t="s">
+        <v>1377</v>
+      </c>
+      <c r="AA55" s="74"/>
+    </row>
+    <row r="56" spans="1:27">
+      <c r="A56" s="16">
+        <v>7</v>
+      </c>
+      <c r="B56" s="16">
+        <v>55</v>
+      </c>
+      <c r="C56" s="74" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D56" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" s="74" t="s">
+        <v>1378</v>
+      </c>
+      <c r="F56" s="74" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G56" s="74"/>
+      <c r="H56" s="74"/>
+      <c r="I56" s="74"/>
+      <c r="J56" s="74"/>
+      <c r="K56" s="74"/>
+      <c r="L56" s="74"/>
+      <c r="M56" s="74"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="74" t="s">
+        <v>1380</v>
+      </c>
+      <c r="P56" s="74" t="s">
+        <v>1381</v>
+      </c>
+      <c r="Q56" s="74" t="s">
+        <v>1382</v>
+      </c>
+      <c r="R56" s="74" t="s">
+        <v>1383</v>
+      </c>
+      <c r="S56" s="74" t="s">
+        <v>1384</v>
+      </c>
+      <c r="T56" s="74" t="s">
+        <v>1385</v>
+      </c>
+      <c r="U56" s="74" t="s">
+        <v>1386</v>
+      </c>
+      <c r="V56" s="74" t="s">
+        <v>1387</v>
+      </c>
+      <c r="W56" s="74" t="s">
+        <v>1388</v>
+      </c>
+      <c r="X56" s="16">
+        <v>1</v>
+      </c>
+      <c r="Y56" s="74" t="s">
+        <v>1389</v>
+      </c>
+      <c r="Z56" s="74" t="s">
+        <v>1390</v>
+      </c>
+      <c r="AA56" s="74"/>
+    </row>
+    <row r="57" spans="1:27">
+      <c r="A57" s="16">
+        <v>7</v>
+      </c>
+      <c r="B57" s="16">
+        <v>56</v>
+      </c>
+      <c r="C57" s="74" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D57" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E57" s="74" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F57" s="74" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G57" s="74"/>
+      <c r="H57" s="74"/>
+      <c r="I57" s="74"/>
+      <c r="J57" s="74"/>
+      <c r="K57" s="74"/>
+      <c r="L57" s="74"/>
+      <c r="M57" s="74"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="74"/>
+      <c r="P57" s="74" t="s">
+        <v>1393</v>
+      </c>
+      <c r="Q57" s="74" t="s">
+        <v>1394</v>
+      </c>
+      <c r="R57" s="74" t="s">
+        <v>1215</v>
+      </c>
+      <c r="S57" s="74" t="s">
+        <v>1395</v>
+      </c>
+      <c r="T57" s="74" t="s">
+        <v>1216</v>
+      </c>
+      <c r="U57" s="74" t="s">
+        <v>1396</v>
+      </c>
+      <c r="V57" s="74" t="s">
+        <v>1397</v>
+      </c>
+      <c r="W57" s="74" t="s">
+        <v>1398</v>
+      </c>
+      <c r="X57" s="16">
+        <v>4</v>
+      </c>
+      <c r="Y57" s="74" t="s">
+        <v>1399</v>
+      </c>
+      <c r="Z57" s="74" t="s">
+        <v>1400</v>
+      </c>
+      <c r="AA57" s="74"/>
+    </row>
+    <row r="58" spans="1:27">
+      <c r="A58" s="16">
+        <v>8</v>
+      </c>
+      <c r="B58" s="16">
+        <v>57</v>
+      </c>
+      <c r="C58" s="74" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D58" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="E58" s="74" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F58" s="74" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G58" s="74" t="s">
+        <v>1403</v>
+      </c>
+      <c r="H58" s="74" t="s">
+        <v>1404</v>
+      </c>
+      <c r="I58" s="74" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J58" s="74" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K58" s="74" t="s">
+        <v>1407</v>
+      </c>
+      <c r="L58" s="74" t="s">
+        <v>1408</v>
+      </c>
+      <c r="M58" s="74" t="s">
+        <v>1409</v>
+      </c>
+      <c r="N58" s="74" t="s">
+        <v>1410</v>
+      </c>
+      <c r="O58" s="74"/>
+      <c r="P58" s="74" t="s">
+        <v>1411</v>
+      </c>
+      <c r="Q58" s="74" t="s">
+        <v>1404</v>
+      </c>
+      <c r="R58" s="74" t="s">
+        <v>1412</v>
+      </c>
+      <c r="S58" s="74" t="s">
+        <v>1406</v>
+      </c>
+      <c r="T58" s="74" t="s">
+        <v>1413</v>
+      </c>
+      <c r="U58" s="74" t="s">
+        <v>1408</v>
+      </c>
+      <c r="V58" s="74" t="s">
+        <v>1414</v>
+      </c>
+      <c r="W58" s="74" t="s">
+        <v>1410</v>
+      </c>
+      <c r="X58" s="16">
+        <v>1</v>
+      </c>
+      <c r="Y58" s="74" t="s">
+        <v>1415</v>
+      </c>
+      <c r="Z58" s="74" t="s">
+        <v>1416</v>
+      </c>
+      <c r="AA58" s="74"/>
+    </row>
+    <row r="59" spans="1:27">
+      <c r="A59" s="16">
+        <v>8</v>
+      </c>
+      <c r="B59" s="16">
+        <v>58</v>
+      </c>
+      <c r="C59" s="74" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D59" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" s="75" t="s">
+        <v>1753</v>
+      </c>
+      <c r="F59" s="74" t="s">
+        <v>1417</v>
+      </c>
+      <c r="G59" s="74"/>
+      <c r="H59" s="74"/>
+      <c r="I59" s="74"/>
+      <c r="J59" s="74"/>
+      <c r="K59" s="74"/>
+      <c r="L59" s="74"/>
+      <c r="M59" s="74"/>
+      <c r="N59" s="74"/>
+      <c r="O59" s="74" t="s">
+        <v>1418</v>
+      </c>
+      <c r="P59" s="74" t="s">
+        <v>1219</v>
+      </c>
+      <c r="Q59" s="74" t="s">
+        <v>1419</v>
+      </c>
+      <c r="R59" s="74" t="s">
+        <v>1220</v>
+      </c>
+      <c r="S59" s="74" t="s">
+        <v>1420</v>
+      </c>
+      <c r="T59" s="74" t="s">
+        <v>1221</v>
+      </c>
+      <c r="U59" s="74" t="s">
+        <v>1421</v>
+      </c>
+      <c r="V59" s="74" t="s">
+        <v>1222</v>
+      </c>
+      <c r="W59" s="74" t="s">
+        <v>1422</v>
+      </c>
+      <c r="X59" s="16">
+        <v>4</v>
+      </c>
+      <c r="Y59" s="74" t="s">
+        <v>1423</v>
+      </c>
+      <c r="Z59" s="74" t="s">
+        <v>1424</v>
+      </c>
+      <c r="AA59" s="74"/>
+    </row>
+    <row r="60" spans="1:27">
+      <c r="A60" s="16">
+        <v>8</v>
+      </c>
+      <c r="B60" s="16">
+        <v>59</v>
+      </c>
+      <c r="C60" s="74" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D60" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" s="74" t="s">
+        <v>1425</v>
+      </c>
+      <c r="F60" s="74" t="s">
+        <v>1426</v>
+      </c>
+      <c r="G60" s="74"/>
+      <c r="H60" s="74"/>
+      <c r="I60" s="74"/>
+      <c r="J60" s="74"/>
+      <c r="K60" s="74"/>
+      <c r="L60" s="74"/>
+      <c r="M60" s="74"/>
+      <c r="N60" s="74"/>
+      <c r="O60" s="75" t="s">
+        <v>1758</v>
+      </c>
+      <c r="P60" s="74" t="s">
+        <v>1427</v>
+      </c>
+      <c r="Q60" s="74" t="s">
+        <v>1428</v>
+      </c>
+      <c r="R60" s="74" t="s">
+        <v>1429</v>
+      </c>
+      <c r="S60" s="74" t="s">
+        <v>1430</v>
+      </c>
+      <c r="T60" s="74" t="s">
+        <v>1431</v>
+      </c>
+      <c r="U60" s="74" t="s">
+        <v>1432</v>
+      </c>
+      <c r="V60" s="74" t="s">
+        <v>1433</v>
+      </c>
+      <c r="W60" s="74" t="s">
+        <v>1434</v>
+      </c>
+      <c r="X60" s="16">
+        <v>1</v>
+      </c>
+      <c r="Y60" s="74" t="s">
+        <v>1435</v>
+      </c>
+      <c r="Z60" s="74" t="s">
+        <v>1436</v>
+      </c>
+      <c r="AA60" s="74"/>
+    </row>
+    <row r="61" spans="1:27">
+      <c r="A61" s="16">
+        <v>8</v>
+      </c>
+      <c r="B61" s="16">
+        <v>60</v>
+      </c>
+      <c r="C61" s="74" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D61" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="74" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F61" s="74" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G61" s="74" t="s">
+        <v>1439</v>
+      </c>
+      <c r="H61" s="74" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I61" s="74"/>
+      <c r="J61" s="74"/>
+      <c r="K61" s="74"/>
+      <c r="L61" s="74"/>
+      <c r="M61" s="74"/>
+      <c r="N61" s="74"/>
+      <c r="O61" s="74" t="s">
+        <v>1440</v>
+      </c>
+      <c r="P61" s="74" t="s">
+        <v>1441</v>
+      </c>
+      <c r="Q61" s="74" t="s">
+        <v>1442</v>
+      </c>
+      <c r="R61" s="74" t="s">
+        <v>1216</v>
+      </c>
+      <c r="S61" s="74" t="s">
+        <v>1396</v>
+      </c>
+      <c r="T61" s="74" t="s">
+        <v>1224</v>
+      </c>
+      <c r="U61" s="74" t="s">
+        <v>1443</v>
+      </c>
+      <c r="V61" s="74" t="s">
+        <v>1444</v>
+      </c>
+      <c r="W61" s="74" t="s">
+        <v>1445</v>
+      </c>
+      <c r="X61" s="16">
+        <v>2</v>
+      </c>
+      <c r="Y61" s="74" t="s">
+        <v>1446</v>
+      </c>
+      <c r="Z61" s="74" t="s">
+        <v>1447</v>
+      </c>
+      <c r="AA61" s="74"/>
+    </row>
+    <row r="62" spans="1:27">
+      <c r="A62" s="16">
+        <v>8</v>
+      </c>
+      <c r="B62" s="16">
+        <v>61</v>
+      </c>
+      <c r="C62" s="74" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D62" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" s="74" t="s">
+        <v>84</v>
+      </c>
+      <c r="F62" s="74" t="s">
+        <v>85</v>
+      </c>
+      <c r="G62" s="74" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H62" s="74" t="s">
+        <v>1449</v>
+      </c>
+      <c r="I62" s="74"/>
+      <c r="J62" s="74"/>
+      <c r="K62" s="74"/>
+      <c r="L62" s="74"/>
+      <c r="M62" s="74"/>
+      <c r="N62" s="74"/>
+      <c r="O62" s="74" t="s">
+        <v>1450</v>
+      </c>
+      <c r="P62" s="74" t="s">
+        <v>1451</v>
+      </c>
+      <c r="Q62" s="74" t="s">
+        <v>1452</v>
+      </c>
+      <c r="R62" s="74" t="s">
+        <v>1453</v>
+      </c>
+      <c r="S62" s="74" t="s">
+        <v>1449</v>
+      </c>
+      <c r="T62" s="74" t="s">
+        <v>1454</v>
+      </c>
+      <c r="U62" s="74" t="s">
+        <v>1455</v>
+      </c>
+      <c r="V62" s="74" t="s">
+        <v>1215</v>
+      </c>
+      <c r="W62" s="74" t="s">
+        <v>1395</v>
+      </c>
+      <c r="X62" s="16">
+        <v>2</v>
+      </c>
+      <c r="Y62" s="74" t="s">
+        <v>1456</v>
+      </c>
+      <c r="Z62" s="74" t="s">
+        <v>1457</v>
+      </c>
+      <c r="AA62" s="74"/>
+    </row>
+    <row r="63" spans="1:27">
+      <c r="A63" s="16">
+        <v>8</v>
+      </c>
+      <c r="B63" s="16">
+        <v>62</v>
+      </c>
+      <c r="C63" s="74" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D63" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" s="75" t="s">
+        <v>1754</v>
+      </c>
+      <c r="F63" s="74" t="s">
+        <v>1458</v>
+      </c>
+      <c r="G63" s="74"/>
+      <c r="H63" s="74"/>
+      <c r="I63" s="74"/>
+      <c r="J63" s="74"/>
+      <c r="K63" s="74"/>
+      <c r="L63" s="74"/>
+      <c r="M63" s="74"/>
+      <c r="N63" s="74"/>
+      <c r="O63" s="74" t="s">
+        <v>1459</v>
+      </c>
+      <c r="P63" s="74" t="s">
+        <v>1228</v>
+      </c>
+      <c r="Q63" s="74" t="s">
+        <v>1460</v>
+      </c>
+      <c r="R63" s="74" t="s">
+        <v>1229</v>
+      </c>
+      <c r="S63" s="74" t="s">
+        <v>1461</v>
+      </c>
+      <c r="T63" s="74" t="s">
+        <v>1230</v>
+      </c>
+      <c r="U63" s="74" t="s">
+        <v>1462</v>
+      </c>
+      <c r="V63" s="74" t="s">
+        <v>1231</v>
+      </c>
+      <c r="W63" s="74" t="s">
+        <v>1463</v>
+      </c>
+      <c r="X63" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y63" s="75" t="s">
+        <v>1857</v>
+      </c>
+      <c r="Z63" s="74" t="s">
+        <v>1464</v>
+      </c>
+      <c r="AA63" s="74"/>
+    </row>
+    <row r="64" spans="1:27">
+      <c r="A64" s="16">
+        <v>8</v>
+      </c>
+      <c r="B64" s="16">
+        <v>63</v>
+      </c>
+      <c r="C64" s="74" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D64" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E64" s="74" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F64" s="74" t="s">
+        <v>1465</v>
+      </c>
+      <c r="G64" s="74"/>
+      <c r="H64" s="74"/>
+      <c r="I64" s="74"/>
+      <c r="J64" s="74"/>
+      <c r="K64" s="74"/>
+      <c r="L64" s="74"/>
+      <c r="M64" s="74"/>
+      <c r="N64" s="74"/>
+      <c r="O64" s="74"/>
+      <c r="P64" s="74" t="s">
+        <v>1466</v>
+      </c>
+      <c r="Q64" s="74" t="s">
+        <v>1467</v>
+      </c>
+      <c r="R64" s="74" t="s">
+        <v>1468</v>
+      </c>
+      <c r="S64" s="74" t="s">
+        <v>1469</v>
+      </c>
+      <c r="T64" s="74" t="s">
+        <v>1470</v>
+      </c>
+      <c r="U64" s="74" t="s">
+        <v>1471</v>
+      </c>
+      <c r="V64" s="74" t="s">
+        <v>1472</v>
+      </c>
+      <c r="W64" s="74" t="s">
+        <v>1473</v>
+      </c>
+      <c r="X64" s="16">
+        <v>2</v>
+      </c>
+      <c r="Y64" s="74" t="s">
+        <v>1474</v>
+      </c>
+      <c r="Z64" s="74" t="s">
+        <v>1475</v>
+      </c>
+      <c r="AA64" s="74"/>
+    </row>
+    <row r="65" spans="1:27">
+      <c r="A65" s="16">
+        <v>8</v>
+      </c>
+      <c r="B65" s="16">
+        <v>64</v>
+      </c>
+      <c r="C65" s="74" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D65" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E65" s="74" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F65" s="74" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G65" s="74"/>
+      <c r="H65" s="74"/>
+      <c r="I65" s="74"/>
+      <c r="J65" s="74"/>
+      <c r="K65" s="74"/>
+      <c r="L65" s="74"/>
+      <c r="M65" s="74"/>
+      <c r="N65" s="74"/>
+      <c r="O65" s="74"/>
+      <c r="P65" s="74" t="s">
+        <v>1478</v>
+      </c>
+      <c r="Q65" s="74" t="s">
+        <v>1479</v>
+      </c>
+      <c r="R65" s="74" t="s">
+        <v>1480</v>
+      </c>
+      <c r="S65" s="74" t="s">
+        <v>1481</v>
+      </c>
+      <c r="T65" s="74" t="s">
+        <v>1482</v>
+      </c>
+      <c r="U65" s="74" t="s">
+        <v>1483</v>
+      </c>
+      <c r="V65" s="74" t="s">
+        <v>1484</v>
+      </c>
+      <c r="W65" s="74" t="s">
+        <v>1485</v>
+      </c>
+      <c r="X65" s="16">
+        <v>2</v>
+      </c>
+      <c r="Y65" s="74" t="s">
+        <v>1486</v>
+      </c>
+      <c r="Z65" s="74" t="s">
+        <v>1487</v>
+      </c>
+      <c r="AA65" s="74"/>
+    </row>
+    <row r="66" spans="1:27">
+      <c r="A66" s="16">
+        <v>8</v>
+      </c>
+      <c r="B66" s="16">
+        <v>65</v>
+      </c>
+      <c r="C66" s="74" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D66" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E66" s="74" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F66" s="74" t="s">
+        <v>1489</v>
+      </c>
+      <c r="G66" s="74"/>
+      <c r="H66" s="74"/>
+      <c r="I66" s="74"/>
+      <c r="J66" s="74"/>
+      <c r="K66" s="74"/>
+      <c r="L66" s="74"/>
+      <c r="M66" s="74"/>
+      <c r="N66" s="74"/>
+      <c r="O66" s="74"/>
+      <c r="P66" s="74" t="s">
+        <v>1490</v>
+      </c>
+      <c r="Q66" s="74" t="s">
+        <v>1491</v>
+      </c>
+      <c r="R66" s="74" t="s">
+        <v>1492</v>
+      </c>
+      <c r="S66" s="74" t="s">
+        <v>1493</v>
+      </c>
+      <c r="T66" s="74" t="s">
+        <v>1494</v>
+      </c>
+      <c r="U66" s="74" t="s">
+        <v>1495</v>
+      </c>
+      <c r="V66" s="74" t="s">
+        <v>1058</v>
+      </c>
+      <c r="W66" s="74" t="s">
+        <v>1059</v>
+      </c>
+      <c r="X66" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y66" s="74" t="s">
+        <v>1496</v>
+      </c>
+      <c r="Z66" s="74" t="s">
+        <v>1497</v>
+      </c>
+      <c r="AA66" s="74"/>
+    </row>
+    <row r="67" spans="1:27">
+      <c r="A67" s="16">
+        <v>9</v>
+      </c>
+      <c r="B67" s="16">
+        <v>66</v>
+      </c>
+      <c r="C67" s="74" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D67" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="75" t="s">
+        <v>1755</v>
+      </c>
+      <c r="F67" s="74" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G67" s="74"/>
+      <c r="H67" s="74"/>
+      <c r="I67" s="74"/>
+      <c r="J67" s="74"/>
+      <c r="K67" s="74"/>
+      <c r="L67" s="74"/>
+      <c r="M67" s="74"/>
+      <c r="N67" s="74"/>
+      <c r="O67" s="74" t="s">
+        <v>1499</v>
+      </c>
+      <c r="P67" s="74" t="s">
+        <v>1236</v>
+      </c>
+      <c r="Q67" s="74" t="s">
+        <v>1500</v>
+      </c>
+      <c r="R67" s="74" t="s">
+        <v>1237</v>
+      </c>
+      <c r="S67" s="74" t="s">
+        <v>1501</v>
+      </c>
+      <c r="T67" s="74" t="s">
+        <v>1238</v>
+      </c>
+      <c r="U67" s="74" t="s">
+        <v>1502</v>
+      </c>
+      <c r="V67" s="74" t="s">
+        <v>1239</v>
+      </c>
+      <c r="W67" s="74" t="s">
+        <v>1503</v>
+      </c>
+      <c r="X67" s="16">
+        <v>2</v>
+      </c>
+      <c r="Y67" s="75" t="s">
+        <v>1858</v>
+      </c>
+      <c r="Z67" s="74" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AA67" s="74"/>
+    </row>
+    <row r="68" spans="1:27">
+      <c r="A68" s="16">
+        <v>9</v>
+      </c>
+      <c r="B68" s="16">
+        <v>67</v>
+      </c>
+      <c r="C68" s="74" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D68" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" s="74" t="s">
+        <v>1505</v>
+      </c>
+      <c r="F68" s="74" t="s">
+        <v>1506</v>
+      </c>
+      <c r="G68" s="74" t="s">
+        <v>1507</v>
+      </c>
+      <c r="H68" s="74" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I68" s="74"/>
+      <c r="J68" s="74"/>
+      <c r="K68" s="74"/>
+      <c r="L68" s="74"/>
+      <c r="M68" s="74"/>
+      <c r="N68" s="74"/>
+      <c r="O68" s="74" t="s">
+        <v>1509</v>
+      </c>
+      <c r="P68" s="74" t="s">
+        <v>1510</v>
+      </c>
+      <c r="Q68" s="74" t="s">
+        <v>1511</v>
+      </c>
+      <c r="R68" s="74" t="s">
+        <v>1512</v>
+      </c>
+      <c r="S68" s="74" t="s">
+        <v>1513</v>
+      </c>
+      <c r="T68" s="74" t="s">
+        <v>1514</v>
+      </c>
+      <c r="U68" s="74" t="s">
+        <v>1508</v>
+      </c>
+      <c r="V68" s="74" t="s">
+        <v>1515</v>
+      </c>
+      <c r="W68" s="74" t="s">
+        <v>1516</v>
+      </c>
+      <c r="X68" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y68" s="75" t="s">
+        <v>1859</v>
+      </c>
+      <c r="Z68" s="74" t="s">
+        <v>1517</v>
+      </c>
+      <c r="AA68" s="74"/>
+    </row>
+    <row r="69" spans="1:27">
+      <c r="A69" s="16">
+        <v>9</v>
+      </c>
+      <c r="B69" s="16">
+        <v>68</v>
+      </c>
+      <c r="C69" s="74" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D69" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="E69" s="74" t="s">
+        <v>1518</v>
+      </c>
+      <c r="F69" s="74" t="s">
+        <v>1519</v>
+      </c>
+      <c r="G69" s="74" t="s">
+        <v>1520</v>
+      </c>
+      <c r="H69" s="74" t="s">
+        <v>1521</v>
+      </c>
+      <c r="I69" s="74" t="s">
+        <v>1522</v>
+      </c>
+      <c r="J69" s="74" t="s">
+        <v>1523</v>
+      </c>
+      <c r="K69" s="74" t="s">
+        <v>1524</v>
+      </c>
+      <c r="L69" s="74" t="s">
+        <v>1525</v>
+      </c>
+      <c r="M69" s="74" t="s">
+        <v>1526</v>
+      </c>
+      <c r="N69" s="74" t="s">
+        <v>1527</v>
+      </c>
+      <c r="O69" s="74"/>
+      <c r="P69" s="74" t="s">
+        <v>1528</v>
+      </c>
+      <c r="Q69" s="74" t="s">
+        <v>1521</v>
+      </c>
+      <c r="R69" s="74" t="s">
+        <v>1529</v>
+      </c>
+      <c r="S69" s="74" t="s">
+        <v>1523</v>
+      </c>
+      <c r="T69" s="74" t="s">
+        <v>1530</v>
+      </c>
+      <c r="U69" s="74" t="s">
+        <v>1525</v>
+      </c>
+      <c r="V69" s="74" t="s">
+        <v>1531</v>
+      </c>
+      <c r="W69" s="74" t="s">
+        <v>1527</v>
+      </c>
+      <c r="X69" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y69" s="74" t="s">
+        <v>1532</v>
+      </c>
+      <c r="Z69" s="74" t="s">
+        <v>1533</v>
+      </c>
+      <c r="AA69" s="74"/>
+    </row>
+    <row r="70" spans="1:27">
+      <c r="A70" s="16">
+        <v>9</v>
+      </c>
+      <c r="B70" s="16">
+        <v>69</v>
+      </c>
+      <c r="C70" s="74" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D70" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="75" t="s">
+        <v>1756</v>
+      </c>
+      <c r="F70" s="74" t="s">
+        <v>1534</v>
+      </c>
+      <c r="G70" s="74"/>
+      <c r="H70" s="74"/>
+      <c r="I70" s="74"/>
+      <c r="J70" s="74"/>
+      <c r="K70" s="74"/>
+      <c r="L70" s="74"/>
+      <c r="M70" s="74"/>
+      <c r="N70" s="74"/>
+      <c r="O70" s="74" t="s">
+        <v>1535</v>
+      </c>
+      <c r="P70" s="74" t="s">
+        <v>1243</v>
+      </c>
+      <c r="Q70" s="74" t="s">
+        <v>1536</v>
+      </c>
+      <c r="R70" s="74" t="s">
+        <v>1244</v>
+      </c>
+      <c r="S70" s="74" t="s">
+        <v>1537</v>
+      </c>
+      <c r="T70" s="74" t="s">
+        <v>1245</v>
+      </c>
+      <c r="U70" s="74" t="s">
+        <v>1538</v>
+      </c>
+      <c r="V70" s="74" t="s">
+        <v>1246</v>
+      </c>
+      <c r="W70" s="74" t="s">
+        <v>1539</v>
+      </c>
+      <c r="X70" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y70" s="75" t="s">
+        <v>1860</v>
+      </c>
+      <c r="Z70" s="74" t="s">
+        <v>1540</v>
+      </c>
+      <c r="AA70" s="74"/>
+    </row>
+    <row r="71" spans="1:27">
+      <c r="A71" s="16">
+        <v>9</v>
+      </c>
+      <c r="B71" s="16">
+        <v>70</v>
+      </c>
+      <c r="C71" s="74" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D71" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E71" s="74" t="s">
+        <v>1541</v>
+      </c>
+      <c r="F71" s="74" t="s">
+        <v>1542</v>
+      </c>
+      <c r="G71" s="74"/>
+      <c r="H71" s="74"/>
+      <c r="I71" s="74"/>
+      <c r="J71" s="74"/>
+      <c r="K71" s="74"/>
+      <c r="L71" s="74"/>
+      <c r="M71" s="74"/>
+      <c r="N71" s="74"/>
+      <c r="O71" s="74"/>
+      <c r="P71" s="74" t="s">
+        <v>1543</v>
+      </c>
+      <c r="Q71" s="74" t="s">
+        <v>1544</v>
+      </c>
+      <c r="R71" s="74" t="s">
+        <v>1545</v>
+      </c>
+      <c r="S71" s="74" t="s">
+        <v>1546</v>
+      </c>
+      <c r="T71" s="74" t="s">
+        <v>1547</v>
+      </c>
+      <c r="U71" s="74" t="s">
+        <v>1548</v>
+      </c>
+      <c r="V71" s="74" t="s">
+        <v>1549</v>
+      </c>
+      <c r="W71" s="74" t="s">
+        <v>1550</v>
+      </c>
+      <c r="X71" s="16">
+        <v>4</v>
+      </c>
+      <c r="Y71" s="74" t="s">
+        <v>1551</v>
+      </c>
+      <c r="Z71" s="74" t="s">
+        <v>1552</v>
+      </c>
+      <c r="AA71" s="74"/>
+    </row>
+    <row r="72" spans="1:27">
+      <c r="A72" s="16">
+        <v>9</v>
+      </c>
+      <c r="B72" s="16">
+        <v>71</v>
+      </c>
+      <c r="C72" s="74" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D72" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="75" t="s">
+        <v>1757</v>
+      </c>
+      <c r="F72" s="74" t="s">
+        <v>1553</v>
+      </c>
+      <c r="G72" s="74"/>
+      <c r="H72" s="74"/>
+      <c r="I72" s="74"/>
+      <c r="J72" s="74"/>
+      <c r="K72" s="74"/>
+      <c r="L72" s="74"/>
+      <c r="M72" s="74"/>
+      <c r="N72" s="74"/>
+      <c r="O72" s="74" t="s">
+        <v>1554</v>
+      </c>
+      <c r="P72" s="74" t="s">
+        <v>1249</v>
+      </c>
+      <c r="Q72" s="74" t="s">
+        <v>1555</v>
+      </c>
+      <c r="R72" s="74" t="s">
+        <v>1250</v>
+      </c>
+      <c r="S72" s="74" t="s">
+        <v>1556</v>
+      </c>
+      <c r="T72" s="74" t="s">
+        <v>1251</v>
+      </c>
+      <c r="U72" s="74" t="s">
+        <v>1557</v>
+      </c>
+      <c r="V72" s="74" t="s">
+        <v>1252</v>
+      </c>
+      <c r="W72" s="74" t="s">
+        <v>1558</v>
+      </c>
+      <c r="X72" s="16">
+        <v>4</v>
+      </c>
+      <c r="Y72" s="75" t="s">
+        <v>1861</v>
+      </c>
+      <c r="Z72" s="74" t="s">
+        <v>1559</v>
+      </c>
+      <c r="AA72" s="74"/>
+    </row>
+    <row r="73" spans="1:27">
+      <c r="A73" s="16">
+        <v>9</v>
+      </c>
+      <c r="B73" s="16">
+        <v>72</v>
+      </c>
+      <c r="C73" s="74" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D73" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E73" s="74" t="s">
+        <v>84</v>
+      </c>
+      <c r="F73" s="74" t="s">
+        <v>85</v>
+      </c>
+      <c r="G73" s="74" t="s">
+        <v>1560</v>
+      </c>
+      <c r="H73" s="74" t="s">
+        <v>1561</v>
+      </c>
+      <c r="I73" s="74"/>
+      <c r="J73" s="74"/>
+      <c r="K73" s="74"/>
+      <c r="L73" s="74"/>
+      <c r="M73" s="74"/>
+      <c r="N73" s="74"/>
+      <c r="O73" s="74" t="s">
+        <v>1562</v>
+      </c>
+      <c r="P73" s="74" t="s">
+        <v>1563</v>
+      </c>
+      <c r="Q73" s="74" t="s">
+        <v>1564</v>
+      </c>
+      <c r="R73" s="74" t="s">
+        <v>1565</v>
+      </c>
+      <c r="S73" s="74" t="s">
+        <v>1566</v>
+      </c>
+      <c r="T73" s="74" t="s">
+        <v>1567</v>
+      </c>
+      <c r="U73" s="74" t="s">
+        <v>1568</v>
+      </c>
+      <c r="V73" s="74" t="s">
+        <v>1569</v>
+      </c>
+      <c r="W73" s="74" t="s">
+        <v>1561</v>
+      </c>
+      <c r="X73" s="16">
+        <v>4</v>
+      </c>
+      <c r="Y73" s="74" t="s">
+        <v>1570</v>
+      </c>
+      <c r="Z73" s="74" t="s">
+        <v>1571</v>
+      </c>
+      <c r="AA73" s="74"/>
+    </row>
+    <row r="74" spans="1:27">
+      <c r="A74" s="16">
+        <v>9</v>
+      </c>
+      <c r="B74" s="16">
+        <v>73</v>
+      </c>
+      <c r="C74" s="74" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D74" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E74" s="74" t="s">
+        <v>1572</v>
+      </c>
+      <c r="F74" s="74" t="s">
+        <v>1573</v>
+      </c>
+      <c r="G74" s="74"/>
+      <c r="H74" s="74"/>
+      <c r="I74" s="74"/>
+      <c r="J74" s="74"/>
+      <c r="K74" s="74"/>
+      <c r="L74" s="74"/>
+      <c r="M74" s="74"/>
+      <c r="N74" s="74"/>
+      <c r="O74" s="74"/>
+      <c r="P74" s="74" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q74" s="74" t="s">
+        <v>296</v>
+      </c>
+      <c r="R74" s="74" t="s">
+        <v>1574</v>
+      </c>
+      <c r="S74" s="74" t="s">
+        <v>1575</v>
+      </c>
+      <c r="T74" s="74" t="s">
+        <v>1576</v>
+      </c>
+      <c r="U74" s="74" t="s">
+        <v>1577</v>
+      </c>
+      <c r="V74" s="74" t="s">
+        <v>1578</v>
+      </c>
+      <c r="W74" s="74" t="s">
+        <v>1579</v>
+      </c>
+      <c r="X74" s="16">
+        <v>4</v>
+      </c>
+      <c r="Y74" s="74" t="s">
+        <v>1580</v>
+      </c>
+      <c r="Z74" s="74" t="s">
+        <v>1581</v>
+      </c>
+      <c r="AA74" s="74"/>
+    </row>
+    <row r="75" spans="1:27">
+      <c r="A75" s="16">
+        <v>9</v>
+      </c>
+      <c r="B75" s="16">
+        <v>74</v>
+      </c>
+      <c r="C75" s="74" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D75" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E75" s="74" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F75" s="74" t="s">
+        <v>1583</v>
+      </c>
+      <c r="G75" s="74"/>
+      <c r="H75" s="74"/>
+      <c r="I75" s="74"/>
+      <c r="J75" s="74"/>
+      <c r="K75" s="74"/>
+      <c r="L75" s="74"/>
+      <c r="M75" s="74"/>
+      <c r="N75" s="74"/>
+      <c r="O75" s="74"/>
+      <c r="P75" s="74" t="s">
+        <v>1584</v>
+      </c>
+      <c r="Q75" s="74" t="s">
+        <v>1585</v>
+      </c>
+      <c r="R75" s="74" t="s">
+        <v>1586</v>
+      </c>
+      <c r="S75" s="74" t="s">
+        <v>1587</v>
+      </c>
+      <c r="T75" s="74" t="s">
+        <v>1588</v>
+      </c>
+      <c r="U75" s="74" t="s">
+        <v>1589</v>
+      </c>
+      <c r="V75" s="74" t="s">
+        <v>1590</v>
+      </c>
+      <c r="W75" s="74" t="s">
+        <v>1591</v>
+      </c>
+      <c r="X75" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y75" s="74" t="s">
+        <v>1592</v>
+      </c>
+      <c r="Z75" s="74" t="s">
+        <v>1593</v>
+      </c>
+      <c r="AA75" s="74"/>
+    </row>
+    <row r="76" spans="1:27">
+      <c r="A76" s="16">
+        <v>10</v>
+      </c>
+      <c r="B76" s="16">
+        <v>75</v>
+      </c>
+      <c r="C76" s="74" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D76" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E76" s="74" t="s">
+        <v>84</v>
+      </c>
+      <c r="F76" s="74" t="s">
+        <v>85</v>
+      </c>
+      <c r="G76" s="74" t="s">
+        <v>1594</v>
+      </c>
+      <c r="H76" s="74" t="s">
+        <v>1595</v>
+      </c>
+      <c r="I76" s="74"/>
+      <c r="J76" s="74"/>
+      <c r="K76" s="74"/>
+      <c r="L76" s="74"/>
+      <c r="M76" s="74"/>
+      <c r="N76" s="74"/>
+      <c r="O76" s="74" t="s">
+        <v>1596</v>
+      </c>
+      <c r="P76" s="74" t="s">
+        <v>1257</v>
+      </c>
+      <c r="Q76" s="74" t="s">
+        <v>1597</v>
+      </c>
+      <c r="R76" s="74" t="s">
+        <v>1258</v>
+      </c>
+      <c r="S76" s="74" t="s">
+        <v>1598</v>
+      </c>
+      <c r="T76" s="74" t="s">
+        <v>1259</v>
+      </c>
+      <c r="U76" s="74" t="s">
+        <v>1599</v>
+      </c>
+      <c r="V76" s="74" t="s">
+        <v>1256</v>
+      </c>
+      <c r="W76" s="74" t="s">
+        <v>1595</v>
+      </c>
+      <c r="X76" s="16">
+        <v>4</v>
+      </c>
+      <c r="Y76" s="74" t="s">
+        <v>1600</v>
+      </c>
+      <c r="Z76" s="74" t="s">
+        <v>1601</v>
+      </c>
+      <c r="AA76" s="74"/>
+    </row>
+    <row r="77" spans="1:27">
+      <c r="A77" s="16">
+        <v>10</v>
+      </c>
+      <c r="B77" s="16">
+        <v>76</v>
+      </c>
+      <c r="C77" s="74" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D77" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E77" s="74" t="s">
+        <v>84</v>
+      </c>
+      <c r="F77" s="74" t="s">
+        <v>85</v>
+      </c>
+      <c r="G77" s="74" t="s">
+        <v>1602</v>
+      </c>
+      <c r="H77" s="74" t="s">
+        <v>1603</v>
+      </c>
+      <c r="I77" s="74"/>
+      <c r="J77" s="74"/>
+      <c r="K77" s="74"/>
+      <c r="L77" s="74"/>
+      <c r="M77" s="74"/>
+      <c r="N77" s="74"/>
+      <c r="O77" s="74" t="s">
+        <v>1604</v>
+      </c>
+      <c r="P77" s="74" t="s">
+        <v>1261</v>
+      </c>
+      <c r="Q77" s="74" t="s">
+        <v>607</v>
+      </c>
+      <c r="R77" s="74" t="s">
+        <v>449</v>
+      </c>
+      <c r="S77" s="74" t="s">
+        <v>608</v>
+      </c>
+      <c r="T77" s="74" t="s">
+        <v>1260</v>
+      </c>
+      <c r="U77" s="74" t="s">
+        <v>1603</v>
+      </c>
+      <c r="V77" s="74" t="s">
+        <v>1262</v>
+      </c>
+      <c r="W77" s="74" t="s">
+        <v>1605</v>
+      </c>
+      <c r="X77" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y77" s="74" t="s">
+        <v>1606</v>
+      </c>
+      <c r="Z77" s="74" t="s">
+        <v>1607</v>
+      </c>
+      <c r="AA77" s="74"/>
+    </row>
+    <row r="78" spans="1:27">
+      <c r="A78" s="16">
+        <v>10</v>
+      </c>
+      <c r="B78" s="16">
+        <v>77</v>
+      </c>
+      <c r="C78" s="74" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D78" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E78" s="74" t="s">
+        <v>1608</v>
+      </c>
+      <c r="F78" s="74" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G78" s="74" t="s">
+        <v>1610</v>
+      </c>
+      <c r="H78" s="74" t="s">
+        <v>1611</v>
+      </c>
+      <c r="I78" s="74"/>
+      <c r="J78" s="74"/>
+      <c r="K78" s="74"/>
+      <c r="L78" s="74"/>
+      <c r="M78" s="74"/>
+      <c r="N78" s="74"/>
+      <c r="O78" s="74" t="s">
+        <v>1612</v>
+      </c>
+      <c r="P78" s="74" t="s">
+        <v>1263</v>
+      </c>
+      <c r="Q78" s="74" t="s">
+        <v>1613</v>
+      </c>
+      <c r="R78" s="74" t="s">
+        <v>1264</v>
+      </c>
+      <c r="S78" s="74" t="s">
+        <v>1614</v>
+      </c>
+      <c r="T78" s="74" t="s">
+        <v>1265</v>
+      </c>
+      <c r="U78" s="74" t="s">
+        <v>1615</v>
+      </c>
+      <c r="V78" s="74" t="s">
+        <v>940</v>
+      </c>
+      <c r="W78" s="74" t="s">
+        <v>941</v>
+      </c>
+      <c r="X78" s="16">
+        <v>1</v>
+      </c>
+      <c r="Y78" s="74" t="s">
+        <v>1616</v>
+      </c>
+      <c r="Z78" s="74" t="s">
+        <v>1617</v>
+      </c>
+      <c r="AA78" s="74"/>
+    </row>
+    <row r="79" spans="1:27">
+      <c r="A79" s="16">
+        <v>10</v>
+      </c>
+      <c r="B79" s="16">
+        <v>78</v>
+      </c>
+      <c r="C79" s="74" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D79" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E79" s="74" t="s">
+        <v>1618</v>
+      </c>
+      <c r="F79" s="74" t="s">
+        <v>1619</v>
+      </c>
+      <c r="G79" s="74"/>
+      <c r="H79" s="74"/>
+      <c r="I79" s="74"/>
+      <c r="J79" s="74"/>
+      <c r="K79" s="74"/>
+      <c r="L79" s="74"/>
+      <c r="M79" s="74"/>
+      <c r="N79" s="74"/>
+      <c r="O79" s="74" t="s">
+        <v>1620</v>
+      </c>
+      <c r="P79" s="74" t="s">
+        <v>1264</v>
+      </c>
+      <c r="Q79" s="74" t="s">
+        <v>1614</v>
+      </c>
+      <c r="R79" s="74" t="s">
+        <v>1266</v>
+      </c>
+      <c r="S79" s="74" t="s">
+        <v>1621</v>
+      </c>
+      <c r="T79" s="74" t="s">
+        <v>1267</v>
+      </c>
+      <c r="U79" s="74" t="s">
+        <v>1622</v>
+      </c>
+      <c r="V79" s="74" t="s">
+        <v>1268</v>
+      </c>
+      <c r="W79" s="74" t="s">
+        <v>1623</v>
+      </c>
+      <c r="X79" s="16">
+        <v>2</v>
+      </c>
+      <c r="Y79" s="74" t="s">
+        <v>1624</v>
+      </c>
+      <c r="Z79" s="74" t="s">
+        <v>1625</v>
+      </c>
+      <c r="AA79" s="74"/>
+    </row>
+    <row r="80" spans="1:27">
+      <c r="A80" s="16">
+        <v>10</v>
+      </c>
+      <c r="B80" s="16">
+        <v>79</v>
+      </c>
+      <c r="C80" s="74" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D80" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E80" s="74" t="s">
+        <v>1626</v>
+      </c>
+      <c r="F80" s="74" t="s">
+        <v>1627</v>
+      </c>
+      <c r="G80" s="74"/>
+      <c r="H80" s="74"/>
+      <c r="I80" s="74"/>
+      <c r="J80" s="74"/>
+      <c r="K80" s="74"/>
+      <c r="L80" s="74"/>
+      <c r="M80" s="74"/>
+      <c r="N80" s="74"/>
+      <c r="O80" s="74"/>
+      <c r="P80" s="74" t="s">
+        <v>1270</v>
+      </c>
+      <c r="Q80" s="74" t="s">
+        <v>1628</v>
+      </c>
+      <c r="R80" s="74" t="s">
+        <v>1271</v>
+      </c>
+      <c r="S80" s="74" t="s">
+        <v>1629</v>
+      </c>
+      <c r="T80" s="74" t="s">
+        <v>1272</v>
+      </c>
+      <c r="U80" s="74" t="s">
+        <v>1630</v>
+      </c>
+      <c r="V80" s="74" t="s">
+        <v>1269</v>
+      </c>
+      <c r="W80" s="74" t="s">
+        <v>1631</v>
+      </c>
+      <c r="X80" s="16">
+        <v>4</v>
+      </c>
+      <c r="Y80" s="74" t="s">
+        <v>1632</v>
+      </c>
+      <c r="Z80" s="74" t="s">
+        <v>1633</v>
+      </c>
+      <c r="AA80" s="74"/>
+    </row>
+    <row r="81" spans="1:27">
+      <c r="A81" s="16">
+        <v>10</v>
+      </c>
+      <c r="B81" s="16">
+        <v>80</v>
+      </c>
+      <c r="C81" s="74" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D81" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E81" s="74" t="s">
+        <v>1634</v>
+      </c>
+      <c r="F81" s="74" t="s">
+        <v>1635</v>
+      </c>
+      <c r="G81" s="74"/>
+      <c r="H81" s="74"/>
+      <c r="I81" s="74"/>
+      <c r="J81" s="74"/>
+      <c r="K81" s="74"/>
+      <c r="L81" s="74"/>
+      <c r="M81" s="74"/>
+      <c r="N81" s="74"/>
+      <c r="O81" s="74"/>
+      <c r="P81" s="74" t="s">
+        <v>1636</v>
+      </c>
+      <c r="Q81" s="74" t="s">
+        <v>1637</v>
+      </c>
+      <c r="R81" s="74" t="s">
+        <v>1638</v>
+      </c>
+      <c r="S81" s="74" t="s">
+        <v>1639</v>
+      </c>
+      <c r="T81" s="74" t="s">
+        <v>1640</v>
+      </c>
+      <c r="U81" s="74" t="s">
+        <v>1641</v>
+      </c>
+      <c r="V81" s="74" t="s">
+        <v>1642</v>
+      </c>
+      <c r="W81" s="74" t="s">
+        <v>1643</v>
+      </c>
+      <c r="X81" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y81" s="74" t="s">
+        <v>1644</v>
+      </c>
+      <c r="Z81" s="74" t="s">
+        <v>1645</v>
+      </c>
+      <c r="AA81" s="74"/>
+    </row>
+    <row r="82" spans="1:27">
+      <c r="A82" s="16">
+        <v>10</v>
+      </c>
+      <c r="B82" s="16">
+        <v>81</v>
+      </c>
+      <c r="C82" s="74" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D82" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E82" s="74" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F82" s="74" t="s">
+        <v>1647</v>
+      </c>
+      <c r="G82" s="74"/>
+      <c r="H82" s="74"/>
+      <c r="I82" s="74"/>
+      <c r="J82" s="74"/>
+      <c r="K82" s="74"/>
+      <c r="L82" s="74"/>
+      <c r="M82" s="74"/>
+      <c r="N82" s="74"/>
+      <c r="O82" s="74"/>
+      <c r="P82" s="74" t="s">
+        <v>1648</v>
+      </c>
+      <c r="Q82" s="74" t="s">
+        <v>1649</v>
+      </c>
+      <c r="R82" s="74" t="s">
+        <v>1650</v>
+      </c>
+      <c r="S82" s="74" t="s">
+        <v>1651</v>
+      </c>
+      <c r="T82" s="74" t="s">
+        <v>1652</v>
+      </c>
+      <c r="U82" s="74" t="s">
+        <v>1653</v>
+      </c>
+      <c r="V82" s="74" t="s">
+        <v>1654</v>
+      </c>
+      <c r="W82" s="74" t="s">
+        <v>1655</v>
+      </c>
+      <c r="X82" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y82" s="74" t="s">
+        <v>1656</v>
+      </c>
+      <c r="Z82" s="74" t="s">
+        <v>1657</v>
+      </c>
+      <c r="AA82" s="74"/>
+    </row>
+    <row r="83" spans="1:27">
+      <c r="A83" s="16">
+        <v>10</v>
+      </c>
+      <c r="B83" s="16">
+        <v>82</v>
+      </c>
+      <c r="C83" s="74" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D83" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E83" s="74" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F83" s="74" t="s">
+        <v>1659</v>
+      </c>
+      <c r="G83" s="74"/>
+      <c r="H83" s="74"/>
+      <c r="I83" s="74"/>
+      <c r="J83" s="74"/>
+      <c r="K83" s="74"/>
+      <c r="L83" s="74"/>
+      <c r="M83" s="74"/>
+      <c r="N83" s="74"/>
+      <c r="O83" s="74" t="s">
+        <v>1660</v>
+      </c>
+      <c r="P83" s="74" t="s">
+        <v>1276</v>
+      </c>
+      <c r="Q83" s="74" t="s">
+        <v>1661</v>
+      </c>
+      <c r="R83" s="74" t="s">
+        <v>1277</v>
+      </c>
+      <c r="S83" s="74" t="s">
+        <v>1662</v>
+      </c>
+      <c r="T83" s="74" t="s">
+        <v>1278</v>
+      </c>
+      <c r="U83" s="74" t="s">
+        <v>1663</v>
+      </c>
+      <c r="V83" s="74" t="s">
+        <v>1275</v>
+      </c>
+      <c r="W83" s="74" t="s">
+        <v>1664</v>
+      </c>
+      <c r="X83" s="16">
+        <v>4</v>
+      </c>
+      <c r="Y83" s="74" t="s">
+        <v>1665</v>
+      </c>
+      <c r="Z83" s="74" t="s">
+        <v>1666</v>
+      </c>
+      <c r="AA83" s="74"/>
+    </row>
+    <row r="84" spans="1:27">
+      <c r="A84" s="16">
+        <v>10</v>
+      </c>
+      <c r="B84" s="16">
+        <v>83</v>
+      </c>
+      <c r="C84" s="74" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D84" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E84" s="74" t="s">
+        <v>1667</v>
+      </c>
+      <c r="F84" s="74" t="s">
+        <v>1668</v>
+      </c>
+      <c r="G84" s="74"/>
+      <c r="H84" s="74"/>
+      <c r="I84" s="74"/>
+      <c r="J84" s="74"/>
+      <c r="K84" s="74"/>
+      <c r="L84" s="74"/>
+      <c r="M84" s="74"/>
+      <c r="N84" s="74"/>
+      <c r="O84" s="74"/>
+      <c r="P84" s="74" t="s">
+        <v>1669</v>
+      </c>
+      <c r="Q84" s="74" t="s">
+        <v>1670</v>
+      </c>
+      <c r="R84" s="74" t="s">
+        <v>1671</v>
+      </c>
+      <c r="S84" s="74" t="s">
+        <v>1672</v>
+      </c>
+      <c r="T84" s="74" t="s">
+        <v>1673</v>
+      </c>
+      <c r="U84" s="74" t="s">
+        <v>1674</v>
+      </c>
+      <c r="V84" s="74" t="s">
+        <v>1675</v>
+      </c>
+      <c r="W84" s="74" t="s">
+        <v>1676</v>
+      </c>
+      <c r="X84" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y84" s="74" t="s">
+        <v>1677</v>
+      </c>
+      <c r="Z84" s="74" t="s">
+        <v>1678</v>
+      </c>
+      <c r="AA84" s="74"/>
+    </row>
+    <row r="85" spans="1:27">
+      <c r="A85" s="16">
+        <v>11</v>
+      </c>
+      <c r="B85" s="16">
+        <v>84</v>
+      </c>
+      <c r="C85" s="74" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D85" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E85" s="74" t="s">
+        <v>1679</v>
+      </c>
+      <c r="F85" s="74" t="s">
+        <v>1680</v>
+      </c>
+      <c r="G85" s="74"/>
+      <c r="H85" s="74"/>
+      <c r="I85" s="74"/>
+      <c r="J85" s="74"/>
+      <c r="K85" s="74"/>
+      <c r="L85" s="74"/>
+      <c r="M85" s="74"/>
+      <c r="N85" s="74"/>
+      <c r="O85" s="74" t="s">
+        <v>1681</v>
+      </c>
+      <c r="P85" s="74" t="s">
+        <v>1281</v>
+      </c>
+      <c r="Q85" s="74" t="s">
+        <v>1682</v>
+      </c>
+      <c r="R85" s="74" t="s">
+        <v>1282</v>
+      </c>
+      <c r="S85" s="74" t="s">
+        <v>1683</v>
+      </c>
+      <c r="T85" s="74" t="s">
+        <v>1283</v>
+      </c>
+      <c r="U85" s="74" t="s">
+        <v>1684</v>
+      </c>
+      <c r="V85" s="74" t="s">
+        <v>1284</v>
+      </c>
+      <c r="W85" s="74" t="s">
+        <v>1685</v>
+      </c>
+      <c r="X85" s="16">
+        <v>4</v>
+      </c>
+      <c r="Y85" s="75" t="s">
+        <v>1862</v>
+      </c>
+      <c r="Z85" s="74" t="s">
+        <v>1686</v>
+      </c>
+      <c r="AA85" s="74"/>
+    </row>
+    <row r="86" spans="1:27">
+      <c r="A86" s="16">
+        <v>11</v>
+      </c>
+      <c r="B86" s="16">
+        <v>85</v>
+      </c>
+      <c r="C86" s="74" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D86" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="E86" s="74" t="s">
+        <v>1687</v>
+      </c>
+      <c r="F86" s="74" t="s">
+        <v>1688</v>
+      </c>
+      <c r="G86" s="74" t="s">
+        <v>1689</v>
+      </c>
+      <c r="H86" s="74" t="s">
+        <v>1690</v>
+      </c>
+      <c r="I86" s="74" t="s">
+        <v>1691</v>
+      </c>
+      <c r="J86" s="74" t="s">
+        <v>1692</v>
+      </c>
+      <c r="K86" s="74" t="s">
+        <v>1693</v>
+      </c>
+      <c r="L86" s="74" t="s">
+        <v>1685</v>
+      </c>
+      <c r="M86" s="74" t="s">
+        <v>1694</v>
+      </c>
+      <c r="N86" s="74" t="s">
+        <v>1695</v>
+      </c>
+      <c r="O86" s="74"/>
+      <c r="P86" s="74" t="s">
+        <v>1696</v>
+      </c>
+      <c r="Q86" s="74" t="s">
+        <v>1690</v>
+      </c>
+      <c r="R86" s="74" t="s">
+        <v>1697</v>
+      </c>
+      <c r="S86" s="74" t="s">
+        <v>1692</v>
+      </c>
+      <c r="T86" s="74" t="s">
+        <v>1698</v>
+      </c>
+      <c r="U86" s="74" t="s">
+        <v>1685</v>
+      </c>
+      <c r="V86" s="74" t="s">
+        <v>1699</v>
+      </c>
+      <c r="W86" s="74" t="s">
+        <v>1700</v>
+      </c>
+      <c r="X86" s="16">
+        <v>1</v>
+      </c>
+      <c r="Y86" s="74" t="s">
+        <v>1701</v>
+      </c>
+      <c r="Z86" s="74" t="s">
+        <v>1702</v>
+      </c>
+      <c r="AA86" s="74"/>
+    </row>
+    <row r="87" spans="1:27">
+      <c r="A87" s="16">
+        <v>11</v>
+      </c>
+      <c r="B87" s="16">
+        <v>86</v>
+      </c>
+      <c r="C87" s="74" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D87" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="E87" s="74" t="s">
+        <v>1703</v>
+      </c>
+      <c r="F87" s="74" t="s">
+        <v>1704</v>
+      </c>
+      <c r="G87" s="74" t="s">
+        <v>1705</v>
+      </c>
+      <c r="H87" s="74" t="s">
+        <v>1706</v>
+      </c>
+      <c r="I87" s="74" t="s">
+        <v>1707</v>
+      </c>
+      <c r="J87" s="74" t="s">
+        <v>1708</v>
+      </c>
+      <c r="K87" s="74" t="s">
+        <v>1709</v>
+      </c>
+      <c r="L87" s="74" t="s">
+        <v>1710</v>
+      </c>
+      <c r="M87" s="74" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N87" s="74" t="s">
+        <v>1712</v>
+      </c>
+      <c r="O87" s="74"/>
+      <c r="P87" s="74" t="s">
+        <v>1713</v>
+      </c>
+      <c r="Q87" s="74" t="s">
+        <v>1706</v>
+      </c>
+      <c r="R87" s="74" t="s">
+        <v>1714</v>
+      </c>
+      <c r="S87" s="74" t="s">
+        <v>1708</v>
+      </c>
+      <c r="T87" s="74" t="s">
+        <v>1715</v>
+      </c>
+      <c r="U87" s="74" t="s">
+        <v>1710</v>
+      </c>
+      <c r="V87" s="74" t="s">
+        <v>1716</v>
+      </c>
+      <c r="W87" s="74" t="s">
+        <v>1712</v>
+      </c>
+      <c r="X87" s="16">
+        <v>4</v>
+      </c>
+      <c r="Y87" s="74" t="s">
+        <v>1717</v>
+      </c>
+      <c r="Z87" s="74" t="s">
+        <v>1718</v>
+      </c>
+      <c r="AA87" s="74"/>
+    </row>
+    <row r="88" spans="1:27">
+      <c r="A88" s="16">
+        <v>11</v>
+      </c>
+      <c r="B88" s="16">
+        <v>87</v>
+      </c>
+      <c r="C88" s="74" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D88" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E88" s="74" t="s">
+        <v>1719</v>
+      </c>
+      <c r="F88" s="74" t="s">
+        <v>1720</v>
+      </c>
+      <c r="G88" s="74"/>
+      <c r="H88" s="74"/>
+      <c r="I88" s="74"/>
+      <c r="J88" s="74"/>
+      <c r="K88" s="74"/>
+      <c r="L88" s="74"/>
+      <c r="M88" s="74"/>
+      <c r="N88" s="74"/>
+      <c r="O88" s="74" t="s">
+        <v>1721</v>
+      </c>
+      <c r="P88" s="74" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q88" s="74" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R88" s="74" t="s">
+        <v>1288</v>
+      </c>
+      <c r="S88" s="74" t="s">
+        <v>1723</v>
+      </c>
+      <c r="T88" s="74" t="s">
+        <v>1724</v>
+      </c>
+      <c r="U88" s="74" t="s">
+        <v>1725</v>
+      </c>
+      <c r="V88" s="74" t="s">
+        <v>1726</v>
+      </c>
+      <c r="W88" s="74" t="s">
+        <v>1727</v>
+      </c>
+      <c r="X88" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y88" s="74" t="s">
+        <v>1728</v>
+      </c>
+      <c r="Z88" s="74" t="s">
+        <v>1729</v>
+      </c>
+      <c r="AA88" s="74"/>
+    </row>
+    <row r="89" spans="1:27">
+      <c r="A89" s="16">
+        <v>11</v>
+      </c>
+      <c r="B89" s="16">
+        <v>88</v>
+      </c>
+      <c r="C89" s="74" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D89" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E89" s="74" t="s">
+        <v>1730</v>
+      </c>
+      <c r="F89" s="74" t="s">
+        <v>1731</v>
+      </c>
+      <c r="G89" s="74" t="s">
+        <v>1732</v>
+      </c>
+      <c r="H89" s="74" t="s">
+        <v>1733</v>
+      </c>
+      <c r="I89" s="74"/>
+      <c r="J89" s="74"/>
+      <c r="K89" s="74"/>
+      <c r="L89" s="74"/>
+      <c r="M89" s="74"/>
+      <c r="N89" s="74"/>
+      <c r="O89" s="74" t="s">
+        <v>1734</v>
+      </c>
+      <c r="P89" s="74" t="s">
+        <v>1290</v>
+      </c>
+      <c r="Q89" s="74" t="s">
+        <v>1735</v>
+      </c>
+      <c r="R89" s="74" t="s">
+        <v>1291</v>
+      </c>
+      <c r="S89" s="74" t="s">
+        <v>1736</v>
+      </c>
+      <c r="T89" s="74" t="s">
+        <v>1292</v>
+      </c>
+      <c r="U89" s="74" t="s">
+        <v>1737</v>
+      </c>
+      <c r="V89" s="74" t="s">
+        <v>1293</v>
+      </c>
+      <c r="W89" s="74" t="s">
+        <v>1738</v>
+      </c>
+      <c r="X89" s="16">
+        <v>4</v>
+      </c>
+      <c r="Y89" s="74" t="s">
+        <v>1739</v>
+      </c>
+      <c r="Z89" s="74" t="s">
+        <v>1740</v>
+      </c>
+      <c r="AA89" s="74"/>
+    </row>
+    <row r="90" spans="1:27">
+      <c r="A90" s="16">
+        <v>11</v>
+      </c>
+      <c r="B90" s="16">
+        <v>90</v>
+      </c>
+      <c r="C90" s="74" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D90" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E90" s="74" t="s">
+        <v>1741</v>
+      </c>
+      <c r="F90" s="74" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G90" s="74"/>
+      <c r="H90" s="74"/>
+      <c r="I90" s="74"/>
+      <c r="J90" s="74"/>
+      <c r="K90" s="74"/>
+      <c r="L90" s="74"/>
+      <c r="M90" s="74"/>
+      <c r="N90" s="74"/>
+      <c r="O90" s="74" t="s">
+        <v>1743</v>
+      </c>
+      <c r="P90" s="74" t="s">
+        <v>1295</v>
+      </c>
+      <c r="Q90" s="74" t="s">
+        <v>1744</v>
+      </c>
+      <c r="R90" s="74" t="s">
+        <v>1296</v>
+      </c>
+      <c r="S90" s="74" t="s">
+        <v>1745</v>
+      </c>
+      <c r="T90" s="74" t="s">
+        <v>1297</v>
+      </c>
+      <c r="U90" s="74" t="s">
+        <v>1746</v>
+      </c>
+      <c r="V90" s="74" t="s">
+        <v>1268</v>
+      </c>
+      <c r="W90" s="74" t="s">
+        <v>1623</v>
+      </c>
+      <c r="X90" s="16">
+        <v>1</v>
+      </c>
+      <c r="Y90" s="74" t="s">
+        <v>1747</v>
+      </c>
+      <c r="Z90" s="74" t="s">
+        <v>1748</v>
+      </c>
+      <c r="AA90" s="74"/>
+    </row>
+    <row r="91" spans="1:27">
+      <c r="A91" s="16">
+        <v>11</v>
+      </c>
+      <c r="B91" s="16">
+        <v>91</v>
+      </c>
+      <c r="C91" s="74" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D91" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E91" s="74" t="s">
+        <v>1759</v>
+      </c>
+      <c r="F91" s="74" t="s">
+        <v>1760</v>
+      </c>
+      <c r="G91" s="74"/>
+      <c r="H91" s="74"/>
+      <c r="I91" s="74"/>
+      <c r="J91" s="74"/>
+      <c r="K91" s="74"/>
+      <c r="L91" s="74"/>
+      <c r="M91" s="74"/>
+      <c r="N91" s="74"/>
+      <c r="O91" s="74"/>
+      <c r="P91" s="76" t="s">
+        <v>1863</v>
+      </c>
+      <c r="Q91" s="76" t="s">
+        <v>1864</v>
+      </c>
+      <c r="R91" s="76" t="s">
+        <v>1865</v>
+      </c>
+      <c r="S91" s="76" t="s">
+        <v>1866</v>
+      </c>
+      <c r="T91" s="76" t="s">
+        <v>1867</v>
+      </c>
+      <c r="U91" s="76" t="s">
+        <v>1868</v>
+      </c>
+      <c r="V91" s="76" t="s">
+        <v>1869</v>
+      </c>
+      <c r="W91" s="76" t="s">
+        <v>1870</v>
+      </c>
+      <c r="X91" s="16">
+        <v>2</v>
+      </c>
+      <c r="Y91" s="74" t="s">
+        <v>1761</v>
+      </c>
+      <c r="Z91" s="74" t="s">
+        <v>1762</v>
+      </c>
+      <c r="AA91" s="74"/>
+    </row>
+    <row r="92" spans="1:27">
+      <c r="A92" s="16">
+        <v>12</v>
+      </c>
+      <c r="B92" s="16">
+        <v>92</v>
+      </c>
+      <c r="C92" s="74" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D92" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E92" s="74" t="s">
+        <v>1763</v>
+      </c>
+      <c r="F92" s="74" t="s">
+        <v>1764</v>
+      </c>
+      <c r="G92" s="74"/>
+      <c r="H92" s="74"/>
+      <c r="I92" s="74"/>
+      <c r="J92" s="74"/>
+      <c r="K92" s="74"/>
+      <c r="L92" s="74"/>
+      <c r="M92" s="74"/>
+      <c r="N92" s="74"/>
+      <c r="O92" s="74"/>
+      <c r="P92" s="74" t="s">
+        <v>1765</v>
+      </c>
+      <c r="Q92" s="74" t="s">
+        <v>1766</v>
+      </c>
+      <c r="R92" s="74" t="s">
+        <v>1767</v>
+      </c>
+      <c r="S92" s="74" t="s">
+        <v>1768</v>
+      </c>
+      <c r="T92" s="74" t="s">
+        <v>1769</v>
+      </c>
+      <c r="U92" s="74" t="s">
+        <v>1770</v>
+      </c>
+      <c r="V92" s="74" t="s">
+        <v>1771</v>
+      </c>
+      <c r="W92" s="74" t="s">
+        <v>1772</v>
+      </c>
+      <c r="X92" s="16">
+        <v>1</v>
+      </c>
+      <c r="Y92" s="74" t="s">
+        <v>1773</v>
+      </c>
+      <c r="Z92" s="74" t="s">
+        <v>1774</v>
+      </c>
+      <c r="AA92" s="74"/>
+    </row>
+    <row r="93" spans="1:27">
+      <c r="A93" s="16">
+        <v>12</v>
+      </c>
+      <c r="B93" s="16">
+        <v>93</v>
+      </c>
+      <c r="C93" s="74" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D93" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E93" s="74" t="s">
+        <v>1775</v>
+      </c>
+      <c r="F93" s="74" t="s">
+        <v>1776</v>
+      </c>
+      <c r="G93" s="74"/>
+      <c r="H93" s="74"/>
+      <c r="I93" s="74"/>
+      <c r="J93" s="74"/>
+      <c r="K93" s="74"/>
+      <c r="L93" s="74"/>
+      <c r="M93" s="74"/>
+      <c r="N93" s="74"/>
+      <c r="O93" s="74" t="s">
+        <v>1777</v>
+      </c>
+      <c r="P93" s="76" t="s">
+        <v>1871</v>
+      </c>
+      <c r="Q93" s="76" t="s">
+        <v>1872</v>
+      </c>
+      <c r="R93" s="76" t="s">
+        <v>1873</v>
+      </c>
+      <c r="S93" s="76" t="s">
+        <v>1874</v>
+      </c>
+      <c r="T93" s="76" t="s">
+        <v>1875</v>
+      </c>
+      <c r="U93" s="76" t="s">
+        <v>1876</v>
+      </c>
+      <c r="V93" s="76" t="s">
+        <v>1877</v>
+      </c>
+      <c r="W93" s="76" t="s">
+        <v>1878</v>
+      </c>
+      <c r="X93" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y93" s="74" t="s">
+        <v>1778</v>
+      </c>
+      <c r="Z93" s="74" t="s">
+        <v>1779</v>
+      </c>
+      <c r="AA93" s="74"/>
+    </row>
+    <row r="94" spans="1:27">
+      <c r="A94" s="16">
+        <v>12</v>
+      </c>
+      <c r="B94" s="16">
+        <v>94</v>
+      </c>
+      <c r="C94" s="74" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D94" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E94" s="74" t="s">
+        <v>1780</v>
+      </c>
+      <c r="F94" s="74" t="s">
+        <v>1781</v>
+      </c>
+      <c r="G94" s="74"/>
+      <c r="H94" s="74"/>
+      <c r="I94" s="74"/>
+      <c r="J94" s="74"/>
+      <c r="K94" s="74"/>
+      <c r="L94" s="74"/>
+      <c r="M94" s="74"/>
+      <c r="N94" s="74"/>
+      <c r="O94" s="74"/>
+      <c r="P94" s="74" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Q94" s="74" t="s">
+        <v>1782</v>
+      </c>
+      <c r="R94" s="74" t="s">
+        <v>1783</v>
+      </c>
+      <c r="S94" s="74" t="s">
+        <v>1784</v>
+      </c>
+      <c r="T94" s="74" t="s">
+        <v>1302</v>
+      </c>
+      <c r="U94" s="74" t="s">
+        <v>1785</v>
+      </c>
+      <c r="V94" s="74" t="s">
+        <v>1303</v>
+      </c>
+      <c r="W94" s="74" t="s">
+        <v>1786</v>
+      </c>
+      <c r="X94" s="16">
+        <v>1</v>
+      </c>
+      <c r="Y94" s="74" t="s">
+        <v>1787</v>
+      </c>
+      <c r="Z94" s="74" t="s">
+        <v>1788</v>
+      </c>
+      <c r="AA94" s="74"/>
+    </row>
+    <row r="95" spans="1:27">
+      <c r="A95" s="16">
+        <v>12</v>
+      </c>
+      <c r="B95" s="16">
+        <v>95</v>
+      </c>
+      <c r="C95" s="74" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D95" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E95" s="74" t="s">
+        <v>1789</v>
+      </c>
+      <c r="F95" s="74" t="s">
+        <v>1790</v>
+      </c>
+      <c r="G95" s="74"/>
+      <c r="H95" s="74"/>
+      <c r="I95" s="74"/>
+      <c r="J95" s="74"/>
+      <c r="K95" s="74"/>
+      <c r="L95" s="74"/>
+      <c r="M95" s="74"/>
+      <c r="N95" s="74"/>
+      <c r="O95" s="74" t="s">
+        <v>1791</v>
+      </c>
+      <c r="P95" s="74" t="s">
+        <v>1792</v>
+      </c>
+      <c r="Q95" s="74" t="s">
+        <v>1793</v>
+      </c>
+      <c r="R95" s="74" t="s">
+        <v>1305</v>
+      </c>
+      <c r="S95" s="74" t="s">
+        <v>1794</v>
+      </c>
+      <c r="T95" s="74" t="s">
+        <v>1795</v>
+      </c>
+      <c r="U95" s="74" t="s">
+        <v>1796</v>
+      </c>
+      <c r="V95" s="74" t="s">
+        <v>1797</v>
+      </c>
+      <c r="W95" s="74" t="s">
+        <v>1798</v>
+      </c>
+      <c r="X95" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y95" s="74" t="s">
+        <v>1799</v>
+      </c>
+      <c r="Z95" s="74" t="s">
+        <v>1800</v>
+      </c>
+      <c r="AA95" s="74"/>
+    </row>
+    <row r="96" spans="1:27">
+      <c r="A96" s="16">
+        <v>12</v>
+      </c>
+      <c r="B96" s="16">
+        <v>96</v>
+      </c>
+      <c r="C96" s="74" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D96" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E96" s="74" t="s">
+        <v>1801</v>
+      </c>
+      <c r="F96" s="74" t="s">
+        <v>1802</v>
+      </c>
+      <c r="G96" s="74"/>
+      <c r="H96" s="74"/>
+      <c r="I96" s="74"/>
+      <c r="J96" s="74"/>
+      <c r="K96" s="74"/>
+      <c r="L96" s="74"/>
+      <c r="M96" s="74"/>
+      <c r="N96" s="74"/>
+      <c r="O96" s="74" t="s">
+        <v>1803</v>
+      </c>
+      <c r="P96" s="74" t="s">
+        <v>1081</v>
+      </c>
+      <c r="Q96" s="74" t="s">
+        <v>1804</v>
+      </c>
+      <c r="R96" s="74" t="s">
+        <v>1307</v>
+      </c>
+      <c r="S96" s="74" t="s">
+        <v>1805</v>
+      </c>
+      <c r="T96" s="74" t="s">
+        <v>233</v>
+      </c>
+      <c r="U96" s="74" t="s">
+        <v>1806</v>
+      </c>
+      <c r="V96" s="74" t="s">
+        <v>1807</v>
+      </c>
+      <c r="W96" s="74" t="s">
+        <v>1808</v>
+      </c>
+      <c r="X96" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y96" s="74" t="s">
+        <v>1809</v>
+      </c>
+      <c r="Z96" s="74" t="s">
+        <v>1810</v>
+      </c>
+      <c r="AA96" s="74"/>
+    </row>
+    <row r="97" spans="1:27">
+      <c r="A97" s="16">
+        <v>12</v>
+      </c>
+      <c r="B97" s="16">
+        <v>97</v>
+      </c>
+      <c r="C97" s="74" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D97" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E97" s="74" t="s">
+        <v>1811</v>
+      </c>
+      <c r="F97" s="74" t="s">
+        <v>1812</v>
+      </c>
+      <c r="G97" s="74"/>
+      <c r="H97" s="74"/>
+      <c r="I97" s="74"/>
+      <c r="J97" s="74"/>
+      <c r="K97" s="74"/>
+      <c r="L97" s="74"/>
+      <c r="M97" s="74"/>
+      <c r="N97" s="74"/>
+      <c r="O97" s="74"/>
+      <c r="P97" s="74" t="s">
+        <v>1309</v>
+      </c>
+      <c r="Q97" s="74" t="s">
+        <v>1813</v>
+      </c>
+      <c r="R97" s="74" t="s">
+        <v>393</v>
+      </c>
+      <c r="S97" s="74" t="s">
+        <v>394</v>
+      </c>
+      <c r="T97" s="74" t="s">
+        <v>1310</v>
+      </c>
+      <c r="U97" s="74" t="s">
+        <v>1814</v>
+      </c>
+      <c r="V97" s="74" t="s">
+        <v>1311</v>
+      </c>
+      <c r="W97" s="74" t="s">
+        <v>1815</v>
+      </c>
+      <c r="X97" s="16">
+        <v>1</v>
+      </c>
+      <c r="Y97" s="74" t="s">
+        <v>1816</v>
+      </c>
+      <c r="Z97" s="74" t="s">
+        <v>1817</v>
+      </c>
+      <c r="AA97" s="74"/>
+    </row>
+    <row r="98" spans="1:27">
+      <c r="A98" s="16">
+        <v>12</v>
+      </c>
+      <c r="B98" s="16">
+        <v>98</v>
+      </c>
+      <c r="C98" s="74" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D98" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E98" s="74" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F98" s="74" t="s">
+        <v>1819</v>
+      </c>
+      <c r="G98" s="74"/>
+      <c r="H98" s="74"/>
+      <c r="I98" s="74"/>
+      <c r="J98" s="74"/>
+      <c r="K98" s="74"/>
+      <c r="L98" s="74"/>
+      <c r="M98" s="74"/>
+      <c r="N98" s="74"/>
+      <c r="O98" s="74"/>
+      <c r="P98" s="74" t="s">
+        <v>1820</v>
+      </c>
+      <c r="Q98" s="74" t="s">
+        <v>1821</v>
+      </c>
+      <c r="R98" s="74" t="s">
+        <v>1822</v>
+      </c>
+      <c r="S98" s="74" t="s">
+        <v>1823</v>
+      </c>
+      <c r="T98" s="74" t="s">
+        <v>1824</v>
+      </c>
+      <c r="U98" s="74" t="s">
+        <v>1825</v>
+      </c>
+      <c r="V98" s="74" t="s">
+        <v>1826</v>
+      </c>
+      <c r="W98" s="74" t="s">
+        <v>1827</v>
+      </c>
+      <c r="X98" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y98" s="74" t="s">
+        <v>1828</v>
+      </c>
+      <c r="Z98" s="74" t="s">
+        <v>1829</v>
+      </c>
+      <c r="AA98" s="74"/>
+    </row>
+    <row r="99" spans="1:27">
+      <c r="A99" s="16">
+        <v>12</v>
+      </c>
+      <c r="B99" s="16">
+        <v>99</v>
+      </c>
+      <c r="C99" s="74" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D99" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E99" s="74" t="s">
+        <v>1830</v>
+      </c>
+      <c r="F99" s="74" t="s">
+        <v>1831</v>
+      </c>
+      <c r="G99" s="74"/>
+      <c r="H99" s="74"/>
+      <c r="I99" s="74"/>
+      <c r="J99" s="74"/>
+      <c r="K99" s="74"/>
+      <c r="L99" s="74"/>
+      <c r="M99" s="74"/>
+      <c r="N99" s="74"/>
+      <c r="O99" s="74" t="s">
+        <v>1832</v>
+      </c>
+      <c r="P99" s="74" t="s">
+        <v>1833</v>
+      </c>
+      <c r="Q99" s="74" t="s">
+        <v>1834</v>
+      </c>
+      <c r="R99" s="74" t="s">
+        <v>1835</v>
+      </c>
+      <c r="S99" s="74" t="s">
+        <v>1836</v>
+      </c>
+      <c r="T99" s="74" t="s">
+        <v>1837</v>
+      </c>
+      <c r="U99" s="74" t="s">
+        <v>1838</v>
+      </c>
+      <c r="V99" s="74" t="s">
+        <v>1839</v>
+      </c>
+      <c r="W99" s="74" t="s">
+        <v>1840</v>
+      </c>
+      <c r="X99" s="16">
+        <v>3</v>
+      </c>
+      <c r="Y99" s="74" t="s">
+        <v>1841</v>
+      </c>
+      <c r="Z99" s="74" t="s">
+        <v>1842</v>
+      </c>
+      <c r="AA99" s="74"/>
+    </row>
+    <row r="100" spans="1:27">
+      <c r="A100" s="16">
+        <v>12</v>
+      </c>
+      <c r="B100" s="16">
+        <v>100</v>
+      </c>
+      <c r="C100" s="74" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D100" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E100" s="74" t="s">
+        <v>1843</v>
+      </c>
+      <c r="F100" s="74" t="s">
+        <v>1844</v>
+      </c>
+      <c r="G100" s="74"/>
+      <c r="H100" s="74"/>
+      <c r="I100" s="74"/>
+      <c r="J100" s="74"/>
+      <c r="K100" s="74"/>
+      <c r="L100" s="74"/>
+      <c r="M100" s="74"/>
+      <c r="N100" s="74"/>
+      <c r="O100" s="74" t="s">
+        <v>1845</v>
+      </c>
+      <c r="P100" s="74" t="s">
+        <v>1846</v>
+      </c>
+      <c r="Q100" s="74" t="s">
+        <v>1847</v>
+      </c>
+      <c r="R100" s="74" t="s">
+        <v>1848</v>
+      </c>
+      <c r="S100" s="74" t="s">
+        <v>1849</v>
+      </c>
+      <c r="T100" s="74" t="s">
+        <v>1850</v>
+      </c>
+      <c r="U100" s="74" t="s">
+        <v>1851</v>
+      </c>
+      <c r="V100" s="74" t="s">
+        <v>1852</v>
+      </c>
+      <c r="W100" s="74" t="s">
+        <v>1853</v>
+      </c>
+      <c r="X100" s="16">
+        <v>4</v>
+      </c>
+      <c r="Y100" s="74" t="s">
+        <v>1854</v>
+      </c>
+      <c r="Z100" s="74" t="s">
+        <v>1855</v>
+      </c>
+      <c r="AA100" s="74"/>
+    </row>
+    <row r="101" spans="1:27">
       <c r="A101" s="16"/>
       <c r="B101" s="16"/>
       <c r="X101" s="16"/>
     </row>
-    <row r="102" spans="1:24">
+    <row r="102" spans="1:27">
       <c r="A102" s="16"/>
       <c r="B102" s="16"/>
       <c r="X102" s="16"/>
     </row>
-    <row r="103" spans="1:24">
+    <row r="103" spans="1:27">
       <c r="A103" s="16"/>
       <c r="B103" s="16"/>
       <c r="X103" s="16"/>
     </row>
-    <row r="104" spans="1:24">
+    <row r="104" spans="1:27">
       <c r="A104" s="16"/>
       <c r="B104" s="16"/>
       <c r="X104" s="16"/>
     </row>
-    <row r="105" spans="1:24">
+    <row r="105" spans="1:27">
       <c r="A105" s="16"/>
       <c r="B105" s="16"/>
       <c r="X105" s="16"/>
     </row>
-    <row r="106" spans="1:24">
+    <row r="106" spans="1:27">
       <c r="A106" s="16"/>
       <c r="B106" s="16"/>
       <c r="X106" s="16"/>
     </row>
-    <row r="107" spans="1:24">
+    <row r="107" spans="1:27">
       <c r="A107" s="16"/>
       <c r="B107" s="16"/>
       <c r="X107" s="16"/>
     </row>
-    <row r="108" spans="1:24">
+    <row r="108" spans="1:27">
       <c r="A108" s="16"/>
       <c r="B108" s="16"/>
       <c r="X108" s="16"/>
     </row>
-    <row r="109" spans="1:24">
+    <row r="109" spans="1:27">
       <c r="A109" s="16"/>
       <c r="B109" s="16"/>
       <c r="X109" s="16"/>
     </row>
-    <row r="110" spans="1:24">
+    <row r="110" spans="1:27">
       <c r="A110" s="16"/>
       <c r="B110" s="16"/>
       <c r="X110" s="16"/>
     </row>
-    <row r="111" spans="1:24">
+    <row r="111" spans="1:27">
       <c r="A111" s="16"/>
       <c r="B111" s="16"/>
       <c r="X111" s="16"/>
     </row>
-    <row r="112" spans="1:24">
+    <row r="112" spans="1:27">
       <c r="A112" s="16"/>
       <c r="B112" s="16"/>
       <c r="X112" s="16"/>

--- a/japan_studies_problem_list.xlsx
+++ b/japan_studies_problem_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shuum\Desktop\JC復習用アプリ\JC_reviewapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BFAD88-2017-44ED-84E6-46FED092970B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{949B03A1-5967-42BB-B0DE-7A95B498F1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4640,9 +4640,6 @@
     <t>After washing your hands, what are you doing?</t>
   </si>
   <si>
-    <t>lesson07_gargling.jpg</t>
-  </si>
-  <si>
     <t>gargling</t>
   </si>
   <si>
@@ -5237,9 +5234,6 @@
     <t>Eiffel Tower</t>
   </si>
   <si>
-    <t>lesson09_tsutenkaku.jpg</t>
-  </si>
-  <si>
     <t>Tsutenkaku</t>
   </si>
   <si>
@@ -5702,9 +5696,6 @@
     <t>“A sparrow’s tears” is an expression meaning a very small amount.</t>
   </si>
   <si>
-    <t>&lt;ruby&gt;楽器&lt;rt&gt;がっき&lt;/rt&gt;&lt;/ruby&gt;の&lt;ruby&gt;名前&lt;rt&gt;なまえ&lt;/rt&gt;&lt;/ruby&gt;「&lt;ruby&gt;三味線&lt;rt&gt;しゃみせん&lt;/rt&gt;&lt;/ruby&gt;」の&lt;ruby&gt;読&lt;rt&gt;よ&lt;/rt&gt;&lt;/ruby&gt;み&lt;ruby&gt;方&lt;rt&gt;かた&lt;/rt&gt;&lt;/ruby&gt;は、どれですか。</t>
-  </si>
-  <si>
     <t>How do you read the name of the instrument 三味線?</t>
   </si>
   <si>
@@ -5730,9 +5721,6 @@
   </si>
   <si>
     <t>Which one is a tsuzumi hand drum?</t>
-  </si>
-  <si>
-    <t>lesson11_tsuzumi.jpg</t>
   </si>
   <si>
     <t>tsuzumi hand drum</t>
@@ -7508,9 +7496,6 @@
     <t>What kind of companies are Toyota, Nissan, and Mazda?</t>
   </si>
   <si>
-    <t>自動車|自動車会社|車|車の会社|じどうしゃ</t>
-  </si>
-  <si>
     <t>&lt;ruby&gt;化粧品&lt;rt&gt;けしょうひん&lt;/rt&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
@@ -7542,9 +7527,6 @@
   </si>
   <si>
     <t>What kind of companies are Glico, Meiji, and Morinaga?</t>
-  </si>
-  <si>
-    <t>お菓子|菓子|製菓|おかし|お菓子の会社|製菓会社</t>
   </si>
   <si>
     <t>airplanes</t>
@@ -9916,6 +9898,397 @@
   </si>
   <si>
     <t>8-Dec</t>
+  </si>
+  <si>
+    <t>lesson07_gargling.jpg</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>lesson09_tsutenkaku.jpg</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>lesson11_tsuzumi.jpg</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>楽器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>がっき</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>名前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>なまえ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「三味線」の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>読</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>よ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>み</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;rt&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>かた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;/rt&gt;&lt;/ruby&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>は、どれですか。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>自動車</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>自動車会社</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>車</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>車の会社</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>じどうしゃ|くるま</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>お菓子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>菓子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>製菓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>おかし</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>お菓子の会社</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>製菓会社|かし</t>
+    </r>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -14064,10 +14437,10 @@
         <v>1324</v>
       </c>
       <c r="G50" s="74" t="s">
+        <v>1873</v>
+      </c>
+      <c r="H50" s="74" t="s">
         <v>1325</v>
-      </c>
-      <c r="H50" s="74" t="s">
-        <v>1326</v>
       </c>
       <c r="I50" s="74"/>
       <c r="J50" s="74"/>
@@ -14080,34 +14453,34 @@
         <v>1195</v>
       </c>
       <c r="Q50" s="74" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="R50" s="74" t="s">
         <v>1194</v>
       </c>
       <c r="S50" s="74" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="T50" s="74" t="s">
         <v>1196</v>
       </c>
       <c r="U50" s="74" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="V50" s="74" t="s">
         <v>1197</v>
       </c>
       <c r="W50" s="74" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="X50" s="16">
         <v>2</v>
       </c>
       <c r="Y50" s="74" t="s">
+        <v>1329</v>
+      </c>
+      <c r="Z50" s="74" t="s">
         <v>1330</v>
-      </c>
-      <c r="Z50" s="74" t="s">
-        <v>1331</v>
       </c>
       <c r="AA50" s="74"/>
     </row>
@@ -14125,10 +14498,10 @@
         <v>25</v>
       </c>
       <c r="E51" s="74" t="s">
-        <v>1749</v>
+        <v>1745</v>
       </c>
       <c r="F51" s="74" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="G51" s="74"/>
       <c r="H51" s="74"/>
@@ -14139,40 +14512,40 @@
       <c r="M51" s="74"/>
       <c r="N51" s="74"/>
       <c r="O51" s="74" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="P51" s="74" t="s">
         <v>1199</v>
       </c>
       <c r="Q51" s="74" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="R51" s="74" t="s">
         <v>1200</v>
       </c>
       <c r="S51" s="74" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="T51" s="74" t="s">
         <v>1201</v>
       </c>
       <c r="U51" s="74" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="V51" s="74" t="s">
         <v>1202</v>
       </c>
       <c r="W51" s="74" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="X51" s="16">
         <v>3</v>
       </c>
       <c r="Y51" s="74" t="s">
+        <v>1337</v>
+      </c>
+      <c r="Z51" s="74" t="s">
         <v>1338</v>
-      </c>
-      <c r="Z51" s="74" t="s">
-        <v>1339</v>
       </c>
       <c r="AA51" s="74"/>
     </row>
@@ -14190,10 +14563,10 @@
         <v>25</v>
       </c>
       <c r="E52" s="75" t="s">
-        <v>1750</v>
+        <v>1746</v>
       </c>
       <c r="F52" s="74" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="G52" s="74"/>
       <c r="H52" s="74"/>
@@ -14204,40 +14577,40 @@
       <c r="M52" s="74"/>
       <c r="N52" s="74"/>
       <c r="O52" s="74" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="P52" s="74" t="s">
         <v>1204</v>
       </c>
       <c r="Q52" s="74" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="R52" s="74" t="s">
         <v>1205</v>
       </c>
       <c r="S52" s="74" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="T52" s="74" t="s">
         <v>1203</v>
       </c>
       <c r="U52" s="74" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="V52" s="74" t="s">
         <v>286</v>
       </c>
       <c r="W52" s="74" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="X52" s="16">
         <v>3</v>
       </c>
       <c r="Y52" s="74" t="s">
+        <v>1345</v>
+      </c>
+      <c r="Z52" s="74" t="s">
         <v>1346</v>
-      </c>
-      <c r="Z52" s="74" t="s">
-        <v>1347</v>
       </c>
       <c r="AA52" s="74"/>
     </row>
@@ -14255,10 +14628,10 @@
         <v>29</v>
       </c>
       <c r="E53" s="75" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="F53" s="74" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="G53" s="74"/>
       <c r="H53" s="74"/>
@@ -14270,37 +14643,37 @@
       <c r="N53" s="74"/>
       <c r="O53" s="74"/>
       <c r="P53" s="74" t="s">
+        <v>1348</v>
+      </c>
+      <c r="Q53" s="74" t="s">
         <v>1349</v>
       </c>
-      <c r="Q53" s="74" t="s">
+      <c r="R53" s="74" t="s">
         <v>1350</v>
       </c>
-      <c r="R53" s="74" t="s">
+      <c r="S53" s="74" t="s">
         <v>1351</v>
       </c>
-      <c r="S53" s="74" t="s">
+      <c r="T53" s="74" t="s">
         <v>1352</v>
       </c>
-      <c r="T53" s="74" t="s">
+      <c r="U53" s="74" t="s">
         <v>1353</v>
       </c>
-      <c r="U53" s="74" t="s">
+      <c r="V53" s="74" t="s">
         <v>1354</v>
       </c>
-      <c r="V53" s="74" t="s">
+      <c r="W53" s="74" t="s">
         <v>1355</v>
-      </c>
-      <c r="W53" s="74" t="s">
-        <v>1356</v>
       </c>
       <c r="X53" s="16">
         <v>3</v>
       </c>
       <c r="Y53" s="75" t="s">
-        <v>1856</v>
+        <v>1850</v>
       </c>
       <c r="Z53" s="74" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="AA53" s="74"/>
     </row>
@@ -14318,10 +14691,10 @@
         <v>25</v>
       </c>
       <c r="E54" s="75" t="s">
-        <v>1752</v>
+        <v>1748</v>
       </c>
       <c r="F54" s="74" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="G54" s="74"/>
       <c r="H54" s="74"/>
@@ -14332,40 +14705,40 @@
       <c r="M54" s="74"/>
       <c r="N54" s="74"/>
       <c r="O54" s="74" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="P54" s="74" t="s">
         <v>1208</v>
       </c>
       <c r="Q54" s="74" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="R54" s="74" t="s">
         <v>1209</v>
       </c>
       <c r="S54" s="74" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="T54" s="74" t="s">
         <v>1210</v>
       </c>
       <c r="U54" s="74" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="V54" s="74" t="s">
         <v>1211</v>
       </c>
       <c r="W54" s="74" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="X54" s="16">
         <v>4</v>
       </c>
       <c r="Y54" s="74" t="s">
+        <v>1363</v>
+      </c>
+      <c r="Z54" s="74" t="s">
         <v>1364</v>
-      </c>
-      <c r="Z54" s="74" t="s">
-        <v>1365</v>
       </c>
       <c r="AA54" s="74"/>
     </row>
@@ -14383,10 +14756,10 @@
         <v>29</v>
       </c>
       <c r="E55" s="74" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F55" s="74" t="s">
         <v>1366</v>
-      </c>
-      <c r="F55" s="74" t="s">
-        <v>1367</v>
       </c>
       <c r="G55" s="74"/>
       <c r="H55" s="74"/>
@@ -14398,37 +14771,37 @@
       <c r="N55" s="74"/>
       <c r="O55" s="74"/>
       <c r="P55" s="74" t="s">
+        <v>1367</v>
+      </c>
+      <c r="Q55" s="74" t="s">
         <v>1368</v>
       </c>
-      <c r="Q55" s="74" t="s">
+      <c r="R55" s="74" t="s">
         <v>1369</v>
       </c>
-      <c r="R55" s="74" t="s">
+      <c r="S55" s="74" t="s">
         <v>1370</v>
       </c>
-      <c r="S55" s="74" t="s">
+      <c r="T55" s="74" t="s">
         <v>1371</v>
       </c>
-      <c r="T55" s="74" t="s">
+      <c r="U55" s="74" t="s">
         <v>1372</v>
       </c>
-      <c r="U55" s="74" t="s">
+      <c r="V55" s="74" t="s">
         <v>1373</v>
       </c>
-      <c r="V55" s="74" t="s">
+      <c r="W55" s="74" t="s">
         <v>1374</v>
-      </c>
-      <c r="W55" s="74" t="s">
-        <v>1375</v>
       </c>
       <c r="X55" s="16">
         <v>3</v>
       </c>
       <c r="Y55" s="74" t="s">
+        <v>1375</v>
+      </c>
+      <c r="Z55" s="74" t="s">
         <v>1376</v>
-      </c>
-      <c r="Z55" s="74" t="s">
-        <v>1377</v>
       </c>
       <c r="AA55" s="74"/>
     </row>
@@ -14446,10 +14819,10 @@
         <v>25</v>
       </c>
       <c r="E56" s="74" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F56" s="74" t="s">
         <v>1378</v>
-      </c>
-      <c r="F56" s="74" t="s">
-        <v>1379</v>
       </c>
       <c r="G56" s="74"/>
       <c r="H56" s="74"/>
@@ -14460,40 +14833,40 @@
       <c r="M56" s="74"/>
       <c r="N56" s="74"/>
       <c r="O56" s="74" t="s">
+        <v>1379</v>
+      </c>
+      <c r="P56" s="74" t="s">
         <v>1380</v>
       </c>
-      <c r="P56" s="74" t="s">
+      <c r="Q56" s="74" t="s">
         <v>1381</v>
       </c>
-      <c r="Q56" s="74" t="s">
+      <c r="R56" s="74" t="s">
         <v>1382</v>
       </c>
-      <c r="R56" s="74" t="s">
+      <c r="S56" s="74" t="s">
         <v>1383</v>
       </c>
-      <c r="S56" s="74" t="s">
+      <c r="T56" s="74" t="s">
         <v>1384</v>
       </c>
-      <c r="T56" s="74" t="s">
+      <c r="U56" s="74" t="s">
         <v>1385</v>
       </c>
-      <c r="U56" s="74" t="s">
+      <c r="V56" s="74" t="s">
         <v>1386</v>
       </c>
-      <c r="V56" s="74" t="s">
+      <c r="W56" s="74" t="s">
         <v>1387</v>
       </c>
-      <c r="W56" s="74" t="s">
+      <c r="X56" s="16">
+        <v>1</v>
+      </c>
+      <c r="Y56" s="74" t="s">
         <v>1388</v>
       </c>
-      <c r="X56" s="16">
-        <v>1</v>
-      </c>
-      <c r="Y56" s="74" t="s">
+      <c r="Z56" s="74" t="s">
         <v>1389</v>
-      </c>
-      <c r="Z56" s="74" t="s">
-        <v>1390</v>
       </c>
       <c r="AA56" s="74"/>
     </row>
@@ -14511,10 +14884,10 @@
         <v>29</v>
       </c>
       <c r="E57" s="74" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F57" s="74" t="s">
         <v>1391</v>
-      </c>
-      <c r="F57" s="74" t="s">
-        <v>1392</v>
       </c>
       <c r="G57" s="74"/>
       <c r="H57" s="74"/>
@@ -14526,37 +14899,37 @@
       <c r="N57" s="74"/>
       <c r="O57" s="74"/>
       <c r="P57" s="74" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q57" s="74" t="s">
         <v>1393</v>
-      </c>
-      <c r="Q57" s="74" t="s">
-        <v>1394</v>
       </c>
       <c r="R57" s="74" t="s">
         <v>1215</v>
       </c>
       <c r="S57" s="74" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="T57" s="74" t="s">
         <v>1216</v>
       </c>
       <c r="U57" s="74" t="s">
+        <v>1395</v>
+      </c>
+      <c r="V57" s="74" t="s">
         <v>1396</v>
       </c>
-      <c r="V57" s="74" t="s">
+      <c r="W57" s="74" t="s">
         <v>1397</v>
-      </c>
-      <c r="W57" s="74" t="s">
-        <v>1398</v>
       </c>
       <c r="X57" s="16">
         <v>4</v>
       </c>
       <c r="Y57" s="74" t="s">
+        <v>1398</v>
+      </c>
+      <c r="Z57" s="74" t="s">
         <v>1399</v>
-      </c>
-      <c r="Z57" s="74" t="s">
-        <v>1400</v>
       </c>
       <c r="AA57" s="74"/>
     </row>
@@ -14574,68 +14947,68 @@
         <v>27</v>
       </c>
       <c r="E58" s="74" t="s">
+        <v>1400</v>
+      </c>
+      <c r="F58" s="74" t="s">
         <v>1401</v>
       </c>
-      <c r="F58" s="74" t="s">
+      <c r="G58" s="74" t="s">
         <v>1402</v>
       </c>
-      <c r="G58" s="74" t="s">
+      <c r="H58" s="74" t="s">
         <v>1403</v>
       </c>
-      <c r="H58" s="74" t="s">
+      <c r="I58" s="74" t="s">
         <v>1404</v>
       </c>
-      <c r="I58" s="74" t="s">
+      <c r="J58" s="74" t="s">
         <v>1405</v>
       </c>
-      <c r="J58" s="74" t="s">
+      <c r="K58" s="74" t="s">
         <v>1406</v>
       </c>
-      <c r="K58" s="74" t="s">
+      <c r="L58" s="74" t="s">
         <v>1407</v>
       </c>
-      <c r="L58" s="74" t="s">
+      <c r="M58" s="74" t="s">
         <v>1408</v>
       </c>
-      <c r="M58" s="74" t="s">
+      <c r="N58" s="74" t="s">
         <v>1409</v>
-      </c>
-      <c r="N58" s="74" t="s">
-        <v>1410</v>
       </c>
       <c r="O58" s="74"/>
       <c r="P58" s="74" t="s">
+        <v>1410</v>
+      </c>
+      <c r="Q58" s="74" t="s">
+        <v>1403</v>
+      </c>
+      <c r="R58" s="74" t="s">
         <v>1411</v>
       </c>
-      <c r="Q58" s="74" t="s">
-        <v>1404</v>
-      </c>
-      <c r="R58" s="74" t="s">
+      <c r="S58" s="74" t="s">
+        <v>1405</v>
+      </c>
+      <c r="T58" s="74" t="s">
         <v>1412</v>
       </c>
-      <c r="S58" s="74" t="s">
-        <v>1406</v>
-      </c>
-      <c r="T58" s="74" t="s">
+      <c r="U58" s="74" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V58" s="74" t="s">
         <v>1413</v>
       </c>
-      <c r="U58" s="74" t="s">
-        <v>1408</v>
-      </c>
-      <c r="V58" s="74" t="s">
+      <c r="W58" s="74" t="s">
+        <v>1409</v>
+      </c>
+      <c r="X58" s="16">
+        <v>1</v>
+      </c>
+      <c r="Y58" s="74" t="s">
         <v>1414</v>
       </c>
-      <c r="W58" s="74" t="s">
-        <v>1410</v>
-      </c>
-      <c r="X58" s="16">
-        <v>1</v>
-      </c>
-      <c r="Y58" s="74" t="s">
+      <c r="Z58" s="74" t="s">
         <v>1415</v>
-      </c>
-      <c r="Z58" s="74" t="s">
-        <v>1416</v>
       </c>
       <c r="AA58" s="74"/>
     </row>
@@ -14653,10 +15026,10 @@
         <v>25</v>
       </c>
       <c r="E59" s="75" t="s">
-        <v>1753</v>
+        <v>1749</v>
       </c>
       <c r="F59" s="74" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="G59" s="74"/>
       <c r="H59" s="74"/>
@@ -14667,40 +15040,40 @@
       <c r="M59" s="74"/>
       <c r="N59" s="74"/>
       <c r="O59" s="74" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="P59" s="74" t="s">
         <v>1219</v>
       </c>
       <c r="Q59" s="74" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="R59" s="74" t="s">
         <v>1220</v>
       </c>
       <c r="S59" s="74" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="T59" s="74" t="s">
         <v>1221</v>
       </c>
       <c r="U59" s="74" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="V59" s="74" t="s">
         <v>1222</v>
       </c>
       <c r="W59" s="74" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="X59" s="16">
         <v>4</v>
       </c>
       <c r="Y59" s="74" t="s">
+        <v>1422</v>
+      </c>
+      <c r="Z59" s="74" t="s">
         <v>1423</v>
-      </c>
-      <c r="Z59" s="74" t="s">
-        <v>1424</v>
       </c>
       <c r="AA59" s="74"/>
     </row>
@@ -14718,10 +15091,10 @@
         <v>25</v>
       </c>
       <c r="E60" s="74" t="s">
+        <v>1424</v>
+      </c>
+      <c r="F60" s="74" t="s">
         <v>1425</v>
-      </c>
-      <c r="F60" s="74" t="s">
-        <v>1426</v>
       </c>
       <c r="G60" s="74"/>
       <c r="H60" s="74"/>
@@ -14732,40 +15105,40 @@
       <c r="M60" s="74"/>
       <c r="N60" s="74"/>
       <c r="O60" s="75" t="s">
-        <v>1758</v>
+        <v>1754</v>
       </c>
       <c r="P60" s="74" t="s">
+        <v>1426</v>
+      </c>
+      <c r="Q60" s="74" t="s">
         <v>1427</v>
       </c>
-      <c r="Q60" s="74" t="s">
+      <c r="R60" s="74" t="s">
         <v>1428</v>
       </c>
-      <c r="R60" s="74" t="s">
+      <c r="S60" s="74" t="s">
         <v>1429</v>
       </c>
-      <c r="S60" s="74" t="s">
+      <c r="T60" s="74" t="s">
         <v>1430</v>
       </c>
-      <c r="T60" s="74" t="s">
+      <c r="U60" s="74" t="s">
         <v>1431</v>
       </c>
-      <c r="U60" s="74" t="s">
+      <c r="V60" s="74" t="s">
         <v>1432</v>
       </c>
-      <c r="V60" s="74" t="s">
+      <c r="W60" s="74" t="s">
         <v>1433</v>
       </c>
-      <c r="W60" s="74" t="s">
+      <c r="X60" s="16">
+        <v>1</v>
+      </c>
+      <c r="Y60" s="74" t="s">
         <v>1434</v>
       </c>
-      <c r="X60" s="16">
-        <v>1</v>
-      </c>
-      <c r="Y60" s="74" t="s">
+      <c r="Z60" s="74" t="s">
         <v>1435</v>
-      </c>
-      <c r="Z60" s="74" t="s">
-        <v>1436</v>
       </c>
       <c r="AA60" s="74"/>
     </row>
@@ -14783,16 +15156,16 @@
         <v>25</v>
       </c>
       <c r="E61" s="74" t="s">
+        <v>1436</v>
+      </c>
+      <c r="F61" s="74" t="s">
         <v>1437</v>
       </c>
-      <c r="F61" s="74" t="s">
+      <c r="G61" s="74" t="s">
         <v>1438</v>
       </c>
-      <c r="G61" s="74" t="s">
-        <v>1439</v>
-      </c>
       <c r="H61" s="74" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="I61" s="74"/>
       <c r="J61" s="74"/>
@@ -14801,40 +15174,40 @@
       <c r="M61" s="74"/>
       <c r="N61" s="74"/>
       <c r="O61" s="74" t="s">
+        <v>1439</v>
+      </c>
+      <c r="P61" s="74" t="s">
         <v>1440</v>
       </c>
-      <c r="P61" s="74" t="s">
+      <c r="Q61" s="74" t="s">
         <v>1441</v>
-      </c>
-      <c r="Q61" s="74" t="s">
-        <v>1442</v>
       </c>
       <c r="R61" s="74" t="s">
         <v>1216</v>
       </c>
       <c r="S61" s="74" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="T61" s="74" t="s">
         <v>1224</v>
       </c>
       <c r="U61" s="74" t="s">
+        <v>1442</v>
+      </c>
+      <c r="V61" s="74" t="s">
         <v>1443</v>
       </c>
-      <c r="V61" s="74" t="s">
+      <c r="W61" s="74" t="s">
         <v>1444</v>
-      </c>
-      <c r="W61" s="74" t="s">
-        <v>1445</v>
       </c>
       <c r="X61" s="16">
         <v>2</v>
       </c>
       <c r="Y61" s="74" t="s">
+        <v>1445</v>
+      </c>
+      <c r="Z61" s="74" t="s">
         <v>1446</v>
-      </c>
-      <c r="Z61" s="74" t="s">
-        <v>1447</v>
       </c>
       <c r="AA61" s="74"/>
     </row>
@@ -14858,10 +15231,10 @@
         <v>85</v>
       </c>
       <c r="G62" s="74" t="s">
+        <v>1447</v>
+      </c>
+      <c r="H62" s="74" t="s">
         <v>1448</v>
-      </c>
-      <c r="H62" s="74" t="s">
-        <v>1449</v>
       </c>
       <c r="I62" s="74"/>
       <c r="J62" s="74"/>
@@ -14870,40 +15243,40 @@
       <c r="M62" s="74"/>
       <c r="N62" s="74"/>
       <c r="O62" s="74" t="s">
+        <v>1449</v>
+      </c>
+      <c r="P62" s="74" t="s">
         <v>1450</v>
       </c>
-      <c r="P62" s="74" t="s">
+      <c r="Q62" s="74" t="s">
         <v>1451</v>
       </c>
-      <c r="Q62" s="74" t="s">
+      <c r="R62" s="74" t="s">
         <v>1452</v>
       </c>
-      <c r="R62" s="74" t="s">
+      <c r="S62" s="74" t="s">
+        <v>1448</v>
+      </c>
+      <c r="T62" s="74" t="s">
         <v>1453</v>
       </c>
-      <c r="S62" s="74" t="s">
-        <v>1449</v>
-      </c>
-      <c r="T62" s="74" t="s">
+      <c r="U62" s="74" t="s">
         <v>1454</v>
-      </c>
-      <c r="U62" s="74" t="s">
-        <v>1455</v>
       </c>
       <c r="V62" s="74" t="s">
         <v>1215</v>
       </c>
       <c r="W62" s="74" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="X62" s="16">
         <v>2</v>
       </c>
       <c r="Y62" s="74" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Z62" s="74" t="s">
         <v>1456</v>
-      </c>
-      <c r="Z62" s="74" t="s">
-        <v>1457</v>
       </c>
       <c r="AA62" s="74"/>
     </row>
@@ -14921,10 +15294,10 @@
         <v>25</v>
       </c>
       <c r="E63" s="75" t="s">
-        <v>1754</v>
+        <v>1750</v>
       </c>
       <c r="F63" s="74" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G63" s="74"/>
       <c r="H63" s="74"/>
@@ -14935,40 +15308,40 @@
       <c r="M63" s="74"/>
       <c r="N63" s="74"/>
       <c r="O63" s="74" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="P63" s="74" t="s">
         <v>1228</v>
       </c>
       <c r="Q63" s="74" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="R63" s="74" t="s">
         <v>1229</v>
       </c>
       <c r="S63" s="74" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="T63" s="74" t="s">
         <v>1230</v>
       </c>
       <c r="U63" s="74" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="V63" s="74" t="s">
         <v>1231</v>
       </c>
       <c r="W63" s="74" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="X63" s="16">
         <v>3</v>
       </c>
       <c r="Y63" s="75" t="s">
-        <v>1857</v>
+        <v>1851</v>
       </c>
       <c r="Z63" s="74" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="AA63" s="74"/>
     </row>
@@ -14989,7 +15362,7 @@
         <v>1233</v>
       </c>
       <c r="F64" s="74" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G64" s="74"/>
       <c r="H64" s="74"/>
@@ -15001,37 +15374,37 @@
       <c r="N64" s="74"/>
       <c r="O64" s="74"/>
       <c r="P64" s="74" t="s">
+        <v>1465</v>
+      </c>
+      <c r="Q64" s="74" t="s">
         <v>1466</v>
       </c>
-      <c r="Q64" s="74" t="s">
+      <c r="R64" s="74" t="s">
         <v>1467</v>
       </c>
-      <c r="R64" s="74" t="s">
+      <c r="S64" s="74" t="s">
         <v>1468</v>
       </c>
-      <c r="S64" s="74" t="s">
+      <c r="T64" s="74" t="s">
         <v>1469</v>
       </c>
-      <c r="T64" s="74" t="s">
+      <c r="U64" s="74" t="s">
         <v>1470</v>
       </c>
-      <c r="U64" s="74" t="s">
+      <c r="V64" s="74" t="s">
         <v>1471</v>
       </c>
-      <c r="V64" s="74" t="s">
+      <c r="W64" s="74" t="s">
         <v>1472</v>
-      </c>
-      <c r="W64" s="74" t="s">
-        <v>1473</v>
       </c>
       <c r="X64" s="16">
         <v>2</v>
       </c>
       <c r="Y64" s="74" t="s">
+        <v>1473</v>
+      </c>
+      <c r="Z64" s="74" t="s">
         <v>1474</v>
-      </c>
-      <c r="Z64" s="74" t="s">
-        <v>1475</v>
       </c>
       <c r="AA64" s="74"/>
     </row>
@@ -15049,10 +15422,10 @@
         <v>29</v>
       </c>
       <c r="E65" s="74" t="s">
+        <v>1475</v>
+      </c>
+      <c r="F65" s="74" t="s">
         <v>1476</v>
-      </c>
-      <c r="F65" s="74" t="s">
-        <v>1477</v>
       </c>
       <c r="G65" s="74"/>
       <c r="H65" s="74"/>
@@ -15064,37 +15437,37 @@
       <c r="N65" s="74"/>
       <c r="O65" s="74"/>
       <c r="P65" s="74" t="s">
+        <v>1477</v>
+      </c>
+      <c r="Q65" s="74" t="s">
         <v>1478</v>
       </c>
-      <c r="Q65" s="74" t="s">
+      <c r="R65" s="74" t="s">
         <v>1479</v>
       </c>
-      <c r="R65" s="74" t="s">
+      <c r="S65" s="74" t="s">
         <v>1480</v>
       </c>
-      <c r="S65" s="74" t="s">
+      <c r="T65" s="74" t="s">
         <v>1481</v>
       </c>
-      <c r="T65" s="74" t="s">
+      <c r="U65" s="74" t="s">
         <v>1482</v>
       </c>
-      <c r="U65" s="74" t="s">
+      <c r="V65" s="74" t="s">
         <v>1483</v>
       </c>
-      <c r="V65" s="74" t="s">
+      <c r="W65" s="74" t="s">
         <v>1484</v>
-      </c>
-      <c r="W65" s="74" t="s">
-        <v>1485</v>
       </c>
       <c r="X65" s="16">
         <v>2</v>
       </c>
       <c r="Y65" s="74" t="s">
+        <v>1485</v>
+      </c>
+      <c r="Z65" s="74" t="s">
         <v>1486</v>
-      </c>
-      <c r="Z65" s="74" t="s">
-        <v>1487</v>
       </c>
       <c r="AA65" s="74"/>
     </row>
@@ -15112,10 +15485,10 @@
         <v>29</v>
       </c>
       <c r="E66" s="74" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F66" s="74" t="s">
         <v>1488</v>
-      </c>
-      <c r="F66" s="74" t="s">
-        <v>1489</v>
       </c>
       <c r="G66" s="74"/>
       <c r="H66" s="74"/>
@@ -15127,22 +15500,22 @@
       <c r="N66" s="74"/>
       <c r="O66" s="74"/>
       <c r="P66" s="74" t="s">
+        <v>1489</v>
+      </c>
+      <c r="Q66" s="74" t="s">
         <v>1490</v>
       </c>
-      <c r="Q66" s="74" t="s">
+      <c r="R66" s="74" t="s">
         <v>1491</v>
       </c>
-      <c r="R66" s="74" t="s">
+      <c r="S66" s="74" t="s">
         <v>1492</v>
       </c>
-      <c r="S66" s="74" t="s">
+      <c r="T66" s="74" t="s">
         <v>1493</v>
       </c>
-      <c r="T66" s="74" t="s">
+      <c r="U66" s="74" t="s">
         <v>1494</v>
-      </c>
-      <c r="U66" s="74" t="s">
-        <v>1495</v>
       </c>
       <c r="V66" s="74" t="s">
         <v>1058</v>
@@ -15154,10 +15527,10 @@
         <v>3</v>
       </c>
       <c r="Y66" s="74" t="s">
+        <v>1495</v>
+      </c>
+      <c r="Z66" s="74" t="s">
         <v>1496</v>
-      </c>
-      <c r="Z66" s="74" t="s">
-        <v>1497</v>
       </c>
       <c r="AA66" s="74"/>
     </row>
@@ -15175,10 +15548,10 @@
         <v>25</v>
       </c>
       <c r="E67" s="75" t="s">
-        <v>1755</v>
+        <v>1751</v>
       </c>
       <c r="F67" s="74" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="G67" s="74"/>
       <c r="H67" s="74"/>
@@ -15189,40 +15562,40 @@
       <c r="M67" s="74"/>
       <c r="N67" s="74"/>
       <c r="O67" s="74" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="P67" s="74" t="s">
         <v>1236</v>
       </c>
       <c r="Q67" s="74" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="R67" s="74" t="s">
         <v>1237</v>
       </c>
       <c r="S67" s="74" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="T67" s="74" t="s">
         <v>1238</v>
       </c>
       <c r="U67" s="74" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="V67" s="74" t="s">
         <v>1239</v>
       </c>
       <c r="W67" s="74" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="X67" s="16">
         <v>2</v>
       </c>
       <c r="Y67" s="75" t="s">
-        <v>1858</v>
+        <v>1852</v>
       </c>
       <c r="Z67" s="74" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="AA67" s="74"/>
     </row>
@@ -15240,16 +15613,16 @@
         <v>25</v>
       </c>
       <c r="E68" s="74" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F68" s="74" t="s">
         <v>1505</v>
       </c>
-      <c r="F68" s="74" t="s">
+      <c r="G68" s="74" t="s">
         <v>1506</v>
       </c>
-      <c r="G68" s="74" t="s">
+      <c r="H68" s="74" t="s">
         <v>1507</v>
-      </c>
-      <c r="H68" s="74" t="s">
-        <v>1508</v>
       </c>
       <c r="I68" s="74"/>
       <c r="J68" s="74"/>
@@ -15258,40 +15631,40 @@
       <c r="M68" s="74"/>
       <c r="N68" s="74"/>
       <c r="O68" s="74" t="s">
+        <v>1508</v>
+      </c>
+      <c r="P68" s="74" t="s">
         <v>1509</v>
       </c>
-      <c r="P68" s="74" t="s">
+      <c r="Q68" s="74" t="s">
         <v>1510</v>
       </c>
-      <c r="Q68" s="74" t="s">
+      <c r="R68" s="74" t="s">
         <v>1511</v>
       </c>
-      <c r="R68" s="74" t="s">
+      <c r="S68" s="74" t="s">
         <v>1512</v>
       </c>
-      <c r="S68" s="74" t="s">
+      <c r="T68" s="74" t="s">
         <v>1513</v>
       </c>
-      <c r="T68" s="74" t="s">
+      <c r="U68" s="74" t="s">
+        <v>1507</v>
+      </c>
+      <c r="V68" s="74" t="s">
         <v>1514</v>
       </c>
-      <c r="U68" s="74" t="s">
-        <v>1508</v>
-      </c>
-      <c r="V68" s="74" t="s">
+      <c r="W68" s="74" t="s">
         <v>1515</v>
-      </c>
-      <c r="W68" s="74" t="s">
-        <v>1516</v>
       </c>
       <c r="X68" s="16">
         <v>3</v>
       </c>
       <c r="Y68" s="75" t="s">
-        <v>1859</v>
+        <v>1853</v>
       </c>
       <c r="Z68" s="74" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="AA68" s="74"/>
     </row>
@@ -15309,68 +15682,68 @@
         <v>27</v>
       </c>
       <c r="E69" s="74" t="s">
+        <v>1517</v>
+      </c>
+      <c r="F69" s="74" t="s">
         <v>1518</v>
       </c>
-      <c r="F69" s="74" t="s">
+      <c r="G69" s="74" t="s">
         <v>1519</v>
       </c>
-      <c r="G69" s="74" t="s">
+      <c r="H69" s="74" t="s">
         <v>1520</v>
       </c>
-      <c r="H69" s="74" t="s">
+      <c r="I69" s="74" t="s">
         <v>1521</v>
       </c>
-      <c r="I69" s="74" t="s">
+      <c r="J69" s="74" t="s">
         <v>1522</v>
       </c>
-      <c r="J69" s="74" t="s">
+      <c r="K69" s="74" t="s">
+        <v>1874</v>
+      </c>
+      <c r="L69" s="74" t="s">
         <v>1523</v>
       </c>
-      <c r="K69" s="74" t="s">
+      <c r="M69" s="74" t="s">
         <v>1524</v>
       </c>
-      <c r="L69" s="74" t="s">
+      <c r="N69" s="74" t="s">
         <v>1525</v>
-      </c>
-      <c r="M69" s="74" t="s">
-        <v>1526</v>
-      </c>
-      <c r="N69" s="74" t="s">
-        <v>1527</v>
       </c>
       <c r="O69" s="74"/>
       <c r="P69" s="74" t="s">
+        <v>1526</v>
+      </c>
+      <c r="Q69" s="74" t="s">
+        <v>1520</v>
+      </c>
+      <c r="R69" s="74" t="s">
+        <v>1527</v>
+      </c>
+      <c r="S69" s="74" t="s">
+        <v>1522</v>
+      </c>
+      <c r="T69" s="74" t="s">
         <v>1528</v>
       </c>
-      <c r="Q69" s="74" t="s">
-        <v>1521</v>
-      </c>
-      <c r="R69" s="74" t="s">
+      <c r="U69" s="74" t="s">
+        <v>1523</v>
+      </c>
+      <c r="V69" s="74" t="s">
         <v>1529</v>
       </c>
-      <c r="S69" s="74" t="s">
-        <v>1523</v>
-      </c>
-      <c r="T69" s="74" t="s">
-        <v>1530</v>
-      </c>
-      <c r="U69" s="74" t="s">
+      <c r="W69" s="74" t="s">
         <v>1525</v>
-      </c>
-      <c r="V69" s="74" t="s">
-        <v>1531</v>
-      </c>
-      <c r="W69" s="74" t="s">
-        <v>1527</v>
       </c>
       <c r="X69" s="16">
         <v>3</v>
       </c>
       <c r="Y69" s="74" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="Z69" s="74" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="AA69" s="74"/>
     </row>
@@ -15388,10 +15761,10 @@
         <v>25</v>
       </c>
       <c r="E70" s="75" t="s">
-        <v>1756</v>
+        <v>1752</v>
       </c>
       <c r="F70" s="74" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="G70" s="74"/>
       <c r="H70" s="74"/>
@@ -15402,40 +15775,40 @@
       <c r="M70" s="74"/>
       <c r="N70" s="74"/>
       <c r="O70" s="74" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="P70" s="74" t="s">
         <v>1243</v>
       </c>
       <c r="Q70" s="74" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="R70" s="74" t="s">
         <v>1244</v>
       </c>
       <c r="S70" s="74" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="T70" s="74" t="s">
         <v>1245</v>
       </c>
       <c r="U70" s="74" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="V70" s="74" t="s">
         <v>1246</v>
       </c>
       <c r="W70" s="74" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="X70" s="16">
         <v>3</v>
       </c>
       <c r="Y70" s="75" t="s">
-        <v>1860</v>
+        <v>1854</v>
       </c>
       <c r="Z70" s="74" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="AA70" s="74"/>
     </row>
@@ -15453,10 +15826,10 @@
         <v>29</v>
       </c>
       <c r="E71" s="74" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="F71" s="74" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="G71" s="74"/>
       <c r="H71" s="74"/>
@@ -15468,37 +15841,37 @@
       <c r="N71" s="74"/>
       <c r="O71" s="74"/>
       <c r="P71" s="74" t="s">
+        <v>1541</v>
+      </c>
+      <c r="Q71" s="74" t="s">
+        <v>1542</v>
+      </c>
+      <c r="R71" s="74" t="s">
         <v>1543</v>
       </c>
-      <c r="Q71" s="74" t="s">
+      <c r="S71" s="74" t="s">
         <v>1544</v>
       </c>
-      <c r="R71" s="74" t="s">
+      <c r="T71" s="74" t="s">
         <v>1545</v>
       </c>
-      <c r="S71" s="74" t="s">
+      <c r="U71" s="74" t="s">
         <v>1546</v>
       </c>
-      <c r="T71" s="74" t="s">
+      <c r="V71" s="74" t="s">
         <v>1547</v>
       </c>
-      <c r="U71" s="74" t="s">
+      <c r="W71" s="74" t="s">
         <v>1548</v>
-      </c>
-      <c r="V71" s="74" t="s">
-        <v>1549</v>
-      </c>
-      <c r="W71" s="74" t="s">
-        <v>1550</v>
       </c>
       <c r="X71" s="16">
         <v>4</v>
       </c>
       <c r="Y71" s="74" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="Z71" s="74" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="AA71" s="74"/>
     </row>
@@ -15516,10 +15889,10 @@
         <v>25</v>
       </c>
       <c r="E72" s="75" t="s">
-        <v>1757</v>
+        <v>1753</v>
       </c>
       <c r="F72" s="74" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="G72" s="74"/>
       <c r="H72" s="74"/>
@@ -15530,40 +15903,40 @@
       <c r="M72" s="74"/>
       <c r="N72" s="74"/>
       <c r="O72" s="74" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="P72" s="74" t="s">
         <v>1249</v>
       </c>
       <c r="Q72" s="74" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="R72" s="74" t="s">
         <v>1250</v>
       </c>
       <c r="S72" s="74" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="T72" s="74" t="s">
         <v>1251</v>
       </c>
       <c r="U72" s="74" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="V72" s="74" t="s">
         <v>1252</v>
       </c>
       <c r="W72" s="74" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="X72" s="16">
         <v>4</v>
       </c>
       <c r="Y72" s="75" t="s">
-        <v>1861</v>
+        <v>1855</v>
       </c>
       <c r="Z72" s="74" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="AA72" s="74"/>
     </row>
@@ -15587,10 +15960,10 @@
         <v>85</v>
       </c>
       <c r="G73" s="74" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="H73" s="74" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="I73" s="74"/>
       <c r="J73" s="74"/>
@@ -15599,40 +15972,40 @@
       <c r="M73" s="74"/>
       <c r="N73" s="74"/>
       <c r="O73" s="74" t="s">
+        <v>1560</v>
+      </c>
+      <c r="P73" s="74" t="s">
+        <v>1561</v>
+      </c>
+      <c r="Q73" s="74" t="s">
         <v>1562</v>
       </c>
-      <c r="P73" s="74" t="s">
+      <c r="R73" s="74" t="s">
         <v>1563</v>
       </c>
-      <c r="Q73" s="74" t="s">
+      <c r="S73" s="74" t="s">
         <v>1564</v>
       </c>
-      <c r="R73" s="74" t="s">
+      <c r="T73" s="74" t="s">
         <v>1565</v>
       </c>
-      <c r="S73" s="74" t="s">
+      <c r="U73" s="74" t="s">
         <v>1566</v>
       </c>
-      <c r="T73" s="74" t="s">
+      <c r="V73" s="74" t="s">
         <v>1567</v>
       </c>
-      <c r="U73" s="74" t="s">
-        <v>1568</v>
-      </c>
-      <c r="V73" s="74" t="s">
-        <v>1569</v>
-      </c>
       <c r="W73" s="74" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="X73" s="16">
         <v>4</v>
       </c>
       <c r="Y73" s="74" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="Z73" s="74" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="AA73" s="74"/>
     </row>
@@ -15650,10 +16023,10 @@
         <v>29</v>
       </c>
       <c r="E74" s="74" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="F74" s="74" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="G74" s="74"/>
       <c r="H74" s="74"/>
@@ -15671,31 +16044,31 @@
         <v>296</v>
       </c>
       <c r="R74" s="74" t="s">
+        <v>1572</v>
+      </c>
+      <c r="S74" s="74" t="s">
+        <v>1573</v>
+      </c>
+      <c r="T74" s="74" t="s">
         <v>1574</v>
       </c>
-      <c r="S74" s="74" t="s">
+      <c r="U74" s="74" t="s">
         <v>1575</v>
       </c>
-      <c r="T74" s="74" t="s">
+      <c r="V74" s="74" t="s">
         <v>1576</v>
       </c>
-      <c r="U74" s="74" t="s">
+      <c r="W74" s="74" t="s">
         <v>1577</v>
-      </c>
-      <c r="V74" s="74" t="s">
-        <v>1578</v>
-      </c>
-      <c r="W74" s="74" t="s">
-        <v>1579</v>
       </c>
       <c r="X74" s="16">
         <v>4</v>
       </c>
       <c r="Y74" s="74" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="Z74" s="74" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="AA74" s="74"/>
     </row>
@@ -15713,10 +16086,10 @@
         <v>29</v>
       </c>
       <c r="E75" s="74" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="F75" s="74" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="G75" s="74"/>
       <c r="H75" s="74"/>
@@ -15728,37 +16101,37 @@
       <c r="N75" s="74"/>
       <c r="O75" s="74"/>
       <c r="P75" s="74" t="s">
+        <v>1582</v>
+      </c>
+      <c r="Q75" s="74" t="s">
+        <v>1583</v>
+      </c>
+      <c r="R75" s="74" t="s">
         <v>1584</v>
       </c>
-      <c r="Q75" s="74" t="s">
+      <c r="S75" s="74" t="s">
         <v>1585</v>
       </c>
-      <c r="R75" s="74" t="s">
+      <c r="T75" s="74" t="s">
         <v>1586</v>
       </c>
-      <c r="S75" s="74" t="s">
+      <c r="U75" s="74" t="s">
         <v>1587</v>
       </c>
-      <c r="T75" s="74" t="s">
+      <c r="V75" s="74" t="s">
         <v>1588</v>
       </c>
-      <c r="U75" s="74" t="s">
+      <c r="W75" s="74" t="s">
         <v>1589</v>
-      </c>
-      <c r="V75" s="74" t="s">
-        <v>1590</v>
-      </c>
-      <c r="W75" s="74" t="s">
-        <v>1591</v>
       </c>
       <c r="X75" s="16">
         <v>3</v>
       </c>
       <c r="Y75" s="74" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="Z75" s="74" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="AA75" s="74"/>
     </row>
@@ -15782,10 +16155,10 @@
         <v>85</v>
       </c>
       <c r="G76" s="74" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="H76" s="74" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="I76" s="74"/>
       <c r="J76" s="74"/>
@@ -15794,40 +16167,40 @@
       <c r="M76" s="74"/>
       <c r="N76" s="74"/>
       <c r="O76" s="74" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="P76" s="74" t="s">
         <v>1257</v>
       </c>
       <c r="Q76" s="74" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="R76" s="74" t="s">
         <v>1258</v>
       </c>
       <c r="S76" s="74" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="T76" s="74" t="s">
         <v>1259</v>
       </c>
       <c r="U76" s="74" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="V76" s="74" t="s">
         <v>1256</v>
       </c>
       <c r="W76" s="74" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="X76" s="16">
         <v>4</v>
       </c>
       <c r="Y76" s="74" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="Z76" s="74" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="AA76" s="74"/>
     </row>
@@ -15851,10 +16224,10 @@
         <v>85</v>
       </c>
       <c r="G77" s="74" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="H77" s="74" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="I77" s="74"/>
       <c r="J77" s="74"/>
@@ -15863,7 +16236,7 @@
       <c r="M77" s="74"/>
       <c r="N77" s="74"/>
       <c r="O77" s="74" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="P77" s="74" t="s">
         <v>1261</v>
@@ -15881,22 +16254,22 @@
         <v>1260</v>
       </c>
       <c r="U77" s="74" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="V77" s="74" t="s">
         <v>1262</v>
       </c>
       <c r="W77" s="74" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="X77" s="16">
         <v>3</v>
       </c>
       <c r="Y77" s="74" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="Z77" s="74" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="AA77" s="74"/>
     </row>
@@ -15914,16 +16287,16 @@
         <v>25</v>
       </c>
       <c r="E78" s="74" t="s">
+        <v>1606</v>
+      </c>
+      <c r="F78" s="74" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G78" s="74" t="s">
         <v>1608</v>
       </c>
-      <c r="F78" s="74" t="s">
+      <c r="H78" s="74" t="s">
         <v>1609</v>
-      </c>
-      <c r="G78" s="74" t="s">
-        <v>1610</v>
-      </c>
-      <c r="H78" s="74" t="s">
-        <v>1611</v>
       </c>
       <c r="I78" s="74"/>
       <c r="J78" s="74"/>
@@ -15932,25 +16305,25 @@
       <c r="M78" s="74"/>
       <c r="N78" s="74"/>
       <c r="O78" s="74" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="P78" s="74" t="s">
         <v>1263</v>
       </c>
       <c r="Q78" s="74" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="R78" s="74" t="s">
         <v>1264</v>
       </c>
       <c r="S78" s="74" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="T78" s="74" t="s">
         <v>1265</v>
       </c>
       <c r="U78" s="74" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="V78" s="74" t="s">
         <v>940</v>
@@ -15962,10 +16335,10 @@
         <v>1</v>
       </c>
       <c r="Y78" s="74" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="Z78" s="74" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="AA78" s="74"/>
     </row>
@@ -15983,10 +16356,10 @@
         <v>25</v>
       </c>
       <c r="E79" s="74" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="F79" s="74" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="G79" s="74"/>
       <c r="H79" s="74"/>
@@ -15997,40 +16370,40 @@
       <c r="M79" s="74"/>
       <c r="N79" s="74"/>
       <c r="O79" s="74" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="P79" s="74" t="s">
         <v>1264</v>
       </c>
       <c r="Q79" s="74" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="R79" s="74" t="s">
         <v>1266</v>
       </c>
       <c r="S79" s="74" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="T79" s="74" t="s">
         <v>1267</v>
       </c>
       <c r="U79" s="74" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="V79" s="74" t="s">
         <v>1268</v>
       </c>
       <c r="W79" s="74" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="X79" s="16">
         <v>2</v>
       </c>
       <c r="Y79" s="74" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="Z79" s="74" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="AA79" s="74"/>
     </row>
@@ -16048,10 +16421,10 @@
         <v>29</v>
       </c>
       <c r="E80" s="74" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="F80" s="74" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="G80" s="74"/>
       <c r="H80" s="74"/>
@@ -16066,34 +16439,34 @@
         <v>1270</v>
       </c>
       <c r="Q80" s="74" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="R80" s="74" t="s">
         <v>1271</v>
       </c>
       <c r="S80" s="74" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="T80" s="74" t="s">
         <v>1272</v>
       </c>
       <c r="U80" s="74" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="V80" s="74" t="s">
         <v>1269</v>
       </c>
       <c r="W80" s="74" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="X80" s="16">
         <v>4</v>
       </c>
       <c r="Y80" s="74" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="Z80" s="74" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="AA80" s="74"/>
     </row>
@@ -16111,10 +16484,10 @@
         <v>29</v>
       </c>
       <c r="E81" s="74" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="F81" s="74" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="G81" s="74"/>
       <c r="H81" s="74"/>
@@ -16126,37 +16499,37 @@
       <c r="N81" s="74"/>
       <c r="O81" s="74"/>
       <c r="P81" s="74" t="s">
+        <v>1634</v>
+      </c>
+      <c r="Q81" s="74" t="s">
+        <v>1635</v>
+      </c>
+      <c r="R81" s="74" t="s">
         <v>1636</v>
       </c>
-      <c r="Q81" s="74" t="s">
+      <c r="S81" s="74" t="s">
         <v>1637</v>
       </c>
-      <c r="R81" s="74" t="s">
+      <c r="T81" s="74" t="s">
         <v>1638</v>
       </c>
-      <c r="S81" s="74" t="s">
+      <c r="U81" s="74" t="s">
         <v>1639</v>
       </c>
-      <c r="T81" s="74" t="s">
+      <c r="V81" s="74" t="s">
         <v>1640</v>
       </c>
-      <c r="U81" s="74" t="s">
+      <c r="W81" s="74" t="s">
         <v>1641</v>
-      </c>
-      <c r="V81" s="74" t="s">
-        <v>1642</v>
-      </c>
-      <c r="W81" s="74" t="s">
-        <v>1643</v>
       </c>
       <c r="X81" s="16">
         <v>3</v>
       </c>
       <c r="Y81" s="74" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="Z81" s="74" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="AA81" s="74"/>
     </row>
@@ -16174,10 +16547,10 @@
         <v>29</v>
       </c>
       <c r="E82" s="74" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="F82" s="74" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="G82" s="74"/>
       <c r="H82" s="74"/>
@@ -16189,37 +16562,37 @@
       <c r="N82" s="74"/>
       <c r="O82" s="74"/>
       <c r="P82" s="74" t="s">
+        <v>1646</v>
+      </c>
+      <c r="Q82" s="74" t="s">
+        <v>1647</v>
+      </c>
+      <c r="R82" s="74" t="s">
         <v>1648</v>
       </c>
-      <c r="Q82" s="74" t="s">
+      <c r="S82" s="74" t="s">
         <v>1649</v>
       </c>
-      <c r="R82" s="74" t="s">
+      <c r="T82" s="74" t="s">
         <v>1650</v>
       </c>
-      <c r="S82" s="74" t="s">
+      <c r="U82" s="74" t="s">
         <v>1651</v>
       </c>
-      <c r="T82" s="74" t="s">
+      <c r="V82" s="74" t="s">
         <v>1652</v>
       </c>
-      <c r="U82" s="74" t="s">
+      <c r="W82" s="74" t="s">
         <v>1653</v>
-      </c>
-      <c r="V82" s="74" t="s">
-        <v>1654</v>
-      </c>
-      <c r="W82" s="74" t="s">
-        <v>1655</v>
       </c>
       <c r="X82" s="16">
         <v>3</v>
       </c>
       <c r="Y82" s="74" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="Z82" s="74" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="AA82" s="74"/>
     </row>
@@ -16237,10 +16610,10 @@
         <v>25</v>
       </c>
       <c r="E83" s="74" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="F83" s="74" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="G83" s="74"/>
       <c r="H83" s="74"/>
@@ -16251,40 +16624,40 @@
       <c r="M83" s="74"/>
       <c r="N83" s="74"/>
       <c r="O83" s="74" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="P83" s="74" t="s">
         <v>1276</v>
       </c>
       <c r="Q83" s="74" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="R83" s="74" t="s">
         <v>1277</v>
       </c>
       <c r="S83" s="74" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="T83" s="74" t="s">
         <v>1278</v>
       </c>
       <c r="U83" s="74" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="V83" s="74" t="s">
         <v>1275</v>
       </c>
       <c r="W83" s="74" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="X83" s="16">
         <v>4</v>
       </c>
       <c r="Y83" s="74" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="Z83" s="74" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="AA83" s="74"/>
     </row>
@@ -16302,10 +16675,10 @@
         <v>29</v>
       </c>
       <c r="E84" s="74" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="F84" s="74" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="G84" s="74"/>
       <c r="H84" s="74"/>
@@ -16317,37 +16690,37 @@
       <c r="N84" s="74"/>
       <c r="O84" s="74"/>
       <c r="P84" s="74" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Q84" s="74" t="s">
+        <v>1668</v>
+      </c>
+      <c r="R84" s="74" t="s">
         <v>1669</v>
       </c>
-      <c r="Q84" s="74" t="s">
+      <c r="S84" s="74" t="s">
         <v>1670</v>
       </c>
-      <c r="R84" s="74" t="s">
+      <c r="T84" s="74" t="s">
         <v>1671</v>
       </c>
-      <c r="S84" s="74" t="s">
+      <c r="U84" s="74" t="s">
         <v>1672</v>
       </c>
-      <c r="T84" s="74" t="s">
+      <c r="V84" s="74" t="s">
         <v>1673</v>
       </c>
-      <c r="U84" s="74" t="s">
+      <c r="W84" s="74" t="s">
         <v>1674</v>
-      </c>
-      <c r="V84" s="74" t="s">
-        <v>1675</v>
-      </c>
-      <c r="W84" s="74" t="s">
-        <v>1676</v>
       </c>
       <c r="X84" s="16">
         <v>3</v>
       </c>
       <c r="Y84" s="74" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="Z84" s="74" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="AA84" s="74"/>
     </row>
@@ -16365,10 +16738,10 @@
         <v>25</v>
       </c>
       <c r="E85" s="74" t="s">
-        <v>1679</v>
+        <v>1876</v>
       </c>
       <c r="F85" s="74" t="s">
-        <v>1680</v>
+        <v>1677</v>
       </c>
       <c r="G85" s="74"/>
       <c r="H85" s="74"/>
@@ -16379,40 +16752,40 @@
       <c r="M85" s="74"/>
       <c r="N85" s="74"/>
       <c r="O85" s="74" t="s">
-        <v>1681</v>
+        <v>1678</v>
       </c>
       <c r="P85" s="74" t="s">
         <v>1281</v>
       </c>
       <c r="Q85" s="74" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
       <c r="R85" s="74" t="s">
         <v>1282</v>
       </c>
       <c r="S85" s="74" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
       <c r="T85" s="74" t="s">
         <v>1283</v>
       </c>
       <c r="U85" s="74" t="s">
-        <v>1684</v>
+        <v>1681</v>
       </c>
       <c r="V85" s="74" t="s">
         <v>1284</v>
       </c>
       <c r="W85" s="74" t="s">
-        <v>1685</v>
+        <v>1682</v>
       </c>
       <c r="X85" s="16">
         <v>4</v>
       </c>
       <c r="Y85" s="75" t="s">
-        <v>1862</v>
+        <v>1856</v>
       </c>
       <c r="Z85" s="74" t="s">
-        <v>1686</v>
+        <v>1683</v>
       </c>
       <c r="AA85" s="74"/>
     </row>
@@ -16430,68 +16803,68 @@
         <v>27</v>
       </c>
       <c r="E86" s="74" t="s">
+        <v>1684</v>
+      </c>
+      <c r="F86" s="74" t="s">
+        <v>1685</v>
+      </c>
+      <c r="G86" s="74" t="s">
+        <v>1875</v>
+      </c>
+      <c r="H86" s="74" t="s">
+        <v>1686</v>
+      </c>
+      <c r="I86" s="74" t="s">
         <v>1687</v>
       </c>
-      <c r="F86" s="74" t="s">
+      <c r="J86" s="74" t="s">
         <v>1688</v>
       </c>
-      <c r="G86" s="74" t="s">
+      <c r="K86" s="74" t="s">
         <v>1689</v>
       </c>
-      <c r="H86" s="74" t="s">
+      <c r="L86" s="74" t="s">
+        <v>1682</v>
+      </c>
+      <c r="M86" s="74" t="s">
         <v>1690</v>
       </c>
-      <c r="I86" s="74" t="s">
+      <c r="N86" s="74" t="s">
         <v>1691</v>
-      </c>
-      <c r="J86" s="74" t="s">
-        <v>1692</v>
-      </c>
-      <c r="K86" s="74" t="s">
-        <v>1693</v>
-      </c>
-      <c r="L86" s="74" t="s">
-        <v>1685</v>
-      </c>
-      <c r="M86" s="74" t="s">
-        <v>1694</v>
-      </c>
-      <c r="N86" s="74" t="s">
-        <v>1695</v>
       </c>
       <c r="O86" s="74"/>
       <c r="P86" s="74" t="s">
+        <v>1692</v>
+      </c>
+      <c r="Q86" s="74" t="s">
+        <v>1686</v>
+      </c>
+      <c r="R86" s="74" t="s">
+        <v>1693</v>
+      </c>
+      <c r="S86" s="74" t="s">
+        <v>1688</v>
+      </c>
+      <c r="T86" s="74" t="s">
+        <v>1694</v>
+      </c>
+      <c r="U86" s="74" t="s">
+        <v>1682</v>
+      </c>
+      <c r="V86" s="74" t="s">
+        <v>1695</v>
+      </c>
+      <c r="W86" s="74" t="s">
         <v>1696</v>
       </c>
-      <c r="Q86" s="74" t="s">
-        <v>1690</v>
-      </c>
-      <c r="R86" s="74" t="s">
+      <c r="X86" s="16">
+        <v>1</v>
+      </c>
+      <c r="Y86" s="74" t="s">
         <v>1697</v>
       </c>
-      <c r="S86" s="74" t="s">
-        <v>1692</v>
-      </c>
-      <c r="T86" s="74" t="s">
+      <c r="Z86" s="74" t="s">
         <v>1698</v>
-      </c>
-      <c r="U86" s="74" t="s">
-        <v>1685</v>
-      </c>
-      <c r="V86" s="74" t="s">
-        <v>1699</v>
-      </c>
-      <c r="W86" s="74" t="s">
-        <v>1700</v>
-      </c>
-      <c r="X86" s="16">
-        <v>1</v>
-      </c>
-      <c r="Y86" s="74" t="s">
-        <v>1701</v>
-      </c>
-      <c r="Z86" s="74" t="s">
-        <v>1702</v>
       </c>
       <c r="AA86" s="74"/>
     </row>
@@ -16509,68 +16882,68 @@
         <v>27</v>
       </c>
       <c r="E87" s="74" t="s">
+        <v>1699</v>
+      </c>
+      <c r="F87" s="74" t="s">
+        <v>1700</v>
+      </c>
+      <c r="G87" s="74" t="s">
+        <v>1701</v>
+      </c>
+      <c r="H87" s="74" t="s">
+        <v>1702</v>
+      </c>
+      <c r="I87" s="74" t="s">
         <v>1703</v>
       </c>
-      <c r="F87" s="74" t="s">
+      <c r="J87" s="74" t="s">
         <v>1704</v>
       </c>
-      <c r="G87" s="74" t="s">
+      <c r="K87" s="74" t="s">
         <v>1705</v>
       </c>
-      <c r="H87" s="74" t="s">
+      <c r="L87" s="74" t="s">
         <v>1706</v>
       </c>
-      <c r="I87" s="74" t="s">
+      <c r="M87" s="74" t="s">
         <v>1707</v>
       </c>
-      <c r="J87" s="74" t="s">
+      <c r="N87" s="74" t="s">
         <v>1708</v>
-      </c>
-      <c r="K87" s="74" t="s">
-        <v>1709</v>
-      </c>
-      <c r="L87" s="74" t="s">
-        <v>1710</v>
-      </c>
-      <c r="M87" s="74" t="s">
-        <v>1711</v>
-      </c>
-      <c r="N87" s="74" t="s">
-        <v>1712</v>
       </c>
       <c r="O87" s="74"/>
       <c r="P87" s="74" t="s">
-        <v>1713</v>
+        <v>1709</v>
       </c>
       <c r="Q87" s="74" t="s">
+        <v>1702</v>
+      </c>
+      <c r="R87" s="74" t="s">
+        <v>1710</v>
+      </c>
+      <c r="S87" s="74" t="s">
+        <v>1704</v>
+      </c>
+      <c r="T87" s="74" t="s">
+        <v>1711</v>
+      </c>
+      <c r="U87" s="74" t="s">
         <v>1706</v>
       </c>
-      <c r="R87" s="74" t="s">
-        <v>1714</v>
-      </c>
-      <c r="S87" s="74" t="s">
+      <c r="V87" s="74" t="s">
+        <v>1712</v>
+      </c>
+      <c r="W87" s="74" t="s">
         <v>1708</v>
-      </c>
-      <c r="T87" s="74" t="s">
-        <v>1715</v>
-      </c>
-      <c r="U87" s="74" t="s">
-        <v>1710</v>
-      </c>
-      <c r="V87" s="74" t="s">
-        <v>1716</v>
-      </c>
-      <c r="W87" s="74" t="s">
-        <v>1712</v>
       </c>
       <c r="X87" s="16">
         <v>4</v>
       </c>
       <c r="Y87" s="74" t="s">
-        <v>1717</v>
+        <v>1713</v>
       </c>
       <c r="Z87" s="74" t="s">
-        <v>1718</v>
+        <v>1714</v>
       </c>
       <c r="AA87" s="74"/>
     </row>
@@ -16588,10 +16961,10 @@
         <v>25</v>
       </c>
       <c r="E88" s="74" t="s">
-        <v>1719</v>
+        <v>1715</v>
       </c>
       <c r="F88" s="74" t="s">
-        <v>1720</v>
+        <v>1716</v>
       </c>
       <c r="G88" s="74"/>
       <c r="H88" s="74"/>
@@ -16602,40 +16975,40 @@
       <c r="M88" s="74"/>
       <c r="N88" s="74"/>
       <c r="O88" s="74" t="s">
-        <v>1721</v>
+        <v>1717</v>
       </c>
       <c r="P88" s="74" t="s">
         <v>162</v>
       </c>
       <c r="Q88" s="74" t="s">
-        <v>1722</v>
+        <v>1718</v>
       </c>
       <c r="R88" s="74" t="s">
         <v>1288</v>
       </c>
       <c r="S88" s="74" t="s">
+        <v>1719</v>
+      </c>
+      <c r="T88" s="74" t="s">
+        <v>1720</v>
+      </c>
+      <c r="U88" s="74" t="s">
+        <v>1721</v>
+      </c>
+      <c r="V88" s="74" t="s">
+        <v>1722</v>
+      </c>
+      <c r="W88" s="74" t="s">
         <v>1723</v>
-      </c>
-      <c r="T88" s="74" t="s">
-        <v>1724</v>
-      </c>
-      <c r="U88" s="74" t="s">
-        <v>1725</v>
-      </c>
-      <c r="V88" s="74" t="s">
-        <v>1726</v>
-      </c>
-      <c r="W88" s="74" t="s">
-        <v>1727</v>
       </c>
       <c r="X88" s="16">
         <v>3</v>
       </c>
       <c r="Y88" s="74" t="s">
-        <v>1728</v>
+        <v>1724</v>
       </c>
       <c r="Z88" s="74" t="s">
-        <v>1729</v>
+        <v>1725</v>
       </c>
       <c r="AA88" s="74"/>
     </row>
@@ -16653,16 +17026,16 @@
         <v>25</v>
       </c>
       <c r="E89" s="74" t="s">
-        <v>1730</v>
+        <v>1726</v>
       </c>
       <c r="F89" s="74" t="s">
-        <v>1731</v>
+        <v>1727</v>
       </c>
       <c r="G89" s="74" t="s">
-        <v>1732</v>
+        <v>1728</v>
       </c>
       <c r="H89" s="74" t="s">
-        <v>1733</v>
+        <v>1729</v>
       </c>
       <c r="I89" s="74"/>
       <c r="J89" s="74"/>
@@ -16671,40 +17044,40 @@
       <c r="M89" s="74"/>
       <c r="N89" s="74"/>
       <c r="O89" s="74" t="s">
-        <v>1734</v>
+        <v>1730</v>
       </c>
       <c r="P89" s="74" t="s">
         <v>1290</v>
       </c>
       <c r="Q89" s="74" t="s">
-        <v>1735</v>
+        <v>1731</v>
       </c>
       <c r="R89" s="74" t="s">
         <v>1291</v>
       </c>
       <c r="S89" s="74" t="s">
-        <v>1736</v>
+        <v>1732</v>
       </c>
       <c r="T89" s="74" t="s">
         <v>1292</v>
       </c>
       <c r="U89" s="74" t="s">
-        <v>1737</v>
+        <v>1733</v>
       </c>
       <c r="V89" s="74" t="s">
         <v>1293</v>
       </c>
       <c r="W89" s="74" t="s">
-        <v>1738</v>
+        <v>1734</v>
       </c>
       <c r="X89" s="16">
         <v>4</v>
       </c>
       <c r="Y89" s="74" t="s">
-        <v>1739</v>
+        <v>1735</v>
       </c>
       <c r="Z89" s="74" t="s">
-        <v>1740</v>
+        <v>1736</v>
       </c>
       <c r="AA89" s="74"/>
     </row>
@@ -16722,10 +17095,10 @@
         <v>25</v>
       </c>
       <c r="E90" s="74" t="s">
-        <v>1741</v>
+        <v>1737</v>
       </c>
       <c r="F90" s="74" t="s">
-        <v>1742</v>
+        <v>1738</v>
       </c>
       <c r="G90" s="74"/>
       <c r="H90" s="74"/>
@@ -16736,40 +17109,40 @@
       <c r="M90" s="74"/>
       <c r="N90" s="74"/>
       <c r="O90" s="74" t="s">
-        <v>1743</v>
+        <v>1739</v>
       </c>
       <c r="P90" s="74" t="s">
         <v>1295</v>
       </c>
       <c r="Q90" s="74" t="s">
-        <v>1744</v>
+        <v>1740</v>
       </c>
       <c r="R90" s="74" t="s">
         <v>1296</v>
       </c>
       <c r="S90" s="74" t="s">
-        <v>1745</v>
+        <v>1741</v>
       </c>
       <c r="T90" s="74" t="s">
         <v>1297</v>
       </c>
       <c r="U90" s="74" t="s">
-        <v>1746</v>
+        <v>1742</v>
       </c>
       <c r="V90" s="74" t="s">
         <v>1268</v>
       </c>
       <c r="W90" s="74" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="X90" s="16">
         <v>1</v>
       </c>
       <c r="Y90" s="74" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
       <c r="Z90" s="74" t="s">
-        <v>1748</v>
+        <v>1744</v>
       </c>
       <c r="AA90" s="74"/>
     </row>
@@ -16787,10 +17160,10 @@
         <v>29</v>
       </c>
       <c r="E91" s="74" t="s">
-        <v>1759</v>
+        <v>1755</v>
       </c>
       <c r="F91" s="74" t="s">
-        <v>1760</v>
+        <v>1756</v>
       </c>
       <c r="G91" s="74"/>
       <c r="H91" s="74"/>
@@ -16802,37 +17175,37 @@
       <c r="N91" s="74"/>
       <c r="O91" s="74"/>
       <c r="P91" s="76" t="s">
+        <v>1857</v>
+      </c>
+      <c r="Q91" s="76" t="s">
+        <v>1858</v>
+      </c>
+      <c r="R91" s="76" t="s">
+        <v>1859</v>
+      </c>
+      <c r="S91" s="76" t="s">
+        <v>1860</v>
+      </c>
+      <c r="T91" s="76" t="s">
+        <v>1861</v>
+      </c>
+      <c r="U91" s="76" t="s">
+        <v>1862</v>
+      </c>
+      <c r="V91" s="76" t="s">
         <v>1863</v>
       </c>
-      <c r="Q91" s="76" t="s">
+      <c r="W91" s="76" t="s">
         <v>1864</v>
-      </c>
-      <c r="R91" s="76" t="s">
-        <v>1865</v>
-      </c>
-      <c r="S91" s="76" t="s">
-        <v>1866</v>
-      </c>
-      <c r="T91" s="76" t="s">
-        <v>1867</v>
-      </c>
-      <c r="U91" s="76" t="s">
-        <v>1868</v>
-      </c>
-      <c r="V91" s="76" t="s">
-        <v>1869</v>
-      </c>
-      <c r="W91" s="76" t="s">
-        <v>1870</v>
       </c>
       <c r="X91" s="16">
         <v>2</v>
       </c>
       <c r="Y91" s="74" t="s">
-        <v>1761</v>
+        <v>1757</v>
       </c>
       <c r="Z91" s="74" t="s">
-        <v>1762</v>
+        <v>1758</v>
       </c>
       <c r="AA91" s="74"/>
     </row>
@@ -16850,10 +17223,10 @@
         <v>29</v>
       </c>
       <c r="E92" s="74" t="s">
-        <v>1763</v>
+        <v>1759</v>
       </c>
       <c r="F92" s="74" t="s">
-        <v>1764</v>
+        <v>1760</v>
       </c>
       <c r="G92" s="74"/>
       <c r="H92" s="74"/>
@@ -16865,37 +17238,37 @@
       <c r="N92" s="74"/>
       <c r="O92" s="74"/>
       <c r="P92" s="74" t="s">
+        <v>1761</v>
+      </c>
+      <c r="Q92" s="74" t="s">
+        <v>1762</v>
+      </c>
+      <c r="R92" s="74" t="s">
+        <v>1763</v>
+      </c>
+      <c r="S92" s="74" t="s">
+        <v>1764</v>
+      </c>
+      <c r="T92" s="74" t="s">
         <v>1765</v>
       </c>
-      <c r="Q92" s="74" t="s">
+      <c r="U92" s="74" t="s">
         <v>1766</v>
       </c>
-      <c r="R92" s="74" t="s">
+      <c r="V92" s="74" t="s">
         <v>1767</v>
       </c>
-      <c r="S92" s="74" t="s">
+      <c r="W92" s="74" t="s">
         <v>1768</v>
       </c>
-      <c r="T92" s="74" t="s">
+      <c r="X92" s="16">
+        <v>1</v>
+      </c>
+      <c r="Y92" s="74" t="s">
         <v>1769</v>
       </c>
-      <c r="U92" s="74" t="s">
+      <c r="Z92" s="74" t="s">
         <v>1770</v>
-      </c>
-      <c r="V92" s="74" t="s">
-        <v>1771</v>
-      </c>
-      <c r="W92" s="74" t="s">
-        <v>1772</v>
-      </c>
-      <c r="X92" s="16">
-        <v>1</v>
-      </c>
-      <c r="Y92" s="74" t="s">
-        <v>1773</v>
-      </c>
-      <c r="Z92" s="74" t="s">
-        <v>1774</v>
       </c>
       <c r="AA92" s="74"/>
     </row>
@@ -16913,10 +17286,10 @@
         <v>25</v>
       </c>
       <c r="E93" s="74" t="s">
-        <v>1775</v>
+        <v>1771</v>
       </c>
       <c r="F93" s="74" t="s">
-        <v>1776</v>
+        <v>1772</v>
       </c>
       <c r="G93" s="74"/>
       <c r="H93" s="74"/>
@@ -16927,40 +17300,40 @@
       <c r="M93" s="74"/>
       <c r="N93" s="74"/>
       <c r="O93" s="74" t="s">
-        <v>1777</v>
+        <v>1773</v>
       </c>
       <c r="P93" s="76" t="s">
+        <v>1865</v>
+      </c>
+      <c r="Q93" s="76" t="s">
+        <v>1866</v>
+      </c>
+      <c r="R93" s="76" t="s">
+        <v>1867</v>
+      </c>
+      <c r="S93" s="76" t="s">
+        <v>1868</v>
+      </c>
+      <c r="T93" s="76" t="s">
+        <v>1869</v>
+      </c>
+      <c r="U93" s="76" t="s">
+        <v>1870</v>
+      </c>
+      <c r="V93" s="76" t="s">
         <v>1871</v>
       </c>
-      <c r="Q93" s="76" t="s">
+      <c r="W93" s="76" t="s">
         <v>1872</v>
-      </c>
-      <c r="R93" s="76" t="s">
-        <v>1873</v>
-      </c>
-      <c r="S93" s="76" t="s">
-        <v>1874</v>
-      </c>
-      <c r="T93" s="76" t="s">
-        <v>1875</v>
-      </c>
-      <c r="U93" s="76" t="s">
-        <v>1876</v>
-      </c>
-      <c r="V93" s="76" t="s">
-        <v>1877</v>
-      </c>
-      <c r="W93" s="76" t="s">
-        <v>1878</v>
       </c>
       <c r="X93" s="16">
         <v>3</v>
       </c>
       <c r="Y93" s="74" t="s">
-        <v>1778</v>
+        <v>1774</v>
       </c>
       <c r="Z93" s="74" t="s">
-        <v>1779</v>
+        <v>1775</v>
       </c>
       <c r="AA93" s="74"/>
     </row>
@@ -16978,10 +17351,10 @@
         <v>29</v>
       </c>
       <c r="E94" s="74" t="s">
-        <v>1780</v>
+        <v>1776</v>
       </c>
       <c r="F94" s="74" t="s">
-        <v>1781</v>
+        <v>1777</v>
       </c>
       <c r="G94" s="74"/>
       <c r="H94" s="74"/>
@@ -16996,34 +17369,34 @@
         <v>1301</v>
       </c>
       <c r="Q94" s="74" t="s">
-        <v>1782</v>
+        <v>1778</v>
       </c>
       <c r="R94" s="74" t="s">
-        <v>1783</v>
+        <v>1779</v>
       </c>
       <c r="S94" s="74" t="s">
-        <v>1784</v>
+        <v>1780</v>
       </c>
       <c r="T94" s="74" t="s">
         <v>1302</v>
       </c>
       <c r="U94" s="74" t="s">
-        <v>1785</v>
+        <v>1781</v>
       </c>
       <c r="V94" s="74" t="s">
         <v>1303</v>
       </c>
       <c r="W94" s="74" t="s">
-        <v>1786</v>
+        <v>1782</v>
       </c>
       <c r="X94" s="16">
         <v>1</v>
       </c>
       <c r="Y94" s="74" t="s">
-        <v>1787</v>
+        <v>1783</v>
       </c>
       <c r="Z94" s="74" t="s">
-        <v>1788</v>
+        <v>1784</v>
       </c>
       <c r="AA94" s="74"/>
     </row>
@@ -17041,10 +17414,10 @@
         <v>25</v>
       </c>
       <c r="E95" s="74" t="s">
-        <v>1789</v>
+        <v>1785</v>
       </c>
       <c r="F95" s="74" t="s">
-        <v>1790</v>
+        <v>1786</v>
       </c>
       <c r="G95" s="74"/>
       <c r="H95" s="74"/>
@@ -17054,41 +17427,41 @@
       <c r="L95" s="74"/>
       <c r="M95" s="74"/>
       <c r="N95" s="74"/>
-      <c r="O95" s="74" t="s">
-        <v>1791</v>
+      <c r="O95" s="75" t="s">
+        <v>1877</v>
       </c>
       <c r="P95" s="74" t="s">
-        <v>1792</v>
+        <v>1787</v>
       </c>
       <c r="Q95" s="74" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="R95" s="74" t="s">
         <v>1305</v>
       </c>
       <c r="S95" s="74" t="s">
-        <v>1794</v>
+        <v>1789</v>
       </c>
       <c r="T95" s="74" t="s">
-        <v>1795</v>
+        <v>1790</v>
       </c>
       <c r="U95" s="74" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="V95" s="74" t="s">
-        <v>1797</v>
+        <v>1792</v>
       </c>
       <c r="W95" s="74" t="s">
-        <v>1798</v>
+        <v>1793</v>
       </c>
       <c r="X95" s="16">
         <v>3</v>
       </c>
       <c r="Y95" s="74" t="s">
-        <v>1799</v>
+        <v>1794</v>
       </c>
       <c r="Z95" s="74" t="s">
-        <v>1800</v>
+        <v>1795</v>
       </c>
       <c r="AA95" s="74"/>
     </row>
@@ -17106,10 +17479,10 @@
         <v>25</v>
       </c>
       <c r="E96" s="74" t="s">
-        <v>1801</v>
+        <v>1796</v>
       </c>
       <c r="F96" s="74" t="s">
-        <v>1802</v>
+        <v>1797</v>
       </c>
       <c r="G96" s="74"/>
       <c r="H96" s="74"/>
@@ -17119,41 +17492,41 @@
       <c r="L96" s="74"/>
       <c r="M96" s="74"/>
       <c r="N96" s="74"/>
-      <c r="O96" s="74" t="s">
-        <v>1803</v>
+      <c r="O96" s="75" t="s">
+        <v>1878</v>
       </c>
       <c r="P96" s="74" t="s">
         <v>1081</v>
       </c>
       <c r="Q96" s="74" t="s">
-        <v>1804</v>
+        <v>1798</v>
       </c>
       <c r="R96" s="74" t="s">
         <v>1307</v>
       </c>
       <c r="S96" s="74" t="s">
-        <v>1805</v>
+        <v>1799</v>
       </c>
       <c r="T96" s="74" t="s">
         <v>233</v>
       </c>
       <c r="U96" s="74" t="s">
-        <v>1806</v>
+        <v>1800</v>
       </c>
       <c r="V96" s="74" t="s">
-        <v>1807</v>
+        <v>1801</v>
       </c>
       <c r="W96" s="74" t="s">
-        <v>1808</v>
+        <v>1802</v>
       </c>
       <c r="X96" s="16">
         <v>3</v>
       </c>
       <c r="Y96" s="74" t="s">
-        <v>1809</v>
+        <v>1803</v>
       </c>
       <c r="Z96" s="74" t="s">
-        <v>1810</v>
+        <v>1804</v>
       </c>
       <c r="AA96" s="74"/>
     </row>
@@ -17171,10 +17544,10 @@
         <v>29</v>
       </c>
       <c r="E97" s="74" t="s">
-        <v>1811</v>
+        <v>1805</v>
       </c>
       <c r="F97" s="74" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="G97" s="74"/>
       <c r="H97" s="74"/>
@@ -17189,7 +17562,7 @@
         <v>1309</v>
       </c>
       <c r="Q97" s="74" t="s">
-        <v>1813</v>
+        <v>1807</v>
       </c>
       <c r="R97" s="74" t="s">
         <v>393</v>
@@ -17201,22 +17574,22 @@
         <v>1310</v>
       </c>
       <c r="U97" s="74" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
       <c r="V97" s="74" t="s">
         <v>1311</v>
       </c>
       <c r="W97" s="74" t="s">
-        <v>1815</v>
+        <v>1809</v>
       </c>
       <c r="X97" s="16">
         <v>1</v>
       </c>
       <c r="Y97" s="74" t="s">
-        <v>1816</v>
+        <v>1810</v>
       </c>
       <c r="Z97" s="74" t="s">
-        <v>1817</v>
+        <v>1811</v>
       </c>
       <c r="AA97" s="74"/>
     </row>
@@ -17234,10 +17607,10 @@
         <v>29</v>
       </c>
       <c r="E98" s="74" t="s">
-        <v>1818</v>
+        <v>1812</v>
       </c>
       <c r="F98" s="74" t="s">
-        <v>1819</v>
+        <v>1813</v>
       </c>
       <c r="G98" s="74"/>
       <c r="H98" s="74"/>
@@ -17249,37 +17622,37 @@
       <c r="N98" s="74"/>
       <c r="O98" s="74"/>
       <c r="P98" s="74" t="s">
+        <v>1814</v>
+      </c>
+      <c r="Q98" s="74" t="s">
+        <v>1815</v>
+      </c>
+      <c r="R98" s="74" t="s">
+        <v>1816</v>
+      </c>
+      <c r="S98" s="74" t="s">
+        <v>1817</v>
+      </c>
+      <c r="T98" s="74" t="s">
+        <v>1818</v>
+      </c>
+      <c r="U98" s="74" t="s">
+        <v>1819</v>
+      </c>
+      <c r="V98" s="74" t="s">
         <v>1820</v>
       </c>
-      <c r="Q98" s="74" t="s">
+      <c r="W98" s="74" t="s">
         <v>1821</v>
-      </c>
-      <c r="R98" s="74" t="s">
-        <v>1822</v>
-      </c>
-      <c r="S98" s="74" t="s">
-        <v>1823</v>
-      </c>
-      <c r="T98" s="74" t="s">
-        <v>1824</v>
-      </c>
-      <c r="U98" s="74" t="s">
-        <v>1825</v>
-      </c>
-      <c r="V98" s="74" t="s">
-        <v>1826</v>
-      </c>
-      <c r="W98" s="74" t="s">
-        <v>1827</v>
       </c>
       <c r="X98" s="16">
         <v>3</v>
       </c>
       <c r="Y98" s="74" t="s">
-        <v>1828</v>
+        <v>1822</v>
       </c>
       <c r="Z98" s="74" t="s">
-        <v>1829</v>
+        <v>1823</v>
       </c>
       <c r="AA98" s="74"/>
     </row>
@@ -17297,10 +17670,10 @@
         <v>25</v>
       </c>
       <c r="E99" s="74" t="s">
-        <v>1830</v>
+        <v>1824</v>
       </c>
       <c r="F99" s="74" t="s">
-        <v>1831</v>
+        <v>1825</v>
       </c>
       <c r="G99" s="74"/>
       <c r="H99" s="74"/>
@@ -17311,40 +17684,40 @@
       <c r="M99" s="74"/>
       <c r="N99" s="74"/>
       <c r="O99" s="74" t="s">
+        <v>1826</v>
+      </c>
+      <c r="P99" s="74" t="s">
+        <v>1827</v>
+      </c>
+      <c r="Q99" s="74" t="s">
+        <v>1828</v>
+      </c>
+      <c r="R99" s="74" t="s">
+        <v>1829</v>
+      </c>
+      <c r="S99" s="74" t="s">
+        <v>1830</v>
+      </c>
+      <c r="T99" s="74" t="s">
+        <v>1831</v>
+      </c>
+      <c r="U99" s="74" t="s">
         <v>1832</v>
       </c>
-      <c r="P99" s="74" t="s">
+      <c r="V99" s="74" t="s">
         <v>1833</v>
       </c>
-      <c r="Q99" s="74" t="s">
+      <c r="W99" s="74" t="s">
         <v>1834</v>
-      </c>
-      <c r="R99" s="74" t="s">
-        <v>1835</v>
-      </c>
-      <c r="S99" s="74" t="s">
-        <v>1836</v>
-      </c>
-      <c r="T99" s="74" t="s">
-        <v>1837</v>
-      </c>
-      <c r="U99" s="74" t="s">
-        <v>1838</v>
-      </c>
-      <c r="V99" s="74" t="s">
-        <v>1839</v>
-      </c>
-      <c r="W99" s="74" t="s">
-        <v>1840</v>
       </c>
       <c r="X99" s="16">
         <v>3</v>
       </c>
       <c r="Y99" s="74" t="s">
-        <v>1841</v>
+        <v>1835</v>
       </c>
       <c r="Z99" s="74" t="s">
-        <v>1842</v>
+        <v>1836</v>
       </c>
       <c r="AA99" s="74"/>
     </row>
@@ -17362,10 +17735,10 @@
         <v>25</v>
       </c>
       <c r="E100" s="74" t="s">
-        <v>1843</v>
+        <v>1837</v>
       </c>
       <c r="F100" s="74" t="s">
-        <v>1844</v>
+        <v>1838</v>
       </c>
       <c r="G100" s="74"/>
       <c r="H100" s="74"/>
@@ -17376,40 +17749,40 @@
       <c r="M100" s="74"/>
       <c r="N100" s="74"/>
       <c r="O100" s="74" t="s">
+        <v>1839</v>
+      </c>
+      <c r="P100" s="74" t="s">
+        <v>1840</v>
+      </c>
+      <c r="Q100" s="74" t="s">
+        <v>1841</v>
+      </c>
+      <c r="R100" s="74" t="s">
+        <v>1842</v>
+      </c>
+      <c r="S100" s="74" t="s">
+        <v>1843</v>
+      </c>
+      <c r="T100" s="74" t="s">
+        <v>1844</v>
+      </c>
+      <c r="U100" s="74" t="s">
         <v>1845</v>
       </c>
-      <c r="P100" s="74" t="s">
+      <c r="V100" s="74" t="s">
         <v>1846</v>
       </c>
-      <c r="Q100" s="74" t="s">
+      <c r="W100" s="74" t="s">
         <v>1847</v>
-      </c>
-      <c r="R100" s="74" t="s">
-        <v>1848</v>
-      </c>
-      <c r="S100" s="74" t="s">
-        <v>1849</v>
-      </c>
-      <c r="T100" s="74" t="s">
-        <v>1850</v>
-      </c>
-      <c r="U100" s="74" t="s">
-        <v>1851</v>
-      </c>
-      <c r="V100" s="74" t="s">
-        <v>1852</v>
-      </c>
-      <c r="W100" s="74" t="s">
-        <v>1853</v>
       </c>
       <c r="X100" s="16">
         <v>4</v>
       </c>
       <c r="Y100" s="74" t="s">
-        <v>1854</v>
+        <v>1848</v>
       </c>
       <c r="Z100" s="74" t="s">
-        <v>1855</v>
+        <v>1849</v>
       </c>
       <c r="AA100" s="74"/>
     </row>
